--- a/web/files/九龙-何文田-天铸 (第2期).xlsx
+++ b/web/files/九龙-何文田-天铸 (第2期).xlsx
@@ -766,7 +766,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>2016-04-07</t>
+          <t>2016-04-08</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
@@ -898,7 +898,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2016-04-20</t>
+          <t>2016-04-21</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -960,7 +960,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2024-05-26</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2016-05-08</t>
+          <t>2016-05-09</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2016-05-12</t>
+          <t>2016-05-13</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2016-04-14</t>
+          <t>2016-04-15</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2016-04-14</t>
+          <t>2016-04-15</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2016-05-17</t>
+          <t>2016-05-18</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2019-04-03</t>
+          <t>2019-04-04</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1588,7 +1588,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2016-05-05</t>
+          <t>2016-05-06</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2016-04-07</t>
+          <t>2016-04-08</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2023-03-20</t>
+          <t>2023-03-21</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2016-05-09</t>
+          <t>2016-05-10</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2016-04-28</t>
+          <t>2016-04-29</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2023-04-03</t>
+          <t>2023-04-04</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2023-03-05</t>
+          <t>2023-03-06</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2016-05-15</t>
+          <t>2016-05-16</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2016-05-15</t>
+          <t>2016-05-16</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2016-05-08</t>
+          <t>2016-05-09</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2023-03-02</t>
+          <t>2023-03-03</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2332,7 +2332,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2016-05-11</t>
+          <t>2016-05-12</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2016-05-17</t>
+          <t>2016-05-18</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2016-05-17</t>
+          <t>2016-05-18</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2019-04-03</t>
+          <t>2019-04-04</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2016-05-10</t>
+          <t>2016-05-11</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2016-05-02</t>
+          <t>2016-05-03</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2704,7 +2704,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2021-11-16</t>
+          <t>2021-11-17</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2766,7 +2766,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2019-09-22</t>
+          <t>2019-09-23</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2016-05-17</t>
+          <t>2016-05-18</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -2890,7 +2890,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2016-05-02</t>
+          <t>2016-05-03</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -2952,7 +2952,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2021-10-10</t>
+          <t>2021-10-11</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2019-04-09</t>
+          <t>2019-04-10</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2016-05-09</t>
+          <t>2016-05-10</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2016-04-26</t>
+          <t>2016-04-27</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -3200,7 +3200,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2016-04-14</t>
+          <t>2016-04-15</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2016-05-09</t>
+          <t>2016-05-10</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -3324,7 +3324,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2016-05-16</t>
+          <t>2016-05-17</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2016-04-28</t>
+          <t>2016-04-29</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2016-05-04</t>
+          <t>2016-05-05</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -3510,7 +3510,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2016-04-25</t>
+          <t>2016-04-26</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -3572,7 +3572,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2016-05-09</t>
+          <t>2016-05-10</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -3634,7 +3634,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2016-05-05</t>
+          <t>2016-05-06</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2016-05-17</t>
+          <t>2016-05-18</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2016-05-17</t>
+          <t>2016-05-18</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -3820,7 +3820,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2016-05-12</t>
+          <t>2016-05-13</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2016-04-28</t>
+          <t>2016-04-29</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2016-04-26</t>
+          <t>2016-04-27</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2016-04-26</t>
+          <t>2016-04-27</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -4068,7 +4068,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2016-05-12</t>
+          <t>2016-05-13</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -4130,7 +4130,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2016-05-12</t>
+          <t>2016-05-13</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -4192,7 +4192,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2016-03-31</t>
+          <t>2016-04-01</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2016-03-31</t>
+          <t>2016-04-01</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2016-05-09</t>
+          <t>2016-05-10</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2016-04-24</t>
+          <t>2016-04-25</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2016-05-08</t>
+          <t>2016-05-09</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -4502,7 +4502,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2016-04-18</t>
+          <t>2016-04-19</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2016-04-14</t>
+          <t>2016-04-15</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2016-04-26</t>
+          <t>2016-04-27</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -4688,7 +4688,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2016-05-03</t>
+          <t>2016-05-04</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -4750,7 +4750,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2016-04-25</t>
+          <t>2016-04-26</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -4874,7 +4874,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2016-05-10</t>
+          <t>2016-05-11</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -4936,7 +4936,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2016-04-19</t>
+          <t>2016-04-20</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -4998,7 +4998,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2016-04-19</t>
+          <t>2016-04-20</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2016-04-21</t>
+          <t>2016-04-22</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2024-04-28</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -5184,7 +5184,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2016-04-17</t>
+          <t>2016-04-18</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2016-04-17</t>
+          <t>2016-04-18</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -5308,7 +5308,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2016-04-20</t>
+          <t>2016-04-21</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -5370,7 +5370,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2016-05-05</t>
+          <t>2016-05-06</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2016-04-12</t>
+          <t>2016-04-13</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -5494,7 +5494,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2016-03-24</t>
+          <t>2016-03-25</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2019-03-03</t>
+          <t>2019-03-04</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -5618,7 +5618,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2019-01-27</t>
+          <t>2019-01-28</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -5680,7 +5680,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2016-04-17</t>
+          <t>2016-04-18</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2016-03-24</t>
+          <t>2016-03-25</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -5804,7 +5804,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2016-05-08</t>
+          <t>2016-05-09</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -5866,7 +5866,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2016-04-19</t>
+          <t>2016-04-20</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -5928,7 +5928,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2016-04-17</t>
+          <t>2016-04-18</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -5990,7 +5990,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2016-04-17</t>
+          <t>2016-04-18</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -6052,7 +6052,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -6114,7 +6114,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -6176,7 +6176,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2016-04-17</t>
+          <t>2016-04-18</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -6238,7 +6238,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2016-04-17</t>
+          <t>2016-04-18</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -6300,7 +6300,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2016-05-11</t>
+          <t>2016-05-12</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -6362,7 +6362,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2016-04-19</t>
+          <t>2016-04-20</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -6424,7 +6424,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2016-04-19</t>
+          <t>2016-04-20</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -6486,7 +6486,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2016-04-19</t>
+          <t>2016-04-20</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2016-04-21</t>
+          <t>2016-04-22</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2016-04-21</t>
+          <t>2016-04-22</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -6672,7 +6672,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2016-04-19</t>
+          <t>2016-04-20</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2016-03-24</t>
+          <t>2016-03-25</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -6796,7 +6796,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2019-08-06</t>
+          <t>2019-08-07</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -6858,7 +6858,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2019-02-17</t>
+          <t>2019-02-18</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -6920,7 +6920,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2016-04-18</t>
+          <t>2016-04-19</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -6982,7 +6982,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2016-03-24</t>
+          <t>2016-03-25</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -7044,7 +7044,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2016-04-18</t>
+          <t>2016-04-19</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2016-05-22</t>
+          <t>2016-05-23</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2016-05-03</t>
+          <t>2016-05-04</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -7230,7 +7230,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2016-05-10</t>
+          <t>2016-05-11</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -7292,7 +7292,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2016-04-19</t>
+          <t>2016-04-20</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -7354,7 +7354,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2016-04-28</t>
+          <t>2016-04-29</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -7416,7 +7416,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2016-04-20</t>
+          <t>2016-04-21</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2016-04-20</t>
+          <t>2016-04-21</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2016-04-20</t>
+          <t>2016-04-21</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -7602,7 +7602,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2016-04-20</t>
+          <t>2016-04-21</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
@@ -7664,7 +7664,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2016-04-18</t>
+          <t>2016-04-19</t>
         </is>
       </c>
       <c r="H114" s="5" t="n">
@@ -7726,7 +7726,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2016-04-13</t>
+          <t>2016-04-14</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2016-04-14</t>
+          <t>2016-04-15</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -7850,7 +7850,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2016-04-14</t>
+          <t>2016-04-15</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -7912,7 +7912,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2016-04-25</t>
+          <t>2016-04-26</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -7974,7 +7974,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2016-05-04</t>
+          <t>2016-05-05</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2016-04-19</t>
+          <t>2016-04-20</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -8098,7 +8098,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2016-04-21</t>
+          <t>2016-04-22</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -8160,7 +8160,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2016-04-26</t>
+          <t>2016-04-27</t>
         </is>
       </c>
       <c r="H122" s="5" t="n">
@@ -8222,7 +8222,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2016-04-26</t>
+          <t>2016-04-27</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -8284,7 +8284,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2016-04-21</t>
+          <t>2016-04-22</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
@@ -8346,7 +8346,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2016-04-18</t>
+          <t>2016-04-19</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -8408,7 +8408,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2016-05-08</t>
+          <t>2016-05-09</t>
         </is>
       </c>
       <c r="H126" s="5" t="n">
@@ -8470,7 +8470,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2016-05-05</t>
+          <t>2016-05-06</t>
         </is>
       </c>
       <c r="H127" s="5" t="n">
@@ -8532,7 +8532,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2016-04-18</t>
+          <t>2016-04-19</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -8594,7 +8594,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2016-05-16</t>
+          <t>2016-05-17</t>
         </is>
       </c>
       <c r="H129" s="5" t="n">
@@ -8656,7 +8656,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2016-04-26</t>
+          <t>2016-04-27</t>
         </is>
       </c>
       <c r="H130" s="5" t="n">
@@ -8718,7 +8718,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2016-04-26</t>
+          <t>2016-04-27</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -8780,7 +8780,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2016-04-18</t>
+          <t>2016-04-19</t>
         </is>
       </c>
       <c r="H132" s="5" t="n">
@@ -8842,7 +8842,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="H133" s="5" t="n">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2016-05-16</t>
+          <t>2016-05-17</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2019-11-03</t>
+          <t>2019-11-04</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -9028,7 +9028,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="H136" s="5" t="n">
@@ -9090,7 +9090,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2016-05-15</t>
+          <t>2016-05-16</t>
         </is>
       </c>
       <c r="H137" s="5" t="n">
@@ -9152,7 +9152,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2016-04-26</t>
+          <t>2016-04-27</t>
         </is>
       </c>
       <c r="H138" s="5" t="n">
@@ -9214,7 +9214,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="H139" s="5" t="n">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2019-02-20</t>
+          <t>2019-02-21</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -9338,7 +9338,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2019-07-29</t>
+          <t>2019-07-30</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
@@ -9400,7 +9400,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2016-04-26</t>
+          <t>2016-04-27</t>
         </is>
       </c>
       <c r="H142" s="5" t="n">
@@ -9462,7 +9462,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2016-03-31</t>
+          <t>2016-04-01</t>
         </is>
       </c>
       <c r="H143" s="5" t="n">
@@ -9524,7 +9524,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2016-04-24</t>
+          <t>2016-04-25</t>
         </is>
       </c>
       <c r="H144" s="5" t="n">
@@ -9586,7 +9586,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2019-02-25</t>
+          <t>2019-02-26</t>
         </is>
       </c>
       <c r="H145" s="5" t="n">
@@ -9648,7 +9648,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2016-04-26</t>
+          <t>2016-04-27</t>
         </is>
       </c>
       <c r="H146" s="5" t="n">
@@ -9710,7 +9710,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2016-04-20</t>
+          <t>2016-04-21</t>
         </is>
       </c>
       <c r="H147" s="5" t="n">
@@ -9772,7 +9772,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2016-05-16</t>
+          <t>2016-05-17</t>
         </is>
       </c>
       <c r="H148" s="5" t="n">
@@ -9834,7 +9834,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>2019-01-30</t>
+          <t>2019-01-31</t>
         </is>
       </c>
       <c r="H149" s="5" t="n">
@@ -9896,7 +9896,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2016-04-26</t>
+          <t>2016-04-27</t>
         </is>
       </c>
       <c r="H150" s="5" t="n">
@@ -9958,7 +9958,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2016-04-26</t>
+          <t>2016-04-27</t>
         </is>
       </c>
       <c r="H151" s="5" t="n">
@@ -10020,7 +10020,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2016-05-09</t>
+          <t>2016-05-10</t>
         </is>
       </c>
       <c r="H152" s="5" t="n">
@@ -10082,7 +10082,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2019-01-24</t>
+          <t>2019-01-25</t>
         </is>
       </c>
       <c r="H153" s="5" t="n">
@@ -10144,7 +10144,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2016-05-08</t>
+          <t>2016-05-09</t>
         </is>
       </c>
       <c r="H154" s="5" t="n">
@@ -10206,7 +10206,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2016-05-03</t>
+          <t>2016-05-04</t>
         </is>
       </c>
       <c r="H155" s="5" t="n">
@@ -10268,7 +10268,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2016-04-14</t>
+          <t>2016-04-15</t>
         </is>
       </c>
       <c r="H156" s="5" t="n">
@@ -10330,7 +10330,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2016-04-14</t>
+          <t>2016-04-15</t>
         </is>
       </c>
       <c r="H157" s="5" t="n">
@@ -10392,7 +10392,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2016-04-20</t>
+          <t>2016-04-21</t>
         </is>
       </c>
       <c r="H158" s="5" t="n">
@@ -10454,7 +10454,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2016-04-20</t>
+          <t>2016-04-21</t>
         </is>
       </c>
       <c r="H159" s="5" t="n">
@@ -10516,7 +10516,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2016-04-20</t>
+          <t>2016-04-21</t>
         </is>
       </c>
       <c r="H160" s="5" t="n">
@@ -10578,7 +10578,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2023-05-04</t>
+          <t>2023-05-05</t>
         </is>
       </c>
       <c r="H161" s="5" t="n">
@@ -10640,7 +10640,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2016-04-18</t>
+          <t>2016-04-19</t>
         </is>
       </c>
       <c r="H162" s="5" t="n">
@@ -10702,7 +10702,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2016-04-25</t>
+          <t>2016-04-26</t>
         </is>
       </c>
       <c r="H163" s="5" t="n">
@@ -10764,7 +10764,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2016-05-15</t>
+          <t>2016-05-16</t>
         </is>
       </c>
       <c r="H164" s="5" t="n">
@@ -10826,7 +10826,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2019-01-20</t>
+          <t>2019-01-21</t>
         </is>
       </c>
       <c r="H165" s="5" t="n">
@@ -10888,7 +10888,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2016-05-16</t>
+          <t>2016-05-17</t>
         </is>
       </c>
       <c r="H166" s="5" t="n">
@@ -10950,7 +10950,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2016-04-28</t>
+          <t>2016-04-29</t>
         </is>
       </c>
       <c r="H167" s="5" t="n">
@@ -11012,7 +11012,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2016-04-28</t>
+          <t>2016-04-29</t>
         </is>
       </c>
       <c r="H168" s="5" t="n">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2019-01-17</t>
+          <t>2019-01-18</t>
         </is>
       </c>
       <c r="H169" s="5" t="n">
@@ -11136,7 +11136,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2016-04-21</t>
+          <t>2016-04-22</t>
         </is>
       </c>
       <c r="H170" s="5" t="n">
@@ -11198,7 +11198,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2016-05-12</t>
+          <t>2016-05-13</t>
         </is>
       </c>
       <c r="H171" s="5" t="n">
@@ -11260,7 +11260,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2016-04-24</t>
+          <t>2016-04-25</t>
         </is>
       </c>
       <c r="H172" s="5" t="n">
@@ -11322,7 +11322,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2016-05-08</t>
+          <t>2016-05-09</t>
         </is>
       </c>
       <c r="H173" s="5" t="n">
@@ -11384,7 +11384,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2016-05-04</t>
+          <t>2016-05-05</t>
         </is>
       </c>
       <c r="H174" s="5" t="n">
@@ -11446,7 +11446,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2016-05-04</t>
+          <t>2016-05-05</t>
         </is>
       </c>
       <c r="H175" s="5" t="n">
@@ -11508,7 +11508,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2016-04-27</t>
+          <t>2016-04-28</t>
         </is>
       </c>
       <c r="H176" s="5" t="n">
@@ -11570,7 +11570,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2019-01-21</t>
+          <t>2019-01-22</t>
         </is>
       </c>
       <c r="H177" s="5" t="n">
@@ -11632,7 +11632,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2016-04-25</t>
+          <t>2016-04-26</t>
         </is>
       </c>
       <c r="H178" s="5" t="n">
@@ -11694,7 +11694,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2016-04-19</t>
+          <t>2016-04-20</t>
         </is>
       </c>
       <c r="H179" s="5" t="n">
@@ -11756,7 +11756,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2016-05-02</t>
+          <t>2016-05-03</t>
         </is>
       </c>
       <c r="H180" s="5" t="n">
@@ -11818,7 +11818,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2019-03-03</t>
+          <t>2019-03-04</t>
         </is>
       </c>
       <c r="H181" s="5" t="n">
@@ -11880,7 +11880,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2016-04-20</t>
+          <t>2016-04-21</t>
         </is>
       </c>
       <c r="H182" s="5" t="n">
@@ -11942,7 +11942,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2016-04-25</t>
+          <t>2016-04-26</t>
         </is>
       </c>
       <c r="H183" s="5" t="n">
@@ -12004,7 +12004,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2016-03-31</t>
+          <t>2016-04-01</t>
         </is>
       </c>
       <c r="H184" s="5" t="n">
@@ -12066,7 +12066,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2016-03-31</t>
+          <t>2016-04-01</t>
         </is>
       </c>
       <c r="H185" s="5" t="n">
@@ -12128,7 +12128,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2016-04-24</t>
+          <t>2016-04-25</t>
         </is>
       </c>
       <c r="H186" s="5" t="n">
@@ -12190,7 +12190,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>2016-04-24</t>
+          <t>2016-04-25</t>
         </is>
       </c>
       <c r="H187" s="5" t="n">
@@ -12252,7 +12252,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2016-04-21</t>
+          <t>2016-04-22</t>
         </is>
       </c>
       <c r="H188" s="5" t="n">
@@ -12314,7 +12314,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2019-01-31</t>
+          <t>2019-02-01</t>
         </is>
       </c>
       <c r="H189" s="5" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2016-04-19</t>
+          <t>2016-04-20</t>
         </is>
       </c>
       <c r="H190" s="5" t="n">
@@ -12438,7 +12438,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2016-04-19</t>
+          <t>2016-04-20</t>
         </is>
       </c>
       <c r="H191" s="5" t="n">
@@ -12500,7 +12500,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2016-04-27</t>
+          <t>2016-04-28</t>
         </is>
       </c>
       <c r="H192" s="5" t="n">
@@ -12562,7 +12562,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2019-01-10</t>
+          <t>2019-01-11</t>
         </is>
       </c>
       <c r="H193" s="5" t="n">
@@ -12624,7 +12624,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2016-04-19</t>
+          <t>2016-04-20</t>
         </is>
       </c>
       <c r="H194" s="5" t="n">
@@ -12686,7 +12686,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2016-04-18</t>
+          <t>2016-04-19</t>
         </is>
       </c>
       <c r="H195" s="5" t="n">
@@ -12748,7 +12748,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2016-04-19</t>
+          <t>2016-04-20</t>
         </is>
       </c>
       <c r="H196" s="5" t="n">
@@ -12810,7 +12810,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>2019-01-14</t>
+          <t>2019-01-15</t>
         </is>
       </c>
       <c r="H197" s="5" t="n">
@@ -12872,7 +12872,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2016-04-21</t>
+          <t>2016-04-22</t>
         </is>
       </c>
       <c r="H198" s="5" t="n">
@@ -12934,7 +12934,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2016-04-21</t>
+          <t>2016-04-22</t>
         </is>
       </c>
       <c r="H199" s="5" t="n">
@@ -12996,7 +12996,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2016-05-17</t>
+          <t>2016-05-18</t>
         </is>
       </c>
       <c r="H200" s="5" t="n">
@@ -13058,7 +13058,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2016-05-03</t>
+          <t>2016-05-04</t>
         </is>
       </c>
       <c r="H201" s="5" t="n">
@@ -13120,7 +13120,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2016-04-14</t>
+          <t>2016-04-15</t>
         </is>
       </c>
       <c r="H202" s="5" t="n">
@@ -13182,7 +13182,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2016-04-21</t>
+          <t>2016-04-22</t>
         </is>
       </c>
       <c r="H203" s="5" t="n">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2019-02-14</t>
+          <t>2019-02-15</t>
         </is>
       </c>
       <c r="H204" s="5" t="n">
@@ -13306,7 +13306,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>2020-02-20</t>
+          <t>2020-02-21</t>
         </is>
       </c>
       <c r="H205" s="5" t="n">
@@ -13368,7 +13368,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>2016-04-26</t>
+          <t>2016-04-27</t>
         </is>
       </c>
       <c r="H206" s="5" t="n">
@@ -13430,7 +13430,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2016-05-08</t>
+          <t>2016-05-09</t>
         </is>
       </c>
       <c r="H207" s="5" t="n">
@@ -13492,7 +13492,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2016-05-10</t>
+          <t>2016-05-11</t>
         </is>
       </c>
       <c r="H208" s="5" t="n">
@@ -13554,7 +13554,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>2016-04-27</t>
+          <t>2016-04-28</t>
         </is>
       </c>
       <c r="H209" s="5" t="n">
@@ -13616,7 +13616,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>2016-05-04</t>
+          <t>2016-05-05</t>
         </is>
       </c>
       <c r="H210" s="5" t="n">
@@ -13678,7 +13678,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2016-05-12</t>
+          <t>2016-05-13</t>
         </is>
       </c>
       <c r="H211" s="5" t="n">
@@ -13740,7 +13740,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2016-05-10</t>
+          <t>2016-05-11</t>
         </is>
       </c>
       <c r="H212" s="5" t="n">
@@ -13802,7 +13802,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2019-01-30</t>
+          <t>2019-01-31</t>
         </is>
       </c>
       <c r="H213" s="5" t="n">
@@ -13864,7 +13864,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2016-04-28</t>
+          <t>2016-04-29</t>
         </is>
       </c>
       <c r="H214" s="5" t="n">
@@ -13926,7 +13926,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2016-05-11</t>
+          <t>2016-05-12</t>
         </is>
       </c>
       <c r="H215" s="5" t="n">
@@ -13988,7 +13988,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>2016-05-11</t>
+          <t>2016-05-12</t>
         </is>
       </c>
       <c r="H216" s="5" t="n">
@@ -14050,7 +14050,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>2019-01-14</t>
+          <t>2019-01-15</t>
         </is>
       </c>
       <c r="H217" s="5" t="n">
@@ -14112,7 +14112,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>2016-04-14</t>
+          <t>2016-04-15</t>
         </is>
       </c>
       <c r="H218" s="5" t="n">
@@ -14174,7 +14174,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2016-04-28</t>
+          <t>2016-04-29</t>
         </is>
       </c>
       <c r="H219" s="5" t="n">
@@ -14236,7 +14236,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2016-04-14</t>
+          <t>2016-04-15</t>
         </is>
       </c>
       <c r="H220" s="5" t="n">
@@ -14298,7 +14298,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="H221" s="5" t="n">
@@ -14360,7 +14360,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>2016-05-08</t>
+          <t>2016-05-09</t>
         </is>
       </c>
       <c r="H222" s="5" t="n">
@@ -14422,7 +14422,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2016-05-16</t>
+          <t>2016-05-17</t>
         </is>
       </c>
       <c r="H223" s="5" t="n">
@@ -14484,7 +14484,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2016-05-17</t>
+          <t>2016-05-18</t>
         </is>
       </c>
       <c r="H224" s="5" t="n">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2019-01-06</t>
+          <t>2019-01-07</t>
         </is>
       </c>
       <c r="H225" s="5" t="n">
@@ -14608,7 +14608,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2016-05-08</t>
+          <t>2016-05-09</t>
         </is>
       </c>
       <c r="H226" s="5" t="n">
@@ -14670,7 +14670,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>2016-05-12</t>
+          <t>2016-05-13</t>
         </is>
       </c>
       <c r="H227" s="5" t="n">
@@ -14732,7 +14732,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2016-05-12</t>
+          <t>2016-05-13</t>
         </is>
       </c>
       <c r="H228" s="5" t="n">
@@ -14794,7 +14794,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>2019-01-16</t>
+          <t>2019-01-17</t>
         </is>
       </c>
       <c r="H229" s="5" t="n">
@@ -14856,7 +14856,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>2016-05-16</t>
+          <t>2016-05-17</t>
         </is>
       </c>
       <c r="H230" s="5" t="n">
@@ -14918,7 +14918,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>2016-05-04</t>
+          <t>2016-05-05</t>
         </is>
       </c>
       <c r="H231" s="5" t="n">
@@ -14980,7 +14980,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2016-05-15</t>
+          <t>2016-05-16</t>
         </is>
       </c>
       <c r="H232" s="5" t="n">
@@ -15042,7 +15042,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>2019-01-16</t>
+          <t>2019-01-17</t>
         </is>
       </c>
       <c r="H233" s="5" t="n">
@@ -15104,7 +15104,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2016-05-12</t>
+          <t>2016-05-13</t>
         </is>
       </c>
       <c r="H234" s="5" t="n">
@@ -15166,7 +15166,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2016-05-05</t>
+          <t>2016-05-06</t>
         </is>
       </c>
       <c r="H235" s="5" t="n">
@@ -15228,7 +15228,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2016-05-12</t>
+          <t>2016-05-13</t>
         </is>
       </c>
       <c r="H236" s="5" t="n">
@@ -15290,7 +15290,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2019-01-06</t>
+          <t>2019-01-07</t>
         </is>
       </c>
       <c r="H237" s="5" t="n">
@@ -15352,7 +15352,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2016-05-16</t>
+          <t>2016-05-17</t>
         </is>
       </c>
       <c r="H238" s="5" t="n">
@@ -15414,7 +15414,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>2016-05-04</t>
+          <t>2016-05-05</t>
         </is>
       </c>
       <c r="H239" s="5" t="n">
@@ -15476,7 +15476,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>2016-05-11</t>
+          <t>2016-05-12</t>
         </is>
       </c>
       <c r="H240" s="5" t="n">
@@ -15538,7 +15538,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>2019-01-16</t>
+          <t>2019-01-17</t>
         </is>
       </c>
       <c r="H241" s="5" t="n">
@@ -15600,7 +15600,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2016-04-27</t>
+          <t>2016-04-28</t>
         </is>
       </c>
       <c r="H242" s="5" t="n">
@@ -15662,7 +15662,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>2016-04-27</t>
+          <t>2016-04-28</t>
         </is>
       </c>
       <c r="H243" s="5" t="n">
@@ -15724,7 +15724,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>2016-05-10</t>
+          <t>2016-05-11</t>
         </is>
       </c>
       <c r="H244" s="5" t="n">
@@ -15786,7 +15786,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>2016-05-08</t>
+          <t>2016-05-09</t>
         </is>
       </c>
       <c r="H245" s="5" t="n">
@@ -15848,7 +15848,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>2016-04-28</t>
+          <t>2016-04-29</t>
         </is>
       </c>
       <c r="H246" s="5" t="n">
@@ -15910,7 +15910,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>2016-04-26</t>
+          <t>2016-04-27</t>
         </is>
       </c>
       <c r="H247" s="5" t="n">
@@ -15972,7 +15972,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>2016-05-11</t>
+          <t>2016-05-12</t>
         </is>
       </c>
       <c r="H248" s="5" t="n">
@@ -16034,7 +16034,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>2016-05-09</t>
+          <t>2016-05-10</t>
         </is>
       </c>
       <c r="H249" s="5" t="n">
@@ -16096,7 +16096,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>2016-04-14</t>
+          <t>2016-04-15</t>
         </is>
       </c>
       <c r="H250" s="5" t="n">
@@ -16158,7 +16158,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>2016-05-11</t>
+          <t>2016-05-12</t>
         </is>
       </c>
       <c r="H251" s="5" t="n">
@@ -16220,7 +16220,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>2016-05-16</t>
+          <t>2016-05-17</t>
         </is>
       </c>
       <c r="H252" s="5" t="n">
@@ -16282,7 +16282,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>2016-05-19</t>
+          <t>2016-05-20</t>
         </is>
       </c>
       <c r="H253" s="5" t="n">
@@ -16344,7 +16344,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>2016-05-02</t>
+          <t>2016-05-03</t>
         </is>
       </c>
       <c r="H254" s="5" t="n">
@@ -16406,7 +16406,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>2016-05-15</t>
+          <t>2016-05-16</t>
         </is>
       </c>
       <c r="H255" s="5" t="n">
@@ -16468,7 +16468,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>2016-05-17</t>
+          <t>2016-05-18</t>
         </is>
       </c>
       <c r="H256" s="5" t="n">
@@ -16530,7 +16530,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>2019-01-15</t>
+          <t>2019-01-16</t>
         </is>
       </c>
       <c r="H257" s="5" t="n">
@@ -16592,7 +16592,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>2016-04-28</t>
+          <t>2016-04-29</t>
         </is>
       </c>
       <c r="H258" s="5" t="n">
@@ -16654,7 +16654,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>2016-05-09</t>
+          <t>2016-05-10</t>
         </is>
       </c>
       <c r="H259" s="5" t="n">
@@ -16716,7 +16716,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>2016-05-15</t>
+          <t>2016-05-16</t>
         </is>
       </c>
       <c r="H260" s="5" t="n">
@@ -16778,7 +16778,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>2019-01-03</t>
+          <t>2019-01-04</t>
         </is>
       </c>
       <c r="H261" s="5" t="n">
@@ -16840,7 +16840,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>2016-04-27</t>
+          <t>2016-04-28</t>
         </is>
       </c>
       <c r="H262" s="5" t="n">
@@ -16902,7 +16902,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>2016-04-14</t>
+          <t>2016-04-15</t>
         </is>
       </c>
       <c r="H263" s="5" t="n">
@@ -16964,7 +16964,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>2016-05-15</t>
+          <t>2016-05-16</t>
         </is>
       </c>
       <c r="H264" s="5" t="n">
@@ -17026,7 +17026,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>2016-05-12</t>
+          <t>2016-05-13</t>
         </is>
       </c>
       <c r="H265" s="5" t="n">
@@ -17088,7 +17088,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>2016-04-26</t>
+          <t>2016-04-27</t>
         </is>
       </c>
       <c r="H266" s="5" t="n">
@@ -17150,7 +17150,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>2016-05-18</t>
+          <t>2016-05-19</t>
         </is>
       </c>
       <c r="H267" s="5" t="n">
@@ -17212,7 +17212,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>2016-05-15</t>
+          <t>2016-05-16</t>
         </is>
       </c>
       <c r="H268" s="5" t="n">
@@ -17274,7 +17274,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>2016-05-15</t>
+          <t>2016-05-16</t>
         </is>
       </c>
       <c r="H269" s="5" t="n">
@@ -17336,7 +17336,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>2016-05-16</t>
+          <t>2016-05-17</t>
         </is>
       </c>
       <c r="H270" s="5" t="n">
@@ -17398,7 +17398,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="H271" s="5" t="n">
@@ -17460,7 +17460,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>2016-05-18</t>
+          <t>2016-05-19</t>
         </is>
       </c>
       <c r="H272" s="5" t="n">
@@ -17522,7 +17522,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>2016-04-07</t>
+          <t>2016-04-08</t>
         </is>
       </c>
       <c r="H273" s="5" t="n">
@@ -17696,7 +17696,7 @@
           <t>C | 2503呎 (4+房)
 $8719万
 $34,834/呎
-(16年-04月-07日)</t>
+(16年-04月-08日)</t>
         </is>
       </c>
       <c r="E5" s="21" t="inlineStr"/>
@@ -17720,7 +17720,7 @@
           <t>B | 2442呎 (4+房)
 $13076万
 $53,546/呎
-(24年-05月-26日)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="D6" s="22" t="inlineStr">
@@ -17728,7 +17728,7 @@
           <t>C | 2489呎 (4+房)
 $10247万
 $41,169/呎
-(16年-04月-20日)</t>
+(16年-04月-21日)</t>
         </is>
       </c>
       <c r="E6" s="21" t="inlineStr"/>
@@ -17744,7 +17744,7 @@
           <t>A | 1910呎 (4+房)
 $7752万
 $40,584/呎
-(25年-11月-12日)</t>
+(25年-11月-13日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -17752,7 +17752,7 @@
           <t>B | 1731呎 (4+房)
 $7478万
 $43,203/呎
-(25年-10月-27日)</t>
+(25年-10月-28日)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -17760,7 +17760,7 @@
           <t>C | 1154呎 (3房)
 $3469万
 $30,058/呎
-(16年-05月-12日)</t>
+(16年-05月-13日)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -17768,7 +17768,7 @@
           <t>D | 994呎 (3房)
 $2977万
 $29,953/呎
-(16年-05月-08日)</t>
+(16年-05月-09日)</t>
         </is>
       </c>
     </row>
@@ -17783,7 +17783,7 @@
           <t>A | 1910呎 (4+房)
 $8480万
 $44,397/呎
-(19年-04月-03日)</t>
+(19年-04月-04日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -17791,7 +17791,7 @@
           <t>B | 1823呎 (4+房)
 $9466万
 $51,927/呎
-(16年-05月-17日)</t>
+(16年-05月-18日)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -17799,7 +17799,7 @@
           <t>C | 1154呎 (3房)
 $6396万
 $55,425/呎
-(16年-04月-14日)</t>
+(16年-04月-15日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -17807,7 +17807,7 @@
           <t>D | 994呎 (3房)
 $6396万
 $64,346/呎
-(16年-04月-14日)</t>
+(16年-04月-15日)</t>
         </is>
       </c>
     </row>
@@ -17822,7 +17822,7 @@
           <t>A | 1910呎 (4+房)
 $7227万
 $37,837/呎
-(25年-08月-19日)</t>
+(25年-08月-20日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -17830,7 +17830,7 @@
           <t>B | 1731呎 (4+房)
 $7854万
 $45,373/呎
-(23年-03月-20日)</t>
+(23年-03月-21日)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -17838,7 +17838,7 @@
           <t>C | 1154呎 (3房)
 $3377万
 $29,263/呎
-(16年-04月-07日)</t>
+(16年-04月-08日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -17846,7 +17846,7 @@
           <t>D | 994呎 (3房)
 $2968万
 $29,863/呎
-(16年-05月-05日)</t>
+(16年-05月-06日)</t>
         </is>
       </c>
     </row>
@@ -17861,7 +17861,7 @@
           <t>A | 1910呎 (4+房)
 $8610万
 $45,078/呎
-(23年-03月-05日)</t>
+(23年-03月-06日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -17869,7 +17869,7 @@
           <t>B | 1731呎 (4+房)
 $7754万
 $44,794/呎
-(23年-04月-03日)</t>
+(23年-04月-04日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -17877,7 +17877,7 @@
           <t>C | 1154呎 (3房)
 $3364万
 $29,146/呎
-(16年-04月-28日)</t>
+(16年-04月-29日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -17885,7 +17885,7 @@
           <t>D | 994呎 (3房)
 $2951万
 $29,685/呎
-(16年-05月-09日)</t>
+(16年-05月-10日)</t>
         </is>
       </c>
     </row>
@@ -17900,7 +17900,7 @@
           <t>A | 1910呎 (4+房)
 $8572万
 $44,880/呎
-(23年-03月-02日)</t>
+(23年-03月-03日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -17908,7 +17908,7 @@
           <t>B | 1823呎 (4+房)
 $8529万
 $46,787/呎
-(16年-05月-08日)</t>
+(16年-05月-09日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -17916,7 +17916,7 @@
           <t>C | 1154呎 (3房)
 $3357万
 $29,088/呎
-(16年-05月-15日)</t>
+(16年-05月-16日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -17924,7 +17924,7 @@
           <t>D | 994呎 (3房)
 $2942万
 $29,596/呎
-(16年-05月-15日)</t>
+(16年-05月-16日)</t>
         </is>
       </c>
     </row>
@@ -17939,7 +17939,7 @@
           <t>A | 1910呎 (4+房)
 $7672万
 $40,169/呎
-(19年-04月-03日)</t>
+(19年-04月-04日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -17947,7 +17947,7 @@
           <t>B | 1823呎 (4+房)
 $8333万
 $45,711/呎
-(16年-05月-17日)</t>
+(16年-05月-18日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -17955,7 +17955,7 @@
           <t>C | 1154呎 (3房)
 $3347万
 $29,001/呎
-(16年-05月-17日)</t>
+(16年-05月-18日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -17963,7 +17963,7 @@
           <t>D | 994呎 (3房)
 $2933万
 $29,507/呎
-(16年-05月-11日)</t>
+(16年-05月-12日)</t>
         </is>
       </c>
     </row>
@@ -17978,7 +17978,7 @@
           <t>A | 2019呎 (4+房)
 $8076万
 $40,000/呎
-(19年-09月-22日)</t>
+(19年-09月-23日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -17986,7 +17986,7 @@
           <t>B | 1823呎 (4+房)
 $7295万
 $40,018/呎
-(21年-11月-16日)</t>
+(21年-11月-17日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -17994,7 +17994,7 @@
           <t>C | 1154呎 (3房)
 $3286万
 $28,479/呎
-(16年-05月-02日)</t>
+(16年-05月-03日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -18002,7 +18002,7 @@
           <t>D | 994呎 (3房)
 $2895万
 $29,124/呎
-(16年-05月-10日)</t>
+(16年-05月-11日)</t>
         </is>
       </c>
     </row>
@@ -18017,7 +18017,7 @@
           <t>A | 1910呎 (4+房)
 $8087万
 $42,338/呎
-(19年-04月-09日)</t>
+(19年-04月-10日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -18025,7 +18025,7 @@
           <t>B | 1823呎 (4+房)
 $6927万
 $38,000/呎
-(21年-10月-10日)</t>
+(21年-10月-11日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -18033,7 +18033,7 @@
           <t>C | 1154呎 (3房)
 $3211万
 $27,824/呎
-(16年-05月-02日)</t>
+(16年-05月-03日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -18041,7 +18041,7 @@
           <t>D | 994呎 (3房)
 $2857万
 $28,745/呎
-(16年-05月-17日)</t>
+(16年-05月-18日)</t>
         </is>
       </c>
     </row>
@@ -18056,7 +18056,7 @@
           <t>A | 2019呎 (4+房)
 $7207万
 $35,698/呎
-(16年-05月-09日)</t>
+(16年-05月-10日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -18064,7 +18064,7 @@
           <t>B | 1823呎 (4+房)
 $15180万
 $83,269/呎
-(16年-04月-14日)</t>
+(16年-04月-15日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -18072,7 +18072,7 @@
           <t>C | 1154呎 (3房)
 $3137万
 $27,184/呎
-(16年-04月-26日)</t>
+(16年-04月-27日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -18080,7 +18080,7 @@
           <t>D | 994呎 (3房)
 $2792万
 $28,084/呎
-(16年-05月-09日)</t>
+(16年-05月-10日)</t>
         </is>
       </c>
     </row>
@@ -18095,7 +18095,7 @@
           <t>A | 2019呎 (4+房)
 $5588万
 $27,679/呎
-(16年-04月-25日)</t>
+(16年-04月-26日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -18103,7 +18103,7 @@
           <t>B | 1823呎 (4+房)
 $5001万
 $27,433/呎
-(16年-05月-04日)</t>
+(16年-05月-05日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -18111,7 +18111,7 @@
           <t>C | 1154呎 (3房)
 $3008万
 $26,069/呎
-(16年-04月-28日)</t>
+(16年-04月-29日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -18119,7 +18119,7 @@
           <t>D | 994呎 (3房)
 $2705万
 $27,213/呎
-(16年-05月-16日)</t>
+(16年-05月-17日)</t>
         </is>
       </c>
     </row>
@@ -18134,7 +18134,7 @@
           <t>A | 1910呎 (4+房)
 $5588万
 $29,257/呎
-(16年-05月-17日)</t>
+(16年-05月-18日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -18142,7 +18142,7 @@
           <t>B | 1823呎 (4+房)
 $5001万
 $27,435/呎
-(16年-05月-17日)</t>
+(16年-05月-18日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -18150,7 +18150,7 @@
           <t>C | 1154呎 (3房)
 $2858万
 $24,766/呎
-(16年-05月-05日)</t>
+(16年-05月-06日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -18158,7 +18158,7 @@
           <t>D | 994呎 (3房)
 $2637万
 $26,533/呎
-(16年-05月-09日)</t>
+(16年-05月-10日)</t>
         </is>
       </c>
     </row>
@@ -18173,7 +18173,7 @@
           <t>A | 2019呎 (4+房)
 $4703万
 $23,292/呎
-(16年-04月-26日)</t>
+(16年-04月-27日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -18181,7 +18181,7 @@
           <t>B | 1823呎 (4+房)
 $4234万
 $23,227/呎
-(16年-04月-26日)</t>
+(16年-04月-27日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -18189,7 +18189,7 @@
           <t>C | 1154呎 (3房)
 $2741万
 $23,751/呎
-(16年-04月-28日)</t>
+(16年-04月-29日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -18197,7 +18197,7 @@
           <t>D | 994呎 (3房)
 $2529万
 $25,445/呎
-(16年-05月-12日)</t>
+(16年-05月-13日)</t>
         </is>
       </c>
     </row>
@@ -18212,7 +18212,7 @@
           <t>A | 2019呎 (4+房)
 $6379万
 $31,596/呎
-(16年-03月-31日)</t>
+(16年-04月-01日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -18220,7 +18220,7 @@
           <t>B | 1823呎 (4+房)
 $6379万
 $34,993/呎
-(16年-03月-31日)</t>
+(16年-04月-01日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -18228,7 +18228,7 @@
           <t>C | 1154呎 (3房)
 $2289万
 $19,832/呎
-(16年-05月-12日)</t>
+(16年-05月-13日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -18236,7 +18236,7 @@
           <t>D | 994呎 (3房)
 $2036万
 $20,483/呎
-(16年-05月-12日)</t>
+(16年-05月-13日)</t>
         </is>
       </c>
     </row>
@@ -18251,7 +18251,7 @@
           <t>A | 2019呎 (4+房)
 $3613万
 $17,895/呎
-(16年-04月-18日)</t>
+(16年-04月-19日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -18259,7 +18259,7 @@
           <t>B | 1807呎 (4+房)
 $3006万
 $16,637/呎
-(16年-05月-08日)</t>
+(16年-05月-09日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -18267,7 +18267,7 @@
           <t>C | 1045呎 (3房)
 $2070万
 $19,812/呎
-(16年-04月-24日)</t>
+(16年-04月-25日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -18275,7 +18275,7 @@
           <t>D | 863呎 (3房)
 $1833万
 $21,235/呎
-(16年-05月-09日)</t>
+(16年-05月-10日)</t>
         </is>
       </c>
     </row>
@@ -18290,7 +18290,7 @@
           <t>A | 2065呎 (3房)
 $4674万
 $22,634/呎
-(16年-04月-26日)</t>
+(16年-04月-27日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -18298,7 +18298,7 @@
           <t>B | 2337呎 (4+房)
 $5436万
 $23,262/呎
-(16年-04月-14日)</t>
+(16年-04月-15日)</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr"/>
@@ -18438,7 +18438,7 @@
           <t>A | 2681呎 (4+房)
 $14831万
 $55,319/呎
-(25年-08月-11日)</t>
+(25年-08月-12日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -18447,7 +18447,7 @@
           <t>C | 2079呎 (3房)
 $7509万
 $36,121/呎
-(16年-04月-25日)</t>
+(16年-04月-26日)</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr">
@@ -18455,7 +18455,7 @@
           <t>D | 2090呎 (3房)
 $7751万
 $37,088/呎
-(16年-05月-03日)</t>
+(16年-05月-04日)</t>
         </is>
       </c>
     </row>
@@ -18472,7 +18472,7 @@
           <t>C | 2026呎 (4+房)
 $8348万
 $41,206/呎
-(16年-05月-10日)</t>
+(16年-05月-11日)</t>
         </is>
       </c>
       <c r="E6" s="21" t="inlineStr"/>
@@ -18480,52 +18480,52 @@
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
         <is>
+          <t>22&amp;23</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 2199呎 (4+房)
+$11391万
+$51,801/呎
+(24年-04月-29日)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 2361呎 (4+房)
+$12169万
+$51,540/呎
+(16年-04月-22日)</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr"/>
+      <c r="E7" s="21" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr"/>
-      <c r="C7" s="21" t="inlineStr"/>
-      <c r="D7" s="22" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr"/>
+      <c r="C8" s="21" t="inlineStr"/>
+      <c r="D8" s="22" t="inlineStr">
         <is>
           <t>C | 1428呎 (4+房)
 $4207万
 $29,461/呎
-(16年-04月-19日)</t>
-        </is>
-      </c>
-      <c r="E7" s="22" t="inlineStr">
+(16年-04月-20日)</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
         <is>
           <t>D | 1237呎 (3房)
 $3534万
 $28,573/呎
-(16年-04月-19日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>22&amp;23</t>
-        </is>
-      </c>
-      <c r="B8" s="22" t="inlineStr">
-        <is>
-          <t>A | 2199呎 (4+房)
-$11391万
-$51,801/呎
-(24年-04月-28日)</t>
-        </is>
-      </c>
-      <c r="C8" s="22" t="inlineStr">
-        <is>
-          <t>B | 2361呎 (4+房)
-$12169万
-$51,540/呎
-(16年-04月-21日)</t>
-        </is>
-      </c>
-      <c r="D8" s="21" t="inlineStr"/>
-      <c r="E8" s="21" t="inlineStr"/>
+(16年-04月-20日)</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
@@ -18538,7 +18538,7 @@
           <t>A | 1738呎 (4+房)
 $7820万
 $44,994/呎
-(16年-05月-05日)</t>
+(16年-05月-06日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -18546,7 +18546,7 @@
           <t>B | 1606呎 (4+房)
 $7198万
 $44,819/呎
-(16年-04月-20日)</t>
+(16年-04月-21日)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -18554,7 +18554,7 @@
           <t>C | 1428呎 (4+房)
 $4194万
 $29,373/呎
-(16年-04月-17日)</t>
+(16年-04月-18日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -18562,7 +18562,7 @@
           <t>D | 1237呎 (3房)
 $3527万
 $28,516/呎
-(16年-04月-17日)</t>
+(16年-04月-18日)</t>
         </is>
       </c>
     </row>
@@ -18577,7 +18577,7 @@
           <t>A | 1646呎 (4+房)
 $8182万
 $49,711/呎
-(19年-01月-27日)</t>
+(19年-01月-28日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -18585,7 +18585,7 @@
           <t>B | 1606呎 (4+房)
 $7464万
 $46,475/呎
-(19年-03月-03日)</t>
+(19年-03月-04日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -18593,7 +18593,7 @@
           <t>C | 1428呎 (4+房)
 $8351万
 $58,483/呎
-(16年-03月-24日)</t>
+(16年-03月-25日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -18601,7 +18601,7 @@
           <t>D | 1237呎 (3房)
 $3520万
 $28,459/呎
-(16年-04月-12日)</t>
+(16年-04月-13日)</t>
         </is>
       </c>
     </row>
@@ -18616,7 +18616,7 @@
           <t>A | 1738呎 (4+房)
 $7583万
 $43,633/呎
-(16年-04月-19日)</t>
+(16年-04月-20日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -18624,7 +18624,7 @@
           <t>B | 1708呎 (4+房)
 $6946万
 $40,665/呎
-(16年-05月-08日)</t>
+(16年-05月-09日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -18632,7 +18632,7 @@
           <t>C | 1428呎 (4+房)
 $8351万
 $58,483/呎
-(16年-03月-24日)</t>
+(16年-03月-25日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -18640,7 +18640,7 @@
           <t>D | 1237呎 (3房)
 $3513万
 $28,402/呎
-(16年-04月-17日)</t>
+(16年-04月-18日)</t>
         </is>
       </c>
     </row>
@@ -18655,7 +18655,7 @@
           <t>A | 1646呎 (4+房)
 $6398万
 $38,870/呎
-(24年-10月-14日)</t>
+(24年-10月-15日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -18663,7 +18663,7 @@
           <t>B | 1606呎 (4+房)
 $7068万
 $44,010/呎
-(26年-01月-06日)</t>
+(26年-01月-07日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -18671,7 +18671,7 @@
           <t>C | 1428呎 (4+房)
 $4169万
 $29,198/呎
-(16年-04月-17日)</t>
+(16年-04月-18日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -18679,7 +18679,7 @@
           <t>D | 1237呎 (3房)
 $3513万
 $28,402/呎
-(16年-04月-17日)</t>
+(16年-04月-18日)</t>
         </is>
       </c>
     </row>
@@ -18694,7 +18694,7 @@
           <t>A | 1738呎 (4+房)
 $7318万
 $42,104/呎
-(16年-04月-19日)</t>
+(16年-04月-20日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -18702,7 +18702,7 @@
           <t>B | 1708呎 (4+房)
 $6735万
 $39,433/呎
-(16年-05月-11日)</t>
+(16年-05月-12日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -18710,7 +18710,7 @@
           <t>C | 1428呎 (4+房)
 $4145万
 $29,024/呎
-(16年-04月-17日)</t>
+(16年-04月-18日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -18718,7 +18718,7 @@
           <t>D | 1237呎 (3房)
 $3499万
 $28,289/呎
-(16年-04月-17日)</t>
+(16年-04月-18日)</t>
         </is>
       </c>
     </row>
@@ -18733,7 +18733,7 @@
           <t>A | 1738呎 (4+房)
 $7188万
 $41,360/呎
-(16年-04月-21日)</t>
+(16年-04月-22日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -18741,7 +18741,7 @@
           <t>B | 1708呎 (4+房)
 $6649万
 $38,927/呎
-(16年-04月-21日)</t>
+(16年-04月-22日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -18749,7 +18749,7 @@
           <t>C | 1428呎 (4+房)
 $4132万
 $28,937/呎
-(16年-04月-19日)</t>
+(16年-04月-20日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -18757,7 +18757,7 @@
           <t>D | 1237呎 (3房)
 $3492万
 $28,233/呎
-(16年-04月-19日)</t>
+(16年-04月-20日)</t>
         </is>
       </c>
     </row>
@@ -18772,7 +18772,7 @@
           <t>A | 1646呎 (4+房)
 $7911万
 $48,062/呎
-(19年-02月-17日)</t>
+(19年-02月-18日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -18780,7 +18780,7 @@
           <t>B | 1606呎 (4+房)
 $6829万
 $42,522/呎
-(19年-08月-06日)</t>
+(19年-08月-07日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -18788,7 +18788,7 @@
           <t>C | 1428呎 (4+房)
 $8145万
 $57,036/呎
-(16年-03月-24日)</t>
+(16年-03月-25日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -18796,7 +18796,7 @@
           <t>D | 1142呎 (3房)
 $3482万
 $30,490/呎
-(16年-04月-19日)</t>
+(16年-04月-20日)</t>
         </is>
       </c>
     </row>
@@ -18811,7 +18811,7 @@
           <t>A | 1738呎 (4+房)
 $6652万
 $38,276/呎
-(16年-05月-22日)</t>
+(16年-05月-23日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -18819,7 +18819,7 @@
           <t>B | 1708呎 (4+房)
 $6410万
 $37,530/呎
-(16年-04月-18日)</t>
+(16年-04月-19日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -18827,7 +18827,7 @@
           <t>C | 1428呎 (4+房)
 $8145万
 $57,036/呎
-(16年-03月-24日)</t>
+(16年-03月-25日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -18835,7 +18835,7 @@
           <t>D | 1142呎 (3房)
 $3419万
 $29,941/呎
-(16年-04月-18日)</t>
+(16年-04月-19日)</t>
         </is>
       </c>
     </row>
@@ -18850,7 +18850,7 @@
           <t>A | 1738呎 (4+房)
 $6167万
 $35,482/呎
-(16年-04月-28日)</t>
+(16年-04月-29日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -18858,7 +18858,7 @@
           <t>B | 1708呎 (4+房)
 $5942万
 $34,790/呎
-(16年-04月-19日)</t>
+(16年-04月-20日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -18866,7 +18866,7 @@
           <t>C | 1428呎 (4+房)
 $3892万
 $27,256/呎
-(16年-05月-10日)</t>
+(16年-05月-11日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -18874,7 +18874,7 @@
           <t>D | 1237呎 (3房)
 $3306万
 $26,729/呎
-(16年-05月-03日)</t>
+(16年-05月-04日)</t>
         </is>
       </c>
     </row>
@@ -18889,7 +18889,7 @@
           <t>A | 1738呎 (4+房)
 $5080万
 $29,231/呎
-(16年-04月-20日)</t>
+(16年-04月-21日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -18897,7 +18897,7 @@
           <t>B | 1708呎 (4+房)
 $4914万
 $28,771/呎
-(16年-04月-20日)</t>
+(16年-04月-21日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -18905,7 +18905,7 @@
           <t>C | 1428呎 (4+房)
 $3764万
 $26,357/呎
-(16年-04月-20日)</t>
+(16年-04月-21日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -18913,7 +18913,7 @@
           <t>D | 1237呎 (3房)
 $3197万
 $25,847/呎
-(16年-04月-20日)</t>
+(16年-04月-21日)</t>
         </is>
       </c>
     </row>
@@ -18928,7 +18928,7 @@
           <t>A | 1738呎 (4+房)
 $4288万
 $24,671/呎
-(16年-04月-14日)</t>
+(16年-04月-15日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -18936,7 +18936,7 @@
           <t>B | 1708呎 (4+房)
 $4197万
 $24,571/呎
-(16年-04月-14日)</t>
+(16年-04月-15日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -18944,7 +18944,7 @@
           <t>C | 1428呎 (4+房)
 $3666万
 $25,672/呎
-(16年-04月-13日)</t>
+(16年-04月-14日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -18952,7 +18952,7 @@
           <t>D | 1237呎 (3房)
 $3114万
 $25,175/呎
-(16年-04月-18日)</t>
+(16年-04月-19日)</t>
         </is>
       </c>
     </row>
@@ -18967,7 +18967,7 @@
           <t>A | 1738呎 (4+房)
 $4159万
 $23,931/呎
-(16年-04月-21日)</t>
+(16年-04月-22日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -18975,7 +18975,7 @@
           <t>B | 1708呎 (4+房)
 $4071万
 $23,833/呎
-(16年-04月-19日)</t>
+(16年-04月-20日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -18983,7 +18983,7 @@
           <t>C | 1428呎 (4+房)
 $3593万
 $25,158/呎
-(16年-05月-04日)</t>
+(16年-05月-05日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -18991,7 +18991,7 @@
           <t>D | 1237呎 (3房)
 $3036万
 $24,546/呎
-(16年-04月-25日)</t>
+(16年-04月-26日)</t>
         </is>
       </c>
     </row>
@@ -19006,7 +19006,7 @@
           <t>A | 1738呎 (4+房)
 $3989万
 $22,950/呎
-(16年-04月-18日)</t>
+(16年-04月-19日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -19014,7 +19014,7 @@
           <t>B | 1708呎 (4+房)
 $3904万
 $22,856/呎
-(16年-04月-21日)</t>
+(16年-04月-22日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -19022,7 +19022,7 @@
           <t>C | 1428呎 (4+房)
 $3409万
 $23,875/呎
-(16年-04月-26日)</t>
+(16年-04月-27日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -19030,7 +19030,7 @@
           <t>D | 1237呎 (3房)
 $2881万
 $23,294/呎
-(16年-04月-26日)</t>
+(16年-04月-27日)</t>
         </is>
       </c>
     </row>
@@ -19045,7 +19045,7 @@
           <t>A | 1738呎 (4+房)
 $3206万
 $18,449/呎
-(16年-05月-16日)</t>
+(16年-05月-17日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -19053,7 +19053,7 @@
           <t>B | 1708呎 (4+房)
 $2903万
 $16,996/呎
-(16年-04月-18日)</t>
+(16年-04月-19日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -19061,7 +19061,7 @@
           <t>C | 1428呎 (4+房)
 $2617万
 $18,328/呎
-(16年-05月-05日)</t>
+(16年-05月-06日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -19069,7 +19069,7 @@
           <t>D | 1237呎 (3房)
 $2320万
 $18,752/呎
-(16年-05月-08日)</t>
+(16年-05月-09日)</t>
         </is>
       </c>
     </row>
@@ -19084,7 +19084,7 @@
           <t>A | 1630呎 (4+房)
 $3503万
 $21,490/呎
-(24年-05月-28日)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -19092,7 +19092,7 @@
           <t>B | 1691呎 (4+房)
 $2905万
 $17,177/呎
-(16年-04月-18日)</t>
+(16年-04月-19日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -19100,7 +19100,7 @@
           <t>C | 1324呎 (4+房)
 $2597万
 $19,615/呎
-(16年-04月-26日)</t>
+(16年-04月-27日)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -19108,7 +19108,7 @@
           <t>D | 1221呎 (3房)
 $2113万
 $17,309/呎
-(16年-04月-26日)</t>
+(16年-04月-27日)</t>
         </is>
       </c>
     </row>
@@ -19246,7 +19246,7 @@
           <t>A | 2681呎 (4+房)
 $15227万
 $56,795/呎
-(25年-11月-24日)</t>
+(25年-11月-25日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -19255,7 +19255,7 @@
           <t>C | 1990呎 (3房)
 $12540万
 $63,015/呎
-(19年-11月-03日)</t>
+(19年-11月-04日)</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr">
@@ -19263,7 +19263,7 @@
           <t>D | 2173呎 (3房)
 $7670万
 $35,298/呎
-(16年-05月-16日)</t>
+(16年-05月-17日)</t>
         </is>
       </c>
     </row>
@@ -19280,7 +19280,7 @@
           <t>C | 2128呎 (3房)
 $8248万
 $38,761/呎
-(16年-05月-15日)</t>
+(16年-05月-16日)</t>
         </is>
       </c>
       <c r="E6" s="21" t="inlineStr"/>
@@ -19288,52 +19288,52 @@
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
         <is>
+          <t>22&amp;23</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 2265呎 (4+房)
+$15583万
+$68,797/呎
+(19年-07月-30日)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 2199呎 (4+房)
+$14260万
+$64,849/呎
+(19年-02月-21日)</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr"/>
+      <c r="E7" s="21" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr"/>
-      <c r="C7" s="21" t="inlineStr"/>
-      <c r="D7" s="22" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr"/>
+      <c r="C8" s="21" t="inlineStr"/>
+      <c r="D8" s="22" t="inlineStr">
         <is>
           <t>C | 1237呎 (3房)
 $3250万
 $26,273/呎
-(24年-04月-15日)</t>
-        </is>
-      </c>
-      <c r="E7" s="22" t="inlineStr">
+(24年-04月-16日)</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
         <is>
           <t>D | 1428呎 (4+房)
 $4251万
 $29,770/呎
-(16年-04月-26日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>22&amp;23</t>
-        </is>
-      </c>
-      <c r="B8" s="22" t="inlineStr">
-        <is>
-          <t>A | 2265呎 (4+房)
-$15583万
-$68,797/呎
-(19年-07月-29日)</t>
-        </is>
-      </c>
-      <c r="C8" s="22" t="inlineStr">
-        <is>
-          <t>B | 2199呎 (4+房)
-$14260万
-$64,849/呎
-(19年-02月-20日)</t>
-        </is>
-      </c>
-      <c r="D8" s="21" t="inlineStr"/>
-      <c r="E8" s="21" t="inlineStr"/>
+(16年-04月-27日)</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
@@ -19346,7 +19346,7 @@
           <t>A | 1708呎 (4+房)
 $7567万
 $44,304/呎
-(19年-02月-25日)</t>
+(19年-02月-26日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -19354,7 +19354,7 @@
           <t>B | 1738呎 (4+房)
 $6650万
 $38,262/呎
-(16年-04月-24日)</t>
+(16年-04月-25日)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -19362,7 +19362,7 @@
           <t>C | 1237呎 (3房)
 $7133万
 $57,666/呎
-(16年-03月-31日)</t>
+(16年-04月-01日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -19370,7 +19370,7 @@
           <t>D | 1428呎 (4+房)
 $4238万
 $29,681/呎
-(16年-04月-26日)</t>
+(16年-04月-27日)</t>
         </is>
       </c>
     </row>
@@ -19385,7 +19385,7 @@
           <t>A | 1708呎 (4+房)
 $7472万
 $43,746/呎
-(19年-01月-30日)</t>
+(19年-01月-31日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -19393,7 +19393,7 @@
           <t>B | 1738呎 (4+房)
 $6532万
 $37,585/呎
-(16年-05月-16日)</t>
+(16年-05月-17日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -19401,7 +19401,7 @@
           <t>C | 1237呎 (3房)
 $3556万
 $28,747/呎
-(16年-04月-20日)</t>
+(16年-04月-21日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -19409,7 +19409,7 @@
           <t>D | 1428呎 (4+房)
 $4226万
 $29,592/呎
-(16年-04月-26日)</t>
+(16年-04月-27日)</t>
         </is>
       </c>
     </row>
@@ -19424,7 +19424,7 @@
           <t>A | 1708呎 (4+房)
 $6764万
 $39,600/呎
-(19年-01月-24日)</t>
+(19年-01月-25日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -19432,7 +19432,7 @@
           <t>B | 1738呎 (4+房)
 $6417万
 $36,921/呎
-(16年-05月-09日)</t>
+(16年-05月-10日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -19440,7 +19440,7 @@
           <t>C | 1237呎 (3房)
 $3549万
 $28,689/呎
-(16年-04月-26日)</t>
+(16年-04月-27日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -19448,7 +19448,7 @@
           <t>D | 1428呎 (4+房)
 $4213万
 $29,503/呎
-(16年-04月-26日)</t>
+(16年-04月-27日)</t>
         </is>
       </c>
     </row>
@@ -19463,7 +19463,7 @@
           <t>A | 1708呎 (4+房)
 $13498万
 $79,030/呎
-(16年-04月-14日)</t>
+(16年-04月-15日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -19471,7 +19471,7 @@
           <t>B | 1738呎 (4+房)
 $13498万
 $77,666/呎
-(16年-04月-14日)</t>
+(16年-04月-15日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -19479,7 +19479,7 @@
           <t>C | 1237呎 (3房)
 $3549万
 $28,689/呎
-(16年-05月-03日)</t>
+(16年-05月-04日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -19487,7 +19487,7 @@
           <t>D | 1428呎 (4+房)
 $4213万
 $29,503/呎
-(16年-05月-08日)</t>
+(16年-05月-09日)</t>
         </is>
       </c>
     </row>
@@ -19502,7 +19502,7 @@
           <t>A | 1708呎 (4+房)
 $6662万
 $39,006/呎
-(23年-05月-04日)</t>
+(23年-05月-05日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -19510,7 +19510,7 @@
           <t>B | 1738呎 (4+房)
 $6192万
 $35,627/呎
-(16年-04月-20日)</t>
+(16年-04月-21日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -19518,7 +19518,7 @@
           <t>C | 1237呎 (3房)
 $3535万
 $28,575/呎
-(16年-04月-20日)</t>
+(16年-04月-21日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -19526,7 +19526,7 @@
           <t>D | 1428呎 (4+房)
 $4188万
 $29,328/呎
-(16年-04月-20日)</t>
+(16年-04月-21日)</t>
         </is>
       </c>
     </row>
@@ -19541,7 +19541,7 @@
           <t>A | 1708呎 (4+房)
 $6663万
 $39,009/呎
-(19年-01月-20日)</t>
+(19年-01月-21日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -19549,7 +19549,7 @@
           <t>B | 1738呎 (4+房)
 $6082万
 $34,997/呎
-(16年-05月-15日)</t>
+(16年-05月-16日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -19557,7 +19557,7 @@
           <t>C | 1237呎 (3房)
 $3528万
 $28,518/呎
-(16年-04月-25日)</t>
+(16年-04月-26日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -19565,7 +19565,7 @@
           <t>D | 1428呎 (4+房)
 $4175万
 $29,240/呎
-(16年-04月-18日)</t>
+(16年-04月-19日)</t>
         </is>
       </c>
     </row>
@@ -19580,7 +19580,7 @@
           <t>A | 1708呎 (4+房)
 $6483万
 $37,957/呎
-(19年-01月-17日)</t>
+(19年-01月-18日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -19588,7 +19588,7 @@
           <t>B | 1738呎 (4+房)
 $6064万
 $34,892/呎
-(16年-04月-28日)</t>
+(16年-04月-29日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -19596,7 +19596,7 @@
           <t>C | 1237呎 (3房)
 $3517万
 $28,432/呎
-(16年-04月-28日)</t>
+(16年-04月-29日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -19604,7 +19604,7 @@
           <t>D | 1428呎 (4+房)
 $4163万
 $29,152/呎
-(16年-05月-16日)</t>
+(16年-05月-17日)</t>
         </is>
       </c>
     </row>
@@ -19619,7 +19619,7 @@
           <t>A | 1708呎 (4+房)
 $6290万
 $36,827/呎
-(16年-05月-08日)</t>
+(16年-05月-09日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -19627,7 +19627,7 @@
           <t>B | 1738呎 (4+房)
 $5864万
 $33,740/呎
-(16年-04月-24日)</t>
+(16年-04月-25日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -19635,7 +19635,7 @@
           <t>C | 1237呎 (3房)
 $3454万
 $27,921/呎
-(16年-05月-12日)</t>
+(16年-05月-13日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -19643,7 +19643,7 @@
           <t>D | 1428呎 (4+房)
 $4067万
 $28,482/呎
-(16年-04月-21日)</t>
+(16年-04月-22日)</t>
         </is>
       </c>
     </row>
@@ -19658,7 +19658,7 @@
           <t>A | 1708呎 (4+房)
 $5890万
 $34,483/呎
-(19年-01月-21日)</t>
+(19年-01月-22日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -19666,7 +19666,7 @@
           <t>B | 1738呎 (4+房)
 $5436万
 $31,277/呎
-(16年-04月-27日)</t>
+(16年-04月-28日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -19674,7 +19674,7 @@
           <t>C | 1237呎 (3房)
 $3340万
 $26,999/呎
-(16年-05月-04日)</t>
+(16年-05月-05日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -19682,7 +19682,7 @@
           <t>D | 1428呎 (4+房)
 $3933万
 $27,542/呎
-(16年-05月-04日)</t>
+(16年-05月-05日)</t>
         </is>
       </c>
     </row>
@@ -19697,7 +19697,7 @@
           <t>A | 1708呎 (4+房)
 $5567万
 $32,593/呎
-(19年-03月-03日)</t>
+(19年-03月-04日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -19705,7 +19705,7 @@
           <t>B | 1738呎 (4+房)
 $4441万
 $25,554/呎
-(16年-05月-02日)</t>
+(16年-05月-03日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -19713,7 +19713,7 @@
           <t>C | 1237呎 (3房)
 $3263万
 $26,378/呎
-(16年-04月-19日)</t>
+(16年-04月-20日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -19721,7 +19721,7 @@
           <t>D | 1428呎 (4+房)
 $3842万
 $26,908/呎
-(16年-04月-25日)</t>
+(16年-04月-26日)</t>
         </is>
       </c>
     </row>
@@ -19736,7 +19736,7 @@
           <t>A | 1708呎 (4+房)
 $8063万
 $47,206/呎
-(16年-03月-31日)</t>
+(16年-04月-01日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -19744,7 +19744,7 @@
           <t>B | 1738呎 (4+房)
 $8063万
 $46,391/呎
-(16年-03月-31日)</t>
+(16年-04月-01日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -19752,7 +19752,7 @@
           <t>C | 1237呎 (3房)
 $3178万
 $25,692/呎
-(16年-04月-25日)</t>
+(16年-04月-26日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -19760,7 +19760,7 @@
           <t>D | 1428呎 (4+房)
 $3743万
 $26,209/呎
-(16年-04月-20日)</t>
+(16年-04月-21日)</t>
         </is>
       </c>
     </row>
@@ -19775,7 +19775,7 @@
           <t>A | 1708呎 (4+房)
 $5332万
 $31,220/呎
-(19年-01月-31日)</t>
+(19年-02月-01日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -19783,7 +19783,7 @@
           <t>B | 1738呎 (4+房)
 $3891万
 $22,388/呎
-(16年-04月-21日)</t>
+(16年-04月-22日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -19791,7 +19791,7 @@
           <t>C | 1237呎 (3房)
 $3115万
 $25,179/呎
-(16年-04月-24日)</t>
+(16年-04月-25日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -19799,7 +19799,7 @@
           <t>D | 1428呎 (4+房)
 $3630万
 $25,422/呎
-(16年-04月-24日)</t>
+(16年-04月-25日)</t>
         </is>
       </c>
     </row>
@@ -19814,7 +19814,7 @@
           <t>A | 1708呎 (4+房)
 $5188万
 $30,378/呎
-(19年-01月-10日)</t>
+(19年-01月-11日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -19822,7 +19822,7 @@
           <t>B | 1738呎 (4+房)
 $3790万
 $21,806/呎
-(16年-04月-27日)</t>
+(16年-04月-28日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -19830,7 +19830,7 @@
           <t>C | 1237呎 (3房)
 $2800万
 $22,635/呎
-(16年-04月-19日)</t>
+(16年-04月-20日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -19838,7 +19838,7 @@
           <t>D | 1428呎 (4+房)
 $3227万
 $22,600/呎
-(16年-04月-19日)</t>
+(16年-04月-20日)</t>
         </is>
       </c>
     </row>
@@ -19853,7 +19853,7 @@
           <t>A | 1708呎 (4+房)
 $5049万
 $29,560/呎
-(19年-01月-14日)</t>
+(19年-01月-15日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -19861,7 +19861,7 @@
           <t>B | 1738呎 (4+房)
 $3127万
 $17,990/呎
-(16年-04月-19日)</t>
+(16年-04月-20日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -19869,7 +19869,7 @@
           <t>C | 1237呎 (3房)
 $2082万
 $16,831/呎
-(16年-04月-18日)</t>
+(16年-04月-19日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -19877,7 +19877,7 @@
           <t>D | 1428呎 (4+房)
 $2499万
 $17,500/呎
-(16年-04月-19日)</t>
+(16年-04月-20日)</t>
         </is>
       </c>
     </row>
@@ -19892,7 +19892,7 @@
           <t>A | 1691呎 (4+房)
 $3166万
 $18,724/呎
-(16年-05月-03日)</t>
+(16年-05月-04日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -19900,7 +19900,7 @@
           <t>B | 1722呎 (4+房)
 $3061万
 $17,778/呎
-(16年-05月-17日)</t>
+(16年-05月-18日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -19908,7 +19908,7 @@
           <t>C | 1221呎 (3房)
 $2198万
 $18,005/呎
-(16年-04月-21日)</t>
+(16年-04月-22日)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -19916,7 +19916,7 @@
           <t>D | 1412呎 (4+房)
 $2421万
 $17,145/呎
-(16年-04月-21日)</t>
+(16年-04月-22日)</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
           <t>A | 2733呎 (4+房)
 $21391万
 $78,270/呎
-(19年-02月-14日)</t>
+(19年-02月-15日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -20063,7 +20063,7 @@
           <t>C | 2130呎 (4+房)
 $9165万
 $43,028/呎
-(16年-04月-21日)</t>
+(16年-04月-22日)</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr">
@@ -20071,7 +20071,7 @@
           <t>D | 2187呎 (4+房)
 $15180万
 $69,410/呎
-(16年-04月-14日)</t>
+(16年-04月-15日)</t>
         </is>
       </c>
     </row>
@@ -20086,7 +20086,7 @@
           <t>A | 1320呎 (4+房)
 $4308万
 $32,634/呎
-(16年-05月-08日)</t>
+(16年-05月-09日)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -20094,7 +20094,7 @@
           <t>B | 1316呎 (4+房)
 $3998万
 $30,381/呎
-(16年-04月-26日)</t>
+(16年-04月-27日)</t>
         </is>
       </c>
       <c r="D6" s="22" t="inlineStr">
@@ -20102,7 +20102,7 @@
           <t>C | 2044呎 (3房)
 $12860万
 $62,916/呎
-(20年-02月-20日)</t>
+(20年-02月-21日)</t>
         </is>
       </c>
       <c r="E6" s="21" t="inlineStr"/>
@@ -20118,7 +20118,7 @@
           <t>A | 1320呎 (4+房)
 $4295万
 $32,535/呎
-(16年-05月-12日)</t>
+(16年-05月-13日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -20126,7 +20126,7 @@
           <t>B | 1221呎 (4+房)
 $3947万
 $32,325/呎
-(16年-05月-04日)</t>
+(16年-05月-05日)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -20134,7 +20134,7 @@
           <t>C | 1723呎 (4+房)
 $7074万
 $41,056/呎
-(16年-04月-27日)</t>
+(16年-04月-28日)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -20142,7 +20142,7 @@
           <t>D | 1160呎 (3房)
 $3862万
 $33,292/呎
-(16年-05月-10日)</t>
+(16年-05月-11日)</t>
         </is>
       </c>
     </row>
@@ -20157,7 +20157,7 @@
           <t>A | 1320呎 (4+房)
 $4273万
 $32,373/呎
-(16年-05月-11日)</t>
+(16年-05月-12日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -20165,7 +20165,7 @@
           <t>B | 1221呎 (4+房)
 $3896万
 $31,910/呎
-(16年-04月-28日)</t>
+(16年-04月-29日)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -20173,7 +20173,7 @@
           <t>C | 1723呎 (4+房)
 $7144万
 $41,465/呎
-(19年-01月-30日)</t>
+(19年-01月-31日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -20181,7 +20181,7 @@
           <t>D | 1160呎 (3房)
 $3841万
 $33,110/呎
-(16年-05月-10日)</t>
+(16年-05月-11日)</t>
         </is>
       </c>
     </row>
@@ -20196,7 +20196,7 @@
           <t>A | 1320呎 (4+房)
 $4190万
 $31,739/呎
-(16年-04月-28日)</t>
+(16年-04月-29日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -20204,7 +20204,7 @@
           <t>B | 1316呎 (4+房)
 $7643万
 $58,079/呎
-(16年-04月-14日)</t>
+(16年-04月-15日)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -20212,7 +20212,7 @@
           <t>C | 1723呎 (4+房)
 $6358万
 $36,904/呎
-(19年-01月-14日)</t>
+(19年-01月-15日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -20220,7 +20220,7 @@
           <t>D | 1160呎 (3房)
 $3820万
 $32,929/呎
-(16年-05月-11日)</t>
+(16年-05月-12日)</t>
         </is>
       </c>
     </row>
@@ -20235,7 +20235,7 @@
           <t>A | 1320呎 (4+房)
 $4196万
 $31,792/呎
-(16年-05月-16日)</t>
+(16年-05月-17日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -20243,7 +20243,7 @@
           <t>B | 1316呎 (4+房)
 $3797万
 $28,851/呎
-(16年-05月-08日)</t>
+(16年-05月-09日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -20251,7 +20251,7 @@
           <t>C | 1723呎 (4+房)
 $5342万
 $31,006/呎
-(24年-06月-23日)</t>
+(24年-06月-24日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -20259,7 +20259,7 @@
           <t>D | 1160呎 (3房)
 $7643万
 $65,889/呎
-(16年-04月-14日)</t>
+(16年-04月-15日)</t>
         </is>
       </c>
     </row>
@@ -20274,7 +20274,7 @@
           <t>A | 1320呎 (4+房)
 $4155万
 $31,477/呎
-(16年-05月-12日)</t>
+(16年-05月-13日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -20282,7 +20282,7 @@
           <t>B | 1316呎 (4+房)
 $3759万
 $28,566/呎
-(16年-05月-08日)</t>
+(16年-05月-09日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -20290,7 +20290,7 @@
           <t>C | 1723呎 (4+房)
 $6268万
 $36,377/呎
-(19年-01月-06日)</t>
+(19年-01月-07日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -20298,7 +20298,7 @@
           <t>D | 1160呎 (3房)
 $3782万
 $32,601/呎
-(16年-05月-17日)</t>
+(16年-05月-18日)</t>
         </is>
       </c>
     </row>
@@ -20313,7 +20313,7 @@
           <t>A | 1320呎 (4+房)
 $4011万
 $30,383/呎
-(16年-05月-04日)</t>
+(16年-05月-05日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -20321,7 +20321,7 @@
           <t>B | 1221呎 (4+房)
 $3700万
 $30,303/呎
-(16年-05月-16日)</t>
+(16年-05月-17日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -20329,7 +20329,7 @@
           <t>C | 1723呎 (4+房)
 $6451万
 $37,442/呎
-(19年-01月-16日)</t>
+(19年-01月-17日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -20337,7 +20337,7 @@
           <t>D | 1160呎 (3房)
 $3653万
 $31,491/呎
-(16年-05月-12日)</t>
+(16年-05月-13日)</t>
         </is>
       </c>
     </row>
@@ -20352,7 +20352,7 @@
           <t>A | 1320呎 (4+房)
 $3940万
 $29,846/呎
-(16年-05月-05日)</t>
+(16年-05月-06日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -20360,7 +20360,7 @@
           <t>B | 1316呎 (4+房)
 $3653万
 $27,755/呎
-(16年-05月-12日)</t>
+(16年-05月-13日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -20368,7 +20368,7 @@
           <t>C | 1723呎 (4+房)
 $6802万
 $39,477/呎
-(19年-01月-16日)</t>
+(19年-01月-17日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -20376,7 +20376,7 @@
           <t>D | 1160呎 (3房)
 $3540万
 $30,514/呎
-(16年-05月-15日)</t>
+(16年-05月-16日)</t>
         </is>
       </c>
     </row>
@@ -20391,7 +20391,7 @@
           <t>A | 1320呎 (4+房)
 $3928万
 $29,756/呎
-(16年-05月-04日)</t>
+(16年-05月-05日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -20399,7 +20399,7 @@
           <t>B | 1316呎 (4+房)
 $3642万
 $27,672/呎
-(16年-05月-16日)</t>
+(16年-05月-17日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -20407,7 +20407,7 @@
           <t>C | 1723呎 (4+房)
 $5814万
 $33,745/呎
-(19年-01月-06日)</t>
+(19年-01月-07日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -20415,7 +20415,7 @@
           <t>D | 1065呎 (3房)
 $3529万
 $33,136/呎
-(16年-05月-12日)</t>
+(16年-05月-13日)</t>
         </is>
       </c>
     </row>
@@ -20430,7 +20430,7 @@
           <t>A | 1320呎 (4+房)
 $3837万
 $29,072/呎
-(16年-04月-27日)</t>
+(16年-04月-28日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -20438,7 +20438,7 @@
           <t>B | 1316呎 (4+房)
 $3576万
 $27,174/呎
-(16年-04月-27日)</t>
+(16年-04月-28日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -20446,7 +20446,7 @@
           <t>C | 1723呎 (4+房)
 $5815万
 $33,750/呎
-(19年-01月-16日)</t>
+(19年-01月-17日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -20454,7 +20454,7 @@
           <t>D | 1160呎 (3房)
 $3501万
 $30,179/呎
-(16年-05月-11日)</t>
+(16年-05月-12日)</t>
         </is>
       </c>
     </row>
@@ -20469,7 +20469,7 @@
           <t>A | 1320呎 (4+房)
 $3711万
 $28,112/呎
-(16年-04月-26日)</t>
+(16年-04月-27日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -20477,7 +20477,7 @@
           <t>B | 1316呎 (4+房)
 $3512万
 $26,685/呎
-(16年-04月-28日)</t>
+(16年-04月-29日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -20485,7 +20485,7 @@
           <t>C | 1723呎 (4+房)
 $5663万
 $32,869/呎
-(16年-05月-08日)</t>
+(16年-05月-09日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -20493,7 +20493,7 @@
           <t>D | 1160呎 (3房)
 $3403万
 $29,337/呎
-(16年-05月-10日)</t>
+(16年-05月-11日)</t>
         </is>
       </c>
     </row>
@@ -20508,7 +20508,7 @@
           <t>A | 1320呎 (4+房)
 $3477万
 $26,341/呎
-(16年-05月-11日)</t>
+(16年-05月-12日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -20516,7 +20516,7 @@
           <t>B | 1221呎 (4+房)
 $3361万
 $27,524/呎
-(16年-04月-14日)</t>
+(16年-04月-15日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -20524,7 +20524,7 @@
           <t>C | 1723呎 (4+房)
 $5448万
 $31,620/呎
-(16年-05月-09日)</t>
+(16年-05月-10日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -20532,7 +20532,7 @@
           <t>D | 1065呎 (3房)
 $3308万
 $31,060/呎
-(16年-05月-11日)</t>
+(16年-05月-12日)</t>
         </is>
       </c>
     </row>
@@ -20547,7 +20547,7 @@
           <t>A | 1320呎 (4+房)
 $3317万
 $25,130/呎
-(16年-05月-15日)</t>
+(16年-05月-16日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -20555,7 +20555,7 @@
           <t>B | 1316呎 (4+房)
 $3139万
 $23,852/呎
-(16年-05月-02日)</t>
+(16年-05月-03日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -20563,7 +20563,7 @@
           <t>C | 1723呎 (4+房)
 $5279万
 $30,640/呎
-(16年-05月-19日)</t>
+(16年-05月-20日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -20571,7 +20571,7 @@
           <t>D | 1160呎 (3房)
 $3156万
 $27,204/呎
-(16年-05月-16日)</t>
+(16年-05月-17日)</t>
         </is>
       </c>
     </row>
@@ -20586,7 +20586,7 @@
           <t>A | 1320呎 (4+房)
 $3085万
 $23,371/呎
-(16年-05月-09日)</t>
+(16年-05月-10日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -20594,7 +20594,7 @@
           <t>B | 1316呎 (4+房)
 $2919万
 $22,182/呎
-(16年-04月-28日)</t>
+(16年-04月-29日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -20602,7 +20602,7 @@
           <t>C | 1723呎 (4+房)
 $5534万
 $32,120/呎
-(19年-01月-15日)</t>
+(19年-01月-16日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -20610,7 +20610,7 @@
           <t>D | 1065呎 (3房)
 $3045万
 $28,596/呎
-(16年-05月-17日)</t>
+(16年-05月-18日)</t>
         </is>
       </c>
     </row>
@@ -20625,7 +20625,7 @@
           <t>A | 1320呎 (4+房)
 $3066万
 $23,230/呎
-(16年-04月-14日)</t>
+(16年-04月-15日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -20633,7 +20633,7 @@
           <t>B | 1316呎 (4+房)
 $2902万
 $22,049/呎
-(16年-04月-27日)</t>
+(16年-04月-28日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -20641,7 +20641,7 @@
           <t>C | 1723呎 (4+房)
 $4871万
 $28,272/呎
-(19年-01月-03日)</t>
+(19年-01月-04日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -20649,7 +20649,7 @@
           <t>D | 1160呎 (3房)
 $2875万
 $24,784/呎
-(16年-05月-15日)</t>
+(16年-05月-16日)</t>
         </is>
       </c>
     </row>
@@ -20664,7 +20664,7 @@
           <t>A | 1320呎 (4+房)
 $2529万
 $19,162/呎
-(16年-05月-18日)</t>
+(16年-05月-19日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -20672,7 +20672,7 @@
           <t>B | 1221呎 (4+房)
 $2211万
 $18,105/呎
-(16年-04月-26日)</t>
+(16年-04月-27日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -20680,7 +20680,7 @@
           <t>C | 1723呎 (4+房)
 $3896万
 $22,610/呎
-(16年-05月-12日)</t>
+(16年-05月-13日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -20688,7 +20688,7 @@
           <t>D | 1160呎 (3房)
 $2329万
 $20,075/呎
-(16年-05月-15日)</t>
+(16年-05月-16日)</t>
         </is>
       </c>
     </row>
@@ -20703,7 +20703,7 @@
           <t>A | 1150呎 (4+房)
 $3623万
 $31,505/呎
-(24年-05月-29日)</t>
+(24年-05月-30日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -20711,7 +20711,7 @@
           <t>B | 1300呎 (4+房)
 $2506万
 $19,276/呎
-(16年-05月-16日)</t>
+(16年-05月-17日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -20719,7 +20719,7 @@
           <t>C | 1723呎 (3房)
 $3909万
 $22,690/呎
-(16年-05月-15日)</t>
+(16年-05月-16日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -20727,7 +20727,7 @@
           <t>D | 1143呎 (3房)
 $2173万
 $19,011/呎
-(16年-05月-15日)</t>
+(16年-05月-16日)</t>
         </is>
       </c>
     </row>
@@ -20742,7 +20742,7 @@
           <t>A | 1929呎 (3房)
 $4593万
 $23,811/呎
-(16年-04月-07日)</t>
+(16年-04月-08日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -20750,7 +20750,7 @@
           <t>B | 1970呎 (2房)
 $6277万
 $31,865/呎
-(16年-05月-18日)</t>
+(16年-05月-19日)</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr"/>

--- a/web/files/九龙-何文田-天铸 (第2期).xlsx
+++ b/web/files/九龙-何文田-天铸 (第2期).xlsx
@@ -18480,10 +18480,35 @@
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr"/>
+      <c r="C7" s="21" t="inlineStr"/>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>C | 1428呎 (4+房)
+$4207万
+$29,461/呎
+(16年-04月-20日)</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>D | 1237呎 (3房)
+$3534万
+$28,573/呎
+(16年-04月-20日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
           <t>22&amp;23</t>
         </is>
       </c>
-      <c r="B7" s="22" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>A | 2199呎 (4+房)
 $11391万
@@ -18491,7 +18516,7 @@
 (24年-04月-29日)</t>
         </is>
       </c>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t>B | 2361呎 (4+房)
 $12169万
@@ -18499,33 +18524,8 @@
 (16年-04月-22日)</t>
         </is>
       </c>
-      <c r="D7" s="21" t="inlineStr"/>
-      <c r="E7" s="21" t="inlineStr"/>
-    </row>
-    <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="B8" s="21" t="inlineStr"/>
-      <c r="C8" s="21" t="inlineStr"/>
-      <c r="D8" s="22" t="inlineStr">
-        <is>
-          <t>C | 1428呎 (4+房)
-$4207万
-$29,461/呎
-(16年-04月-20日)</t>
-        </is>
-      </c>
-      <c r="E8" s="22" t="inlineStr">
-        <is>
-          <t>D | 1237呎 (3房)
-$3534万
-$28,573/呎
-(16年-04月-20日)</t>
-        </is>
-      </c>
+      <c r="D8" s="21" t="inlineStr"/>
+      <c r="E8" s="21" t="inlineStr"/>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
@@ -19288,10 +19288,35 @@
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr"/>
+      <c r="C7" s="21" t="inlineStr"/>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>C | 1237呎 (3房)
+$3250万
+$26,273/呎
+(24年-04月-16日)</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>D | 1428呎 (4+房)
+$4251万
+$29,770/呎
+(16年-04月-27日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
           <t>22&amp;23</t>
         </is>
       </c>
-      <c r="B7" s="22" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>A | 2265呎 (4+房)
 $15583万
@@ -19299,7 +19324,7 @@
 (19年-07月-30日)</t>
         </is>
       </c>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t>B | 2199呎 (4+房)
 $14260万
@@ -19307,33 +19332,8 @@
 (19年-02月-21日)</t>
         </is>
       </c>
-      <c r="D7" s="21" t="inlineStr"/>
-      <c r="E7" s="21" t="inlineStr"/>
-    </row>
-    <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="B8" s="21" t="inlineStr"/>
-      <c r="C8" s="21" t="inlineStr"/>
-      <c r="D8" s="22" t="inlineStr">
-        <is>
-          <t>C | 1237呎 (3房)
-$3250万
-$26,273/呎
-(24年-04月-16日)</t>
-        </is>
-      </c>
-      <c r="E8" s="22" t="inlineStr">
-        <is>
-          <t>D | 1428呎 (4+房)
-$4251万
-$29,770/呎
-(16年-04月-27日)</t>
-        </is>
-      </c>
+      <c r="D8" s="21" t="inlineStr"/>
+      <c r="E8" s="21" t="inlineStr"/>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="19" t="inlineStr">

--- a/web/files/九龙-何文田-天铸 (第2期).xlsx
+++ b/web/files/九龙-何文田-天铸 (第2期).xlsx
@@ -18480,12 +18480,37 @@
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
         <is>
+          <t>22&amp;23</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 2199呎 (4+房)
+$11391万
+$51,801/呎
+(24年-04月-29日)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 2361呎 (4+房)
+$12169万
+$51,540/呎
+(16年-04月-22日)</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr"/>
+      <c r="E7" s="21" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr"/>
-      <c r="C7" s="21" t="inlineStr"/>
-      <c r="D7" s="22" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr"/>
+      <c r="C8" s="21" t="inlineStr"/>
+      <c r="D8" s="22" t="inlineStr">
         <is>
           <t>C | 1428呎 (4+房)
 $4207万
@@ -18493,7 +18518,7 @@
 (16年-04月-20日)</t>
         </is>
       </c>
-      <c r="E7" s="22" t="inlineStr">
+      <c r="E8" s="22" t="inlineStr">
         <is>
           <t>D | 1237呎 (3房)
 $3534万
@@ -18501,31 +18526,6 @@
 (16年-04月-20日)</t>
         </is>
       </c>
-    </row>
-    <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>22&amp;23</t>
-        </is>
-      </c>
-      <c r="B8" s="22" t="inlineStr">
-        <is>
-          <t>A | 2199呎 (4+房)
-$11391万
-$51,801/呎
-(24年-04月-29日)</t>
-        </is>
-      </c>
-      <c r="C8" s="22" t="inlineStr">
-        <is>
-          <t>B | 2361呎 (4+房)
-$12169万
-$51,540/呎
-(16年-04月-22日)</t>
-        </is>
-      </c>
-      <c r="D8" s="21" t="inlineStr"/>
-      <c r="E8" s="21" t="inlineStr"/>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
@@ -19288,12 +19288,37 @@
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
         <is>
+          <t>22&amp;23</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 2265呎 (4+房)
+$15583万
+$68,797/呎
+(19年-07月-30日)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 2199呎 (4+房)
+$14260万
+$64,849/呎
+(19年-02月-21日)</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr"/>
+      <c r="E7" s="21" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr"/>
-      <c r="C7" s="21" t="inlineStr"/>
-      <c r="D7" s="22" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr"/>
+      <c r="C8" s="21" t="inlineStr"/>
+      <c r="D8" s="22" t="inlineStr">
         <is>
           <t>C | 1237呎 (3房)
 $3250万
@@ -19301,7 +19326,7 @@
 (24年-04月-16日)</t>
         </is>
       </c>
-      <c r="E7" s="22" t="inlineStr">
+      <c r="E8" s="22" t="inlineStr">
         <is>
           <t>D | 1428呎 (4+房)
 $4251万
@@ -19309,31 +19334,6 @@
 (16年-04月-27日)</t>
         </is>
       </c>
-    </row>
-    <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>22&amp;23</t>
-        </is>
-      </c>
-      <c r="B8" s="22" t="inlineStr">
-        <is>
-          <t>A | 2265呎 (4+房)
-$15583万
-$68,797/呎
-(19年-07月-30日)</t>
-        </is>
-      </c>
-      <c r="C8" s="22" t="inlineStr">
-        <is>
-          <t>B | 2199呎 (4+房)
-$14260万
-$64,849/呎
-(19年-02月-21日)</t>
-        </is>
-      </c>
-      <c r="D8" s="21" t="inlineStr"/>
-      <c r="E8" s="21" t="inlineStr"/>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="19" t="inlineStr">

--- a/web/files/九龙-何文田-天铸 (第2期).xlsx
+++ b/web/files/九龙-何文田-天铸 (第2期).xlsx
@@ -10,8 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3座" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5座" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5座" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -637,7 +636,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N273"/>
+  <dimension ref="A1:N205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -8876,7 +8875,7 @@
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>5座</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
@@ -8891,11 +8890,11 @@
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E134" s="4" t="n">
-        <v>2173</v>
+        <v>2187</v>
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
@@ -8904,14 +8903,14 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2016-05-17</t>
+          <t>2016-04-15</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
-        <v>76702500</v>
+        <v>151799500</v>
       </c>
       <c r="I134" s="5" t="n">
-        <v>35298</v>
+        <v>69410</v>
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
@@ -8919,10 +8918,10 @@
         </is>
       </c>
       <c r="K134" s="5" t="n">
-        <v>76702500</v>
+        <v>151799500</v>
       </c>
       <c r="L134" s="5" t="n">
-        <v>35298</v>
+        <v>69410</v>
       </c>
       <c r="M134" s="3" t="inlineStr">
         <is>
@@ -8938,7 +8937,7 @@
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>5座</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
@@ -8953,11 +8952,11 @@
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E135" s="4" t="n">
-        <v>1990</v>
+        <v>2130</v>
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
@@ -8966,14 +8965,14 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2019-11-04</t>
+          <t>2016-04-22</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
-        <v>125400000</v>
+        <v>91650000</v>
       </c>
       <c r="I135" s="5" t="n">
-        <v>63015</v>
+        <v>43028</v>
       </c>
       <c r="J135" s="3" t="inlineStr">
         <is>
@@ -8981,10 +8980,10 @@
         </is>
       </c>
       <c r="K135" s="5" t="n">
-        <v>125400000</v>
+        <v>91650000</v>
       </c>
       <c r="L135" s="5" t="n">
-        <v>63015</v>
+        <v>43028</v>
       </c>
       <c r="M135" s="3" t="inlineStr">
         <is>
@@ -9000,7 +8999,7 @@
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>5座</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
@@ -9019,7 +9018,7 @@
         </is>
       </c>
       <c r="E136" s="4" t="n">
-        <v>2681</v>
+        <v>2733</v>
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
@@ -9028,14 +9027,14 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2019-02-15</t>
         </is>
       </c>
       <c r="H136" s="5" t="n">
-        <v>152267800</v>
+        <v>213912000</v>
       </c>
       <c r="I136" s="5" t="n">
-        <v>56795</v>
+        <v>78270</v>
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
@@ -9043,10 +9042,10 @@
         </is>
       </c>
       <c r="K136" s="5" t="n">
-        <v>152267800</v>
+        <v>213912000</v>
       </c>
       <c r="L136" s="5" t="n">
-        <v>56795</v>
+        <v>78270</v>
       </c>
       <c r="M136" s="3" t="inlineStr">
         <is>
@@ -9062,7 +9061,7 @@
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>5座</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
@@ -9081,7 +9080,7 @@
         </is>
       </c>
       <c r="E137" s="4" t="n">
-        <v>2128</v>
+        <v>2044</v>
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
@@ -9090,14 +9089,14 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2016-05-16</t>
+          <t>2020-02-21</t>
         </is>
       </c>
       <c r="H137" s="5" t="n">
-        <v>82484200</v>
+        <v>128601000</v>
       </c>
       <c r="I137" s="5" t="n">
-        <v>38761</v>
+        <v>62916</v>
       </c>
       <c r="J137" s="3" t="inlineStr">
         <is>
@@ -9105,10 +9104,10 @@
         </is>
       </c>
       <c r="K137" s="5" t="n">
-        <v>82484200</v>
+        <v>128601000</v>
       </c>
       <c r="L137" s="5" t="n">
-        <v>38761</v>
+        <v>62916</v>
       </c>
       <c r="M137" s="3" t="inlineStr">
         <is>
@@ -9124,17 +9123,17 @@
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>5座</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D138" s="3" t="inlineStr">
@@ -9143,7 +9142,7 @@
         </is>
       </c>
       <c r="E138" s="4" t="n">
-        <v>1428</v>
+        <v>1316</v>
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
@@ -9156,10 +9155,10 @@
         </is>
       </c>
       <c r="H138" s="5" t="n">
-        <v>42511300</v>
+        <v>39981600</v>
       </c>
       <c r="I138" s="5" t="n">
-        <v>29770</v>
+        <v>30381</v>
       </c>
       <c r="J138" s="3" t="inlineStr">
         <is>
@@ -9167,10 +9166,10 @@
         </is>
       </c>
       <c r="K138" s="5" t="n">
-        <v>42511300</v>
+        <v>39981600</v>
       </c>
       <c r="L138" s="5" t="n">
-        <v>29770</v>
+        <v>30381</v>
       </c>
       <c r="M138" s="3" t="inlineStr">
         <is>
@@ -9186,26 +9185,26 @@
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>5座</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E139" s="4" t="n">
-        <v>1237</v>
+        <v>1320</v>
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
@@ -9214,14 +9213,14 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2016-05-09</t>
         </is>
       </c>
       <c r="H139" s="5" t="n">
-        <v>32500000</v>
+        <v>43077300</v>
       </c>
       <c r="I139" s="5" t="n">
-        <v>26273</v>
+        <v>32634</v>
       </c>
       <c r="J139" s="3" t="inlineStr">
         <is>
@@ -9229,10 +9228,10 @@
         </is>
       </c>
       <c r="K139" s="5" t="n">
-        <v>32500000</v>
+        <v>43077300</v>
       </c>
       <c r="L139" s="5" t="n">
-        <v>26273</v>
+        <v>32634</v>
       </c>
       <c r="M139" s="3" t="inlineStr">
         <is>
@@ -9248,26 +9247,26 @@
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>5座</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>22&amp;23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E140" s="4" t="n">
-        <v>2199</v>
+        <v>1160</v>
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
@@ -9276,14 +9275,14 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2019-02-21</t>
+          <t>2016-05-11</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
-        <v>142602800</v>
+        <v>38618900</v>
       </c>
       <c r="I140" s="5" t="n">
-        <v>64849</v>
+        <v>33292</v>
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
@@ -9291,10 +9290,10 @@
         </is>
       </c>
       <c r="K140" s="5" t="n">
-        <v>142602800</v>
+        <v>38618900</v>
       </c>
       <c r="L140" s="5" t="n">
-        <v>64849</v>
+        <v>33292</v>
       </c>
       <c r="M140" s="3" t="inlineStr">
         <is>
@@ -9310,17 +9309,17 @@
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>5座</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>22&amp;23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D141" s="3" t="inlineStr">
@@ -9329,7 +9328,7 @@
         </is>
       </c>
       <c r="E141" s="4" t="n">
-        <v>2265</v>
+        <v>1723</v>
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
@@ -9338,14 +9337,14 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2019-07-30</t>
+          <t>2016-04-28</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
-        <v>155826000</v>
+        <v>70738800</v>
       </c>
       <c r="I141" s="5" t="n">
-        <v>68797</v>
+        <v>41056</v>
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
@@ -9353,10 +9352,10 @@
         </is>
       </c>
       <c r="K141" s="5" t="n">
-        <v>155826000</v>
+        <v>70738800</v>
       </c>
       <c r="L141" s="5" t="n">
-        <v>68797</v>
+        <v>41056</v>
       </c>
       <c r="M141" s="3" t="inlineStr">
         <is>
@@ -9372,17 +9371,17 @@
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>5座</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D142" s="3" t="inlineStr">
@@ -9391,7 +9390,7 @@
         </is>
       </c>
       <c r="E142" s="4" t="n">
-        <v>1428</v>
+        <v>1221</v>
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
@@ -9400,14 +9399,14 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2016-04-27</t>
+          <t>2016-05-05</t>
         </is>
       </c>
       <c r="H142" s="5" t="n">
-        <v>42384100</v>
+        <v>39468600</v>
       </c>
       <c r="I142" s="5" t="n">
-        <v>29681</v>
+        <v>32325</v>
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
@@ -9415,10 +9414,10 @@
         </is>
       </c>
       <c r="K142" s="5" t="n">
-        <v>42384100</v>
+        <v>39468600</v>
       </c>
       <c r="L142" s="5" t="n">
-        <v>29681</v>
+        <v>32325</v>
       </c>
       <c r="M142" s="3" t="inlineStr">
         <is>
@@ -9434,26 +9433,26 @@
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>5座</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E143" s="4" t="n">
-        <v>1237</v>
+        <v>1320</v>
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
@@ -9462,14 +9461,14 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2016-04-01</t>
+          <t>2016-05-13</t>
         </is>
       </c>
       <c r="H143" s="5" t="n">
-        <v>71332700</v>
+        <v>42946400</v>
       </c>
       <c r="I143" s="5" t="n">
-        <v>57666</v>
+        <v>32535</v>
       </c>
       <c r="J143" s="3" t="inlineStr">
         <is>
@@ -9477,10 +9476,10 @@
         </is>
       </c>
       <c r="K143" s="5" t="n">
-        <v>71332700</v>
+        <v>42946400</v>
       </c>
       <c r="L143" s="5" t="n">
-        <v>57666</v>
+        <v>32535</v>
       </c>
       <c r="M143" s="3" t="inlineStr">
         <is>
@@ -9496,7 +9495,7 @@
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>5座</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
@@ -9506,16 +9505,16 @@
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E144" s="4" t="n">
-        <v>1738</v>
+        <v>1160</v>
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
@@ -9524,14 +9523,14 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2016-04-25</t>
+          <t>2016-05-11</t>
         </is>
       </c>
       <c r="H144" s="5" t="n">
-        <v>66498900</v>
+        <v>38407700</v>
       </c>
       <c r="I144" s="5" t="n">
-        <v>38262</v>
+        <v>33110</v>
       </c>
       <c r="J144" s="3" t="inlineStr">
         <is>
@@ -9539,10 +9538,10 @@
         </is>
       </c>
       <c r="K144" s="5" t="n">
-        <v>66498900</v>
+        <v>38407700</v>
       </c>
       <c r="L144" s="5" t="n">
-        <v>38262</v>
+        <v>33110</v>
       </c>
       <c r="M144" s="3" t="inlineStr">
         <is>
@@ -9558,7 +9557,7 @@
     <row r="145">
       <c r="A145" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>5座</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
@@ -9568,7 +9567,7 @@
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr">
@@ -9577,7 +9576,7 @@
         </is>
       </c>
       <c r="E145" s="4" t="n">
-        <v>1708</v>
+        <v>1723</v>
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
@@ -9586,14 +9585,14 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2019-02-26</t>
+          <t>2019-01-31</t>
         </is>
       </c>
       <c r="H145" s="5" t="n">
-        <v>75670800</v>
+        <v>71444000</v>
       </c>
       <c r="I145" s="5" t="n">
-        <v>44304</v>
+        <v>41465</v>
       </c>
       <c r="J145" s="3" t="inlineStr">
         <is>
@@ -9601,10 +9600,10 @@
         </is>
       </c>
       <c r="K145" s="5" t="n">
-        <v>75670800</v>
+        <v>71444000</v>
       </c>
       <c r="L145" s="5" t="n">
-        <v>44304</v>
+        <v>41465</v>
       </c>
       <c r="M145" s="3" t="inlineStr">
         <is>
@@ -9620,17 +9619,17 @@
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>5座</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D146" s="3" t="inlineStr">
@@ -9639,7 +9638,7 @@
         </is>
       </c>
       <c r="E146" s="4" t="n">
-        <v>1428</v>
+        <v>1221</v>
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
@@ -9648,14 +9647,14 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2016-04-27</t>
+          <t>2016-04-29</t>
         </is>
       </c>
       <c r="H146" s="5" t="n">
-        <v>42257300</v>
+        <v>38962000</v>
       </c>
       <c r="I146" s="5" t="n">
-        <v>29592</v>
+        <v>31910</v>
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
@@ -9663,10 +9662,10 @@
         </is>
       </c>
       <c r="K146" s="5" t="n">
-        <v>42257300</v>
+        <v>38962000</v>
       </c>
       <c r="L146" s="5" t="n">
-        <v>29592</v>
+        <v>31910</v>
       </c>
       <c r="M146" s="3" t="inlineStr">
         <is>
@@ -9682,26 +9681,26 @@
     <row r="147">
       <c r="A147" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>5座</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E147" s="4" t="n">
-        <v>1237</v>
+        <v>1320</v>
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
@@ -9710,14 +9709,14 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2016-04-21</t>
+          <t>2016-05-12</t>
         </is>
       </c>
       <c r="H147" s="5" t="n">
-        <v>35559600</v>
+        <v>42732700</v>
       </c>
       <c r="I147" s="5" t="n">
-        <v>28747</v>
+        <v>32373</v>
       </c>
       <c r="J147" s="3" t="inlineStr">
         <is>
@@ -9725,10 +9724,10 @@
         </is>
       </c>
       <c r="K147" s="5" t="n">
-        <v>35559600</v>
+        <v>42732700</v>
       </c>
       <c r="L147" s="5" t="n">
-        <v>28747</v>
+        <v>32373</v>
       </c>
       <c r="M147" s="3" t="inlineStr">
         <is>
@@ -9744,7 +9743,7 @@
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>5座</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
@@ -9754,16 +9753,16 @@
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E148" s="4" t="n">
-        <v>1738</v>
+        <v>1160</v>
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
@@ -9772,14 +9771,14 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2016-05-17</t>
+          <t>2016-05-12</t>
         </is>
       </c>
       <c r="H148" s="5" t="n">
-        <v>65323000</v>
+        <v>38197600</v>
       </c>
       <c r="I148" s="5" t="n">
-        <v>37585</v>
+        <v>32929</v>
       </c>
       <c r="J148" s="3" t="inlineStr">
         <is>
@@ -9787,10 +9786,10 @@
         </is>
       </c>
       <c r="K148" s="5" t="n">
-        <v>65323000</v>
+        <v>38197600</v>
       </c>
       <c r="L148" s="5" t="n">
-        <v>37585</v>
+        <v>32929</v>
       </c>
       <c r="M148" s="3" t="inlineStr">
         <is>
@@ -9806,7 +9805,7 @@
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>5座</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
@@ -9816,7 +9815,7 @@
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D149" s="3" t="inlineStr">
@@ -9825,7 +9824,7 @@
         </is>
       </c>
       <c r="E149" s="4" t="n">
-        <v>1708</v>
+        <v>1723</v>
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
@@ -9834,14 +9833,14 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>2019-01-31</t>
+          <t>2019-01-15</t>
         </is>
       </c>
       <c r="H149" s="5" t="n">
-        <v>74718000</v>
+        <v>63585000</v>
       </c>
       <c r="I149" s="5" t="n">
-        <v>43746</v>
+        <v>36904</v>
       </c>
       <c r="J149" s="3" t="inlineStr">
         <is>
@@ -9849,10 +9848,10 @@
         </is>
       </c>
       <c r="K149" s="5" t="n">
-        <v>74718000</v>
+        <v>63585000</v>
       </c>
       <c r="L149" s="5" t="n">
-        <v>43746</v>
+        <v>36904</v>
       </c>
       <c r="M149" s="3" t="inlineStr">
         <is>
@@ -9868,17 +9867,17 @@
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>5座</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D150" s="3" t="inlineStr">
@@ -9887,7 +9886,7 @@
         </is>
       </c>
       <c r="E150" s="4" t="n">
-        <v>1428</v>
+        <v>1316</v>
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
@@ -9896,14 +9895,14 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2016-04-27</t>
+          <t>2016-04-15</t>
         </is>
       </c>
       <c r="H150" s="5" t="n">
-        <v>42130900</v>
+        <v>76431800</v>
       </c>
       <c r="I150" s="5" t="n">
-        <v>29503</v>
+        <v>58079</v>
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
@@ -9911,10 +9910,10 @@
         </is>
       </c>
       <c r="K150" s="5" t="n">
-        <v>42130900</v>
+        <v>76431800</v>
       </c>
       <c r="L150" s="5" t="n">
-        <v>29503</v>
+        <v>58079</v>
       </c>
       <c r="M150" s="3" t="inlineStr">
         <is>
@@ -9930,26 +9929,26 @@
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>5座</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E151" s="4" t="n">
-        <v>1237</v>
+        <v>1320</v>
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
@@ -9958,14 +9957,14 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2016-04-27</t>
+          <t>2016-04-29</t>
         </is>
       </c>
       <c r="H151" s="5" t="n">
-        <v>35488600</v>
+        <v>41895500</v>
       </c>
       <c r="I151" s="5" t="n">
-        <v>28689</v>
+        <v>31739</v>
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
@@ -9973,10 +9972,10 @@
         </is>
       </c>
       <c r="K151" s="5" t="n">
-        <v>35488600</v>
+        <v>41895500</v>
       </c>
       <c r="L151" s="5" t="n">
-        <v>28689</v>
+        <v>31739</v>
       </c>
       <c r="M151" s="3" t="inlineStr">
         <is>
@@ -9992,7 +9991,7 @@
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>5座</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
@@ -10002,16 +10001,16 @@
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E152" s="4" t="n">
-        <v>1738</v>
+        <v>1160</v>
       </c>
       <c r="F152" s="3" t="inlineStr">
         <is>
@@ -10020,14 +10019,14 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2016-05-10</t>
+          <t>2016-04-15</t>
         </is>
       </c>
       <c r="H152" s="5" t="n">
-        <v>64168100</v>
+        <v>76431800</v>
       </c>
       <c r="I152" s="5" t="n">
-        <v>36921</v>
+        <v>65889</v>
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
@@ -10035,10 +10034,10 @@
         </is>
       </c>
       <c r="K152" s="5" t="n">
-        <v>64168100</v>
+        <v>76431800</v>
       </c>
       <c r="L152" s="5" t="n">
-        <v>36921</v>
+        <v>65889</v>
       </c>
       <c r="M152" s="3" t="inlineStr">
         <is>
@@ -10054,7 +10053,7 @@
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>5座</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
@@ -10064,7 +10063,7 @@
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
@@ -10073,7 +10072,7 @@
         </is>
       </c>
       <c r="E153" s="4" t="n">
-        <v>1708</v>
+        <v>1723</v>
       </c>
       <c r="F153" s="3" t="inlineStr">
         <is>
@@ -10082,14 +10081,14 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2019-01-25</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="H153" s="5" t="n">
-        <v>67636800</v>
+        <v>53423338</v>
       </c>
       <c r="I153" s="5" t="n">
-        <v>39600</v>
+        <v>31006</v>
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
@@ -10097,10 +10096,10 @@
         </is>
       </c>
       <c r="K153" s="5" t="n">
-        <v>67636800</v>
+        <v>53423338</v>
       </c>
       <c r="L153" s="5" t="n">
-        <v>39600</v>
+        <v>31006</v>
       </c>
       <c r="M153" s="3" t="inlineStr">
         <is>
@@ -10116,17 +10115,17 @@
     <row r="154">
       <c r="A154" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>5座</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D154" s="3" t="inlineStr">
@@ -10135,7 +10134,7 @@
         </is>
       </c>
       <c r="E154" s="4" t="n">
-        <v>1428</v>
+        <v>1316</v>
       </c>
       <c r="F154" s="3" t="inlineStr">
         <is>
@@ -10148,10 +10147,10 @@
         </is>
       </c>
       <c r="H154" s="5" t="n">
-        <v>42130900</v>
+        <v>37968500</v>
       </c>
       <c r="I154" s="5" t="n">
-        <v>29503</v>
+        <v>28851</v>
       </c>
       <c r="J154" s="3" t="inlineStr">
         <is>
@@ -10159,10 +10158,10 @@
         </is>
       </c>
       <c r="K154" s="5" t="n">
-        <v>42130900</v>
+        <v>37968500</v>
       </c>
       <c r="L154" s="5" t="n">
-        <v>29503</v>
+        <v>28851</v>
       </c>
       <c r="M154" s="3" t="inlineStr">
         <is>
@@ -10178,26 +10177,26 @@
     <row r="155">
       <c r="A155" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>5座</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E155" s="4" t="n">
-        <v>1237</v>
+        <v>1320</v>
       </c>
       <c r="F155" s="3" t="inlineStr">
         <is>
@@ -10206,14 +10205,14 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2016-05-04</t>
+          <t>2016-05-17</t>
         </is>
       </c>
       <c r="H155" s="5" t="n">
-        <v>35488600</v>
+        <v>41964900</v>
       </c>
       <c r="I155" s="5" t="n">
-        <v>28689</v>
+        <v>31792</v>
       </c>
       <c r="J155" s="3" t="inlineStr">
         <is>
@@ -10221,10 +10220,10 @@
         </is>
       </c>
       <c r="K155" s="5" t="n">
-        <v>35488600</v>
+        <v>41964900</v>
       </c>
       <c r="L155" s="5" t="n">
-        <v>28689</v>
+        <v>31792</v>
       </c>
       <c r="M155" s="3" t="inlineStr">
         <is>
@@ -10240,7 +10239,7 @@
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>5座</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
@@ -10250,16 +10249,16 @@
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E156" s="4" t="n">
-        <v>1738</v>
+        <v>1160</v>
       </c>
       <c r="F156" s="3" t="inlineStr">
         <is>
@@ -10268,14 +10267,14 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2016-04-15</t>
+          <t>2016-05-18</t>
         </is>
       </c>
       <c r="H156" s="5" t="n">
-        <v>134983100</v>
+        <v>37816800</v>
       </c>
       <c r="I156" s="5" t="n">
-        <v>77666</v>
+        <v>32601</v>
       </c>
       <c r="J156" s="3" t="inlineStr">
         <is>
@@ -10283,10 +10282,10 @@
         </is>
       </c>
       <c r="K156" s="5" t="n">
-        <v>134983100</v>
+        <v>37816800</v>
       </c>
       <c r="L156" s="5" t="n">
-        <v>77666</v>
+        <v>32601</v>
       </c>
       <c r="M156" s="3" t="inlineStr">
         <is>
@@ -10302,7 +10301,7 @@
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>5座</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
@@ -10312,7 +10311,7 @@
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D157" s="3" t="inlineStr">
@@ -10321,7 +10320,7 @@
         </is>
       </c>
       <c r="E157" s="4" t="n">
-        <v>1708</v>
+        <v>1723</v>
       </c>
       <c r="F157" s="3" t="inlineStr">
         <is>
@@ -10330,14 +10329,14 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2016-04-15</t>
+          <t>2019-01-07</t>
         </is>
       </c>
       <c r="H157" s="5" t="n">
-        <v>134983100</v>
+        <v>62677000</v>
       </c>
       <c r="I157" s="5" t="n">
-        <v>79030</v>
+        <v>36377</v>
       </c>
       <c r="J157" s="3" t="inlineStr">
         <is>
@@ -10345,10 +10344,10 @@
         </is>
       </c>
       <c r="K157" s="5" t="n">
-        <v>134983100</v>
+        <v>62677000</v>
       </c>
       <c r="L157" s="5" t="n">
-        <v>79030</v>
+        <v>36377</v>
       </c>
       <c r="M157" s="3" t="inlineStr">
         <is>
@@ -10364,17 +10363,17 @@
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>5座</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D158" s="3" t="inlineStr">
@@ -10383,7 +10382,7 @@
         </is>
       </c>
       <c r="E158" s="4" t="n">
-        <v>1428</v>
+        <v>1316</v>
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
@@ -10392,14 +10391,14 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2016-04-21</t>
+          <t>2016-05-09</t>
         </is>
       </c>
       <c r="H158" s="5" t="n">
-        <v>41879700</v>
+        <v>37592500</v>
       </c>
       <c r="I158" s="5" t="n">
-        <v>29328</v>
+        <v>28566</v>
       </c>
       <c r="J158" s="3" t="inlineStr">
         <is>
@@ -10407,10 +10406,10 @@
         </is>
       </c>
       <c r="K158" s="5" t="n">
-        <v>41879700</v>
+        <v>37592500</v>
       </c>
       <c r="L158" s="5" t="n">
-        <v>29328</v>
+        <v>28566</v>
       </c>
       <c r="M158" s="3" t="inlineStr">
         <is>
@@ -10426,26 +10425,26 @@
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>5座</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E159" s="4" t="n">
-        <v>1237</v>
+        <v>1320</v>
       </c>
       <c r="F159" s="3" t="inlineStr">
         <is>
@@ -10454,14 +10453,14 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2016-04-21</t>
+          <t>2016-05-13</t>
         </is>
       </c>
       <c r="H159" s="5" t="n">
-        <v>35347200</v>
+        <v>41549400</v>
       </c>
       <c r="I159" s="5" t="n">
-        <v>28575</v>
+        <v>31477</v>
       </c>
       <c r="J159" s="3" t="inlineStr">
         <is>
@@ -10469,10 +10468,10 @@
         </is>
       </c>
       <c r="K159" s="5" t="n">
-        <v>35347200</v>
+        <v>41549400</v>
       </c>
       <c r="L159" s="5" t="n">
-        <v>28575</v>
+        <v>31477</v>
       </c>
       <c r="M159" s="3" t="inlineStr">
         <is>
@@ -10488,7 +10487,7 @@
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>5座</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
@@ -10498,16 +10497,16 @@
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D160" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E160" s="4" t="n">
-        <v>1738</v>
+        <v>1160</v>
       </c>
       <c r="F160" s="3" t="inlineStr">
         <is>
@@ -10516,14 +10515,14 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2016-04-21</t>
+          <t>2016-05-13</t>
         </is>
       </c>
       <c r="H160" s="5" t="n">
-        <v>61919400</v>
+        <v>36529200</v>
       </c>
       <c r="I160" s="5" t="n">
-        <v>35627</v>
+        <v>31491</v>
       </c>
       <c r="J160" s="3" t="inlineStr">
         <is>
@@ -10531,10 +10530,10 @@
         </is>
       </c>
       <c r="K160" s="5" t="n">
-        <v>61919400</v>
+        <v>36529200</v>
       </c>
       <c r="L160" s="5" t="n">
-        <v>35627</v>
+        <v>31491</v>
       </c>
       <c r="M160" s="3" t="inlineStr">
         <is>
@@ -10550,7 +10549,7 @@
     <row r="161">
       <c r="A161" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>5座</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
@@ -10560,7 +10559,7 @@
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr">
@@ -10569,7 +10568,7 @@
         </is>
       </c>
       <c r="E161" s="4" t="n">
-        <v>1708</v>
+        <v>1723</v>
       </c>
       <c r="F161" s="3" t="inlineStr">
         <is>
@@ -10578,14 +10577,14 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2023-05-05</t>
+          <t>2019-01-17</t>
         </is>
       </c>
       <c r="H161" s="5" t="n">
-        <v>66622000</v>
+        <v>64512640</v>
       </c>
       <c r="I161" s="5" t="n">
-        <v>39006</v>
+        <v>37442</v>
       </c>
       <c r="J161" s="3" t="inlineStr">
         <is>
@@ -10593,10 +10592,10 @@
         </is>
       </c>
       <c r="K161" s="5" t="n">
-        <v>66622000</v>
+        <v>64512640</v>
       </c>
       <c r="L161" s="5" t="n">
-        <v>39006</v>
+        <v>37442</v>
       </c>
       <c r="M161" s="3" t="inlineStr">
         <is>
@@ -10612,17 +10611,17 @@
     <row r="162">
       <c r="A162" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>5座</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D162" s="3" t="inlineStr">
@@ -10631,7 +10630,7 @@
         </is>
       </c>
       <c r="E162" s="4" t="n">
-        <v>1428</v>
+        <v>1221</v>
       </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
@@ -10640,14 +10639,14 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2016-04-19</t>
+          <t>2016-05-17</t>
         </is>
       </c>
       <c r="H162" s="5" t="n">
-        <v>41754400</v>
+        <v>37000500</v>
       </c>
       <c r="I162" s="5" t="n">
-        <v>29240</v>
+        <v>30303</v>
       </c>
       <c r="J162" s="3" t="inlineStr">
         <is>
@@ -10655,10 +10654,10 @@
         </is>
       </c>
       <c r="K162" s="5" t="n">
-        <v>41754400</v>
+        <v>37000500</v>
       </c>
       <c r="L162" s="5" t="n">
-        <v>29240</v>
+        <v>30303</v>
       </c>
       <c r="M162" s="3" t="inlineStr">
         <is>
@@ -10674,26 +10673,26 @@
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>5座</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D163" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E163" s="4" t="n">
-        <v>1237</v>
+        <v>1320</v>
       </c>
       <c r="F163" s="3" t="inlineStr">
         <is>
@@ -10702,14 +10701,14 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2016-04-26</t>
+          <t>2016-05-05</t>
         </is>
       </c>
       <c r="H163" s="5" t="n">
-        <v>35276700</v>
+        <v>40105600</v>
       </c>
       <c r="I163" s="5" t="n">
-        <v>28518</v>
+        <v>30383</v>
       </c>
       <c r="J163" s="3" t="inlineStr">
         <is>
@@ -10717,10 +10716,10 @@
         </is>
       </c>
       <c r="K163" s="5" t="n">
-        <v>35276700</v>
+        <v>40105600</v>
       </c>
       <c r="L163" s="5" t="n">
-        <v>28518</v>
+        <v>30383</v>
       </c>
       <c r="M163" s="3" t="inlineStr">
         <is>
@@ -10736,7 +10735,7 @@
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>5座</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
@@ -10746,16 +10745,16 @@
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E164" s="4" t="n">
-        <v>1738</v>
+        <v>1160</v>
       </c>
       <c r="F164" s="3" t="inlineStr">
         <is>
@@ -10768,10 +10767,10 @@
         </is>
       </c>
       <c r="H164" s="5" t="n">
-        <v>60824600</v>
+        <v>35396400</v>
       </c>
       <c r="I164" s="5" t="n">
-        <v>34997</v>
+        <v>30514</v>
       </c>
       <c r="J164" s="3" t="inlineStr">
         <is>
@@ -10779,10 +10778,10 @@
         </is>
       </c>
       <c r="K164" s="5" t="n">
-        <v>60824600</v>
+        <v>35396400</v>
       </c>
       <c r="L164" s="5" t="n">
-        <v>34997</v>
+        <v>30514</v>
       </c>
       <c r="M164" s="3" t="inlineStr">
         <is>
@@ -10798,7 +10797,7 @@
     <row r="165">
       <c r="A165" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>5座</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
@@ -10808,7 +10807,7 @@
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D165" s="3" t="inlineStr">
@@ -10817,7 +10816,7 @@
         </is>
       </c>
       <c r="E165" s="4" t="n">
-        <v>1708</v>
+        <v>1723</v>
       </c>
       <c r="F165" s="3" t="inlineStr">
         <is>
@@ -10826,14 +10825,14 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2019-01-21</t>
+          <t>2019-01-17</t>
         </is>
       </c>
       <c r="H165" s="5" t="n">
-        <v>66628000</v>
+        <v>68018820</v>
       </c>
       <c r="I165" s="5" t="n">
-        <v>39009</v>
+        <v>39477</v>
       </c>
       <c r="J165" s="3" t="inlineStr">
         <is>
@@ -10841,10 +10840,10 @@
         </is>
       </c>
       <c r="K165" s="5" t="n">
-        <v>66628000</v>
+        <v>68018820</v>
       </c>
       <c r="L165" s="5" t="n">
-        <v>39009</v>
+        <v>39477</v>
       </c>
       <c r="M165" s="3" t="inlineStr">
         <is>
@@ -10860,17 +10859,17 @@
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>5座</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D166" s="3" t="inlineStr">
@@ -10879,7 +10878,7 @@
         </is>
       </c>
       <c r="E166" s="4" t="n">
-        <v>1428</v>
+        <v>1316</v>
       </c>
       <c r="F166" s="3" t="inlineStr">
         <is>
@@ -10888,14 +10887,14 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2016-05-17</t>
+          <t>2016-05-13</t>
         </is>
       </c>
       <c r="H166" s="5" t="n">
-        <v>41629100</v>
+        <v>36525700</v>
       </c>
       <c r="I166" s="5" t="n">
-        <v>29152</v>
+        <v>27755</v>
       </c>
       <c r="J166" s="3" t="inlineStr">
         <is>
@@ -10903,10 +10902,10 @@
         </is>
       </c>
       <c r="K166" s="5" t="n">
-        <v>41629100</v>
+        <v>36525700</v>
       </c>
       <c r="L166" s="5" t="n">
-        <v>29152</v>
+        <v>27755</v>
       </c>
       <c r="M166" s="3" t="inlineStr">
         <is>
@@ -10922,26 +10921,26 @@
     <row r="167">
       <c r="A167" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>5座</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D167" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E167" s="4" t="n">
-        <v>1237</v>
+        <v>1320</v>
       </c>
       <c r="F167" s="3" t="inlineStr">
         <is>
@@ -10950,14 +10949,14 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2016-04-29</t>
+          <t>2016-05-06</t>
         </is>
       </c>
       <c r="H167" s="5" t="n">
-        <v>35170800</v>
+        <v>39396400</v>
       </c>
       <c r="I167" s="5" t="n">
-        <v>28432</v>
+        <v>29846</v>
       </c>
       <c r="J167" s="3" t="inlineStr">
         <is>
@@ -10965,10 +10964,10 @@
         </is>
       </c>
       <c r="K167" s="5" t="n">
-        <v>35170800</v>
+        <v>39396400</v>
       </c>
       <c r="L167" s="5" t="n">
-        <v>28432</v>
+        <v>29846</v>
       </c>
       <c r="M167" s="3" t="inlineStr">
         <is>
@@ -10984,7 +10983,7 @@
     <row r="168">
       <c r="A168" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>5座</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
@@ -10994,16 +10993,16 @@
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D168" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E168" s="4" t="n">
-        <v>1738</v>
+        <v>1065</v>
       </c>
       <c r="F168" s="3" t="inlineStr">
         <is>
@@ -11012,14 +11011,14 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2016-04-29</t>
+          <t>2016-05-13</t>
         </is>
       </c>
       <c r="H168" s="5" t="n">
-        <v>60642100</v>
+        <v>35290300</v>
       </c>
       <c r="I168" s="5" t="n">
-        <v>34892</v>
+        <v>33136</v>
       </c>
       <c r="J168" s="3" t="inlineStr">
         <is>
@@ -11027,10 +11026,10 @@
         </is>
       </c>
       <c r="K168" s="5" t="n">
-        <v>60642100</v>
+        <v>35290300</v>
       </c>
       <c r="L168" s="5" t="n">
-        <v>34892</v>
+        <v>33136</v>
       </c>
       <c r="M168" s="3" t="inlineStr">
         <is>
@@ -11046,7 +11045,7 @@
     <row r="169">
       <c r="A169" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>5座</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
@@ -11056,7 +11055,7 @@
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D169" s="3" t="inlineStr">
@@ -11065,7 +11064,7 @@
         </is>
       </c>
       <c r="E169" s="4" t="n">
-        <v>1708</v>
+        <v>1723</v>
       </c>
       <c r="F169" s="3" t="inlineStr">
         <is>
@@ -11074,14 +11073,14 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2019-01-18</t>
+          <t>2019-01-07</t>
         </is>
       </c>
       <c r="H169" s="5" t="n">
-        <v>64830000</v>
+        <v>58143200</v>
       </c>
       <c r="I169" s="5" t="n">
-        <v>37957</v>
+        <v>33745</v>
       </c>
       <c r="J169" s="3" t="inlineStr">
         <is>
@@ -11089,10 +11088,10 @@
         </is>
       </c>
       <c r="K169" s="5" t="n">
-        <v>64830000</v>
+        <v>58143200</v>
       </c>
       <c r="L169" s="5" t="n">
-        <v>37957</v>
+        <v>33745</v>
       </c>
       <c r="M169" s="3" t="inlineStr">
         <is>
@@ -11108,17 +11107,17 @@
     <row r="170">
       <c r="A170" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>5座</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D170" s="3" t="inlineStr">
@@ -11127,7 +11126,7 @@
         </is>
       </c>
       <c r="E170" s="4" t="n">
-        <v>1428</v>
+        <v>1316</v>
       </c>
       <c r="F170" s="3" t="inlineStr">
         <is>
@@ -11136,14 +11135,14 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2016-04-22</t>
+          <t>2016-05-17</t>
         </is>
       </c>
       <c r="H170" s="5" t="n">
-        <v>40671700</v>
+        <v>36416100</v>
       </c>
       <c r="I170" s="5" t="n">
-        <v>28482</v>
+        <v>27672</v>
       </c>
       <c r="J170" s="3" t="inlineStr">
         <is>
@@ -11151,10 +11150,10 @@
         </is>
       </c>
       <c r="K170" s="5" t="n">
-        <v>40671700</v>
+        <v>36416100</v>
       </c>
       <c r="L170" s="5" t="n">
-        <v>28482</v>
+        <v>27672</v>
       </c>
       <c r="M170" s="3" t="inlineStr">
         <is>
@@ -11170,26 +11169,26 @@
     <row r="171">
       <c r="A171" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>5座</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D171" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E171" s="4" t="n">
-        <v>1237</v>
+        <v>1320</v>
       </c>
       <c r="F171" s="3" t="inlineStr">
         <is>
@@ -11198,14 +11197,14 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2016-05-13</t>
+          <t>2016-05-05</t>
         </is>
       </c>
       <c r="H171" s="5" t="n">
-        <v>34537800</v>
+        <v>39278300</v>
       </c>
       <c r="I171" s="5" t="n">
-        <v>27921</v>
+        <v>29756</v>
       </c>
       <c r="J171" s="3" t="inlineStr">
         <is>
@@ -11213,10 +11212,10 @@
         </is>
       </c>
       <c r="K171" s="5" t="n">
-        <v>34537800</v>
+        <v>39278300</v>
       </c>
       <c r="L171" s="5" t="n">
-        <v>27921</v>
+        <v>29756</v>
       </c>
       <c r="M171" s="3" t="inlineStr">
         <is>
@@ -11232,7 +11231,7 @@
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>5座</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
@@ -11242,16 +11241,16 @@
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D172" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E172" s="4" t="n">
-        <v>1738</v>
+        <v>1160</v>
       </c>
       <c r="F172" s="3" t="inlineStr">
         <is>
@@ -11260,14 +11259,14 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2016-04-25</t>
+          <t>2016-05-12</t>
         </is>
       </c>
       <c r="H172" s="5" t="n">
-        <v>58640900</v>
+        <v>35007900</v>
       </c>
       <c r="I172" s="5" t="n">
-        <v>33740</v>
+        <v>30179</v>
       </c>
       <c r="J172" s="3" t="inlineStr">
         <is>
@@ -11275,10 +11274,10 @@
         </is>
       </c>
       <c r="K172" s="5" t="n">
-        <v>58640900</v>
+        <v>35007900</v>
       </c>
       <c r="L172" s="5" t="n">
-        <v>33740</v>
+        <v>30179</v>
       </c>
       <c r="M172" s="3" t="inlineStr">
         <is>
@@ -11294,7 +11293,7 @@
     <row r="173">
       <c r="A173" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>5座</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
@@ -11304,7 +11303,7 @@
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D173" s="3" t="inlineStr">
@@ -11313,7 +11312,7 @@
         </is>
       </c>
       <c r="E173" s="4" t="n">
-        <v>1708</v>
+        <v>1723</v>
       </c>
       <c r="F173" s="3" t="inlineStr">
         <is>
@@ -11322,14 +11321,14 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2016-05-09</t>
+          <t>2019-01-17</t>
         </is>
       </c>
       <c r="H173" s="5" t="n">
-        <v>62900600</v>
+        <v>58150600</v>
       </c>
       <c r="I173" s="5" t="n">
-        <v>36827</v>
+        <v>33750</v>
       </c>
       <c r="J173" s="3" t="inlineStr">
         <is>
@@ -11337,10 +11336,10 @@
         </is>
       </c>
       <c r="K173" s="5" t="n">
-        <v>62900600</v>
+        <v>58150600</v>
       </c>
       <c r="L173" s="5" t="n">
-        <v>36827</v>
+        <v>33750</v>
       </c>
       <c r="M173" s="3" t="inlineStr">
         <is>
@@ -11356,17 +11355,17 @@
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>5座</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C174" s="3" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D174" s="3" t="inlineStr">
@@ -11375,7 +11374,7 @@
         </is>
       </c>
       <c r="E174" s="4" t="n">
-        <v>1428</v>
+        <v>1316</v>
       </c>
       <c r="F174" s="3" t="inlineStr">
         <is>
@@ -11384,14 +11383,14 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2016-05-05</t>
+          <t>2016-04-28</t>
         </is>
       </c>
       <c r="H174" s="5" t="n">
-        <v>39329500</v>
+        <v>35760600</v>
       </c>
       <c r="I174" s="5" t="n">
-        <v>27542</v>
+        <v>27174</v>
       </c>
       <c r="J174" s="3" t="inlineStr">
         <is>
@@ -11399,10 +11398,10 @@
         </is>
       </c>
       <c r="K174" s="5" t="n">
-        <v>39329500</v>
+        <v>35760600</v>
       </c>
       <c r="L174" s="5" t="n">
-        <v>27542</v>
+        <v>27174</v>
       </c>
       <c r="M174" s="3" t="inlineStr">
         <is>
@@ -11418,26 +11417,26 @@
     <row r="175">
       <c r="A175" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>5座</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C175" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D175" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E175" s="4" t="n">
-        <v>1237</v>
+        <v>1320</v>
       </c>
       <c r="F175" s="3" t="inlineStr">
         <is>
@@ -11446,14 +11445,14 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2016-05-05</t>
+          <t>2016-04-28</t>
         </is>
       </c>
       <c r="H175" s="5" t="n">
-        <v>33398000</v>
+        <v>38374900</v>
       </c>
       <c r="I175" s="5" t="n">
-        <v>26999</v>
+        <v>29072</v>
       </c>
       <c r="J175" s="3" t="inlineStr">
         <is>
@@ -11461,10 +11460,10 @@
         </is>
       </c>
       <c r="K175" s="5" t="n">
-        <v>33398000</v>
+        <v>38374900</v>
       </c>
       <c r="L175" s="5" t="n">
-        <v>26999</v>
+        <v>29072</v>
       </c>
       <c r="M175" s="3" t="inlineStr">
         <is>
@@ -11480,7 +11479,7 @@
     <row r="176">
       <c r="A176" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>5座</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
@@ -11490,16 +11489,16 @@
       </c>
       <c r="C176" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D176" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E176" s="4" t="n">
-        <v>1738</v>
+        <v>1160</v>
       </c>
       <c r="F176" s="3" t="inlineStr">
         <is>
@@ -11508,14 +11507,14 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2016-04-28</t>
+          <t>2016-05-11</t>
         </is>
       </c>
       <c r="H176" s="5" t="n">
-        <v>54360100</v>
+        <v>34031200</v>
       </c>
       <c r="I176" s="5" t="n">
-        <v>31277</v>
+        <v>29337</v>
       </c>
       <c r="J176" s="3" t="inlineStr">
         <is>
@@ -11523,10 +11522,10 @@
         </is>
       </c>
       <c r="K176" s="5" t="n">
-        <v>54360100</v>
+        <v>34031200</v>
       </c>
       <c r="L176" s="5" t="n">
-        <v>31277</v>
+        <v>29337</v>
       </c>
       <c r="M176" s="3" t="inlineStr">
         <is>
@@ -11542,7 +11541,7 @@
     <row r="177">
       <c r="A177" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>5座</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
@@ -11552,7 +11551,7 @@
       </c>
       <c r="C177" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D177" s="3" t="inlineStr">
@@ -11561,7 +11560,7 @@
         </is>
       </c>
       <c r="E177" s="4" t="n">
-        <v>1708</v>
+        <v>1723</v>
       </c>
       <c r="F177" s="3" t="inlineStr">
         <is>
@@ -11570,14 +11569,14 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2019-01-22</t>
+          <t>2016-05-09</t>
         </is>
       </c>
       <c r="H177" s="5" t="n">
-        <v>58896440</v>
+        <v>56633900</v>
       </c>
       <c r="I177" s="5" t="n">
-        <v>34483</v>
+        <v>32869</v>
       </c>
       <c r="J177" s="3" t="inlineStr">
         <is>
@@ -11585,10 +11584,10 @@
         </is>
       </c>
       <c r="K177" s="5" t="n">
-        <v>58896440</v>
+        <v>56633900</v>
       </c>
       <c r="L177" s="5" t="n">
-        <v>34483</v>
+        <v>32869</v>
       </c>
       <c r="M177" s="3" t="inlineStr">
         <is>
@@ -11604,17 +11603,17 @@
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>5座</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C178" s="3" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D178" s="3" t="inlineStr">
@@ -11623,7 +11622,7 @@
         </is>
       </c>
       <c r="E178" s="4" t="n">
-        <v>1428</v>
+        <v>1316</v>
       </c>
       <c r="F178" s="3" t="inlineStr">
         <is>
@@ -11632,14 +11631,14 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2016-04-26</t>
+          <t>2016-04-29</t>
         </is>
       </c>
       <c r="H178" s="5" t="n">
-        <v>38424900</v>
+        <v>35117000</v>
       </c>
       <c r="I178" s="5" t="n">
-        <v>26908</v>
+        <v>26685</v>
       </c>
       <c r="J178" s="3" t="inlineStr">
         <is>
@@ -11647,10 +11646,10 @@
         </is>
       </c>
       <c r="K178" s="5" t="n">
-        <v>38424900</v>
+        <v>35117000</v>
       </c>
       <c r="L178" s="5" t="n">
-        <v>26908</v>
+        <v>26685</v>
       </c>
       <c r="M178" s="3" t="inlineStr">
         <is>
@@ -11666,26 +11665,26 @@
     <row r="179">
       <c r="A179" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>5座</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C179" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D179" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E179" s="4" t="n">
-        <v>1237</v>
+        <v>1320</v>
       </c>
       <c r="F179" s="3" t="inlineStr">
         <is>
@@ -11694,14 +11693,14 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2016-04-20</t>
+          <t>2016-04-27</t>
         </is>
       </c>
       <c r="H179" s="5" t="n">
-        <v>32629900</v>
+        <v>37108500</v>
       </c>
       <c r="I179" s="5" t="n">
-        <v>26378</v>
+        <v>28112</v>
       </c>
       <c r="J179" s="3" t="inlineStr">
         <is>
@@ -11709,10 +11708,10 @@
         </is>
       </c>
       <c r="K179" s="5" t="n">
-        <v>32629900</v>
+        <v>37108500</v>
       </c>
       <c r="L179" s="5" t="n">
-        <v>26378</v>
+        <v>28112</v>
       </c>
       <c r="M179" s="3" t="inlineStr">
         <is>
@@ -11728,7 +11727,7 @@
     <row r="180">
       <c r="A180" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>5座</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
@@ -11738,16 +11737,16 @@
       </c>
       <c r="C180" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D180" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E180" s="4" t="n">
-        <v>1738</v>
+        <v>1065</v>
       </c>
       <c r="F180" s="3" t="inlineStr">
         <is>
@@ -11756,14 +11755,14 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2016-05-03</t>
+          <t>2016-05-12</t>
         </is>
       </c>
       <c r="H180" s="5" t="n">
-        <v>44412200</v>
+        <v>33078400</v>
       </c>
       <c r="I180" s="5" t="n">
-        <v>25554</v>
+        <v>31060</v>
       </c>
       <c r="J180" s="3" t="inlineStr">
         <is>
@@ -11771,10 +11770,10 @@
         </is>
       </c>
       <c r="K180" s="5" t="n">
-        <v>44412200</v>
+        <v>33078400</v>
       </c>
       <c r="L180" s="5" t="n">
-        <v>25554</v>
+        <v>31060</v>
       </c>
       <c r="M180" s="3" t="inlineStr">
         <is>
@@ -11790,7 +11789,7 @@
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>5座</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
@@ -11800,7 +11799,7 @@
       </c>
       <c r="C181" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D181" s="3" t="inlineStr">
@@ -11809,7 +11808,7 @@
         </is>
       </c>
       <c r="E181" s="4" t="n">
-        <v>1708</v>
+        <v>1723</v>
       </c>
       <c r="F181" s="3" t="inlineStr">
         <is>
@@ -11818,14 +11817,14 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2019-03-04</t>
+          <t>2016-05-10</t>
         </is>
       </c>
       <c r="H181" s="5" t="n">
-        <v>55668000</v>
+        <v>54481700</v>
       </c>
       <c r="I181" s="5" t="n">
-        <v>32593</v>
+        <v>31620</v>
       </c>
       <c r="J181" s="3" t="inlineStr">
         <is>
@@ -11833,10 +11832,10 @@
         </is>
       </c>
       <c r="K181" s="5" t="n">
-        <v>55668000</v>
+        <v>54481700</v>
       </c>
       <c r="L181" s="5" t="n">
-        <v>32593</v>
+        <v>31620</v>
       </c>
       <c r="M181" s="3" t="inlineStr">
         <is>
@@ -11852,17 +11851,17 @@
     <row r="182">
       <c r="A182" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>5座</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C182" s="3" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D182" s="3" t="inlineStr">
@@ -11871,7 +11870,7 @@
         </is>
       </c>
       <c r="E182" s="4" t="n">
-        <v>1428</v>
+        <v>1221</v>
       </c>
       <c r="F182" s="3" t="inlineStr">
         <is>
@@ -11880,14 +11879,14 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2016-04-21</t>
+          <t>2016-04-15</t>
         </is>
       </c>
       <c r="H182" s="5" t="n">
-        <v>37425800</v>
+        <v>33606900</v>
       </c>
       <c r="I182" s="5" t="n">
-        <v>26209</v>
+        <v>27524</v>
       </c>
       <c r="J182" s="3" t="inlineStr">
         <is>
@@ -11895,10 +11894,10 @@
         </is>
       </c>
       <c r="K182" s="5" t="n">
-        <v>37425800</v>
+        <v>33606900</v>
       </c>
       <c r="L182" s="5" t="n">
-        <v>26209</v>
+        <v>27524</v>
       </c>
       <c r="M182" s="3" t="inlineStr">
         <is>
@@ -11914,26 +11913,26 @@
     <row r="183">
       <c r="A183" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>5座</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C183" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D183" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E183" s="4" t="n">
-        <v>1237</v>
+        <v>1320</v>
       </c>
       <c r="F183" s="3" t="inlineStr">
         <is>
@@ -11942,14 +11941,14 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2016-04-26</t>
+          <t>2016-05-12</t>
         </is>
       </c>
       <c r="H183" s="5" t="n">
-        <v>31781500</v>
+        <v>34770700</v>
       </c>
       <c r="I183" s="5" t="n">
-        <v>25692</v>
+        <v>26341</v>
       </c>
       <c r="J183" s="3" t="inlineStr">
         <is>
@@ -11957,10 +11956,10 @@
         </is>
       </c>
       <c r="K183" s="5" t="n">
-        <v>31781500</v>
+        <v>34770700</v>
       </c>
       <c r="L183" s="5" t="n">
-        <v>25692</v>
+        <v>26341</v>
       </c>
       <c r="M183" s="3" t="inlineStr">
         <is>
@@ -11976,7 +11975,7 @@
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>5座</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
@@ -11986,16 +11985,16 @@
       </c>
       <c r="C184" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D184" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E184" s="4" t="n">
-        <v>1738</v>
+        <v>1160</v>
       </c>
       <c r="F184" s="3" t="inlineStr">
         <is>
@@ -12004,14 +12003,14 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2016-04-01</t>
+          <t>2016-05-17</t>
         </is>
       </c>
       <c r="H184" s="5" t="n">
-        <v>80627200</v>
+        <v>31556800</v>
       </c>
       <c r="I184" s="5" t="n">
-        <v>46391</v>
+        <v>27204</v>
       </c>
       <c r="J184" s="3" t="inlineStr">
         <is>
@@ -12019,10 +12018,10 @@
         </is>
       </c>
       <c r="K184" s="5" t="n">
-        <v>80627200</v>
+        <v>31556800</v>
       </c>
       <c r="L184" s="5" t="n">
-        <v>46391</v>
+        <v>27204</v>
       </c>
       <c r="M184" s="3" t="inlineStr">
         <is>
@@ -12038,7 +12037,7 @@
     <row r="185">
       <c r="A185" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>5座</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
@@ -12048,7 +12047,7 @@
       </c>
       <c r="C185" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D185" s="3" t="inlineStr">
@@ -12057,7 +12056,7 @@
         </is>
       </c>
       <c r="E185" s="4" t="n">
-        <v>1708</v>
+        <v>1723</v>
       </c>
       <c r="F185" s="3" t="inlineStr">
         <is>
@@ -12066,14 +12065,14 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2016-04-01</t>
+          <t>2016-05-20</t>
         </is>
       </c>
       <c r="H185" s="5" t="n">
-        <v>80627200</v>
+        <v>52792900</v>
       </c>
       <c r="I185" s="5" t="n">
-        <v>47206</v>
+        <v>30640</v>
       </c>
       <c r="J185" s="3" t="inlineStr">
         <is>
@@ -12081,10 +12080,10 @@
         </is>
       </c>
       <c r="K185" s="5" t="n">
-        <v>80627200</v>
+        <v>52792900</v>
       </c>
       <c r="L185" s="5" t="n">
-        <v>47206</v>
+        <v>30640</v>
       </c>
       <c r="M185" s="3" t="inlineStr">
         <is>
@@ -12100,17 +12099,17 @@
     <row r="186">
       <c r="A186" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>5座</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C186" s="3" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D186" s="3" t="inlineStr">
@@ -12119,7 +12118,7 @@
         </is>
       </c>
       <c r="E186" s="4" t="n">
-        <v>1428</v>
+        <v>1316</v>
       </c>
       <c r="F186" s="3" t="inlineStr">
         <is>
@@ -12128,14 +12127,14 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2016-04-25</t>
+          <t>2016-05-03</t>
         </is>
       </c>
       <c r="H186" s="5" t="n">
-        <v>36303100</v>
+        <v>31388900</v>
       </c>
       <c r="I186" s="5" t="n">
-        <v>25422</v>
+        <v>23852</v>
       </c>
       <c r="J186" s="3" t="inlineStr">
         <is>
@@ -12143,10 +12142,10 @@
         </is>
       </c>
       <c r="K186" s="5" t="n">
-        <v>36303100</v>
+        <v>31388900</v>
       </c>
       <c r="L186" s="5" t="n">
-        <v>25422</v>
+        <v>23852</v>
       </c>
       <c r="M186" s="3" t="inlineStr">
         <is>
@@ -12162,26 +12161,26 @@
     <row r="187">
       <c r="A187" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>5座</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C187" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D187" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E187" s="4" t="n">
-        <v>1237</v>
+        <v>1320</v>
       </c>
       <c r="F187" s="3" t="inlineStr">
         <is>
@@ -12190,14 +12189,14 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>2016-04-25</t>
+          <t>2016-05-16</t>
         </is>
       </c>
       <c r="H187" s="5" t="n">
-        <v>31145900</v>
+        <v>33171200</v>
       </c>
       <c r="I187" s="5" t="n">
-        <v>25179</v>
+        <v>25130</v>
       </c>
       <c r="J187" s="3" t="inlineStr">
         <is>
@@ -12205,10 +12204,10 @@
         </is>
       </c>
       <c r="K187" s="5" t="n">
-        <v>31145900</v>
+        <v>33171200</v>
       </c>
       <c r="L187" s="5" t="n">
-        <v>25179</v>
+        <v>25130</v>
       </c>
       <c r="M187" s="3" t="inlineStr">
         <is>
@@ -12224,7 +12223,7 @@
     <row r="188">
       <c r="A188" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>5座</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
@@ -12234,16 +12233,16 @@
       </c>
       <c r="C188" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D188" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E188" s="4" t="n">
-        <v>1738</v>
+        <v>1065</v>
       </c>
       <c r="F188" s="3" t="inlineStr">
         <is>
@@ -12252,14 +12251,14 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2016-04-22</t>
+          <t>2016-05-18</t>
         </is>
       </c>
       <c r="H188" s="5" t="n">
-        <v>38910400</v>
+        <v>30454700</v>
       </c>
       <c r="I188" s="5" t="n">
-        <v>22388</v>
+        <v>28596</v>
       </c>
       <c r="J188" s="3" t="inlineStr">
         <is>
@@ -12267,10 +12266,10 @@
         </is>
       </c>
       <c r="K188" s="5" t="n">
-        <v>38910400</v>
+        <v>30454700</v>
       </c>
       <c r="L188" s="5" t="n">
-        <v>22388</v>
+        <v>28596</v>
       </c>
       <c r="M188" s="3" t="inlineStr">
         <is>
@@ -12286,7 +12285,7 @@
     <row r="189">
       <c r="A189" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>5座</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
@@ -12296,7 +12295,7 @@
       </c>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D189" s="3" t="inlineStr">
@@ -12305,7 +12304,7 @@
         </is>
       </c>
       <c r="E189" s="4" t="n">
-        <v>1708</v>
+        <v>1723</v>
       </c>
       <c r="F189" s="3" t="inlineStr">
         <is>
@@ -12314,14 +12313,14 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2019-02-01</t>
+          <t>2019-01-16</t>
         </is>
       </c>
       <c r="H189" s="5" t="n">
-        <v>53323000</v>
+        <v>55342040</v>
       </c>
       <c r="I189" s="5" t="n">
-        <v>31220</v>
+        <v>32120</v>
       </c>
       <c r="J189" s="3" t="inlineStr">
         <is>
@@ -12329,10 +12328,10 @@
         </is>
       </c>
       <c r="K189" s="5" t="n">
-        <v>53323000</v>
+        <v>55342040</v>
       </c>
       <c r="L189" s="5" t="n">
-        <v>31220</v>
+        <v>32120</v>
       </c>
       <c r="M189" s="3" t="inlineStr">
         <is>
@@ -12348,17 +12347,17 @@
     <row r="190">
       <c r="A190" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>5座</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C190" s="3" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D190" s="3" t="inlineStr">
@@ -12367,7 +12366,7 @@
         </is>
       </c>
       <c r="E190" s="4" t="n">
-        <v>1428</v>
+        <v>1316</v>
       </c>
       <c r="F190" s="3" t="inlineStr">
         <is>
@@ -12376,14 +12375,14 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2016-04-20</t>
+          <t>2016-04-29</t>
         </is>
       </c>
       <c r="H190" s="5" t="n">
-        <v>32273500</v>
+        <v>29191600</v>
       </c>
       <c r="I190" s="5" t="n">
-        <v>22600</v>
+        <v>22182</v>
       </c>
       <c r="J190" s="3" t="inlineStr">
         <is>
@@ -12391,10 +12390,10 @@
         </is>
       </c>
       <c r="K190" s="5" t="n">
-        <v>32273500</v>
+        <v>29191600</v>
       </c>
       <c r="L190" s="5" t="n">
-        <v>22600</v>
+        <v>22182</v>
       </c>
       <c r="M190" s="3" t="inlineStr">
         <is>
@@ -12410,26 +12409,26 @@
     <row r="191">
       <c r="A191" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>5座</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C191" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D191" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E191" s="4" t="n">
-        <v>1237</v>
+        <v>1320</v>
       </c>
       <c r="F191" s="3" t="inlineStr">
         <is>
@@ -12438,14 +12437,14 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2016-04-20</t>
+          <t>2016-05-10</t>
         </is>
       </c>
       <c r="H191" s="5" t="n">
-        <v>28000100</v>
+        <v>30849200</v>
       </c>
       <c r="I191" s="5" t="n">
-        <v>22635</v>
+        <v>23371</v>
       </c>
       <c r="J191" s="3" t="inlineStr">
         <is>
@@ -12453,10 +12452,10 @@
         </is>
       </c>
       <c r="K191" s="5" t="n">
-        <v>28000100</v>
+        <v>30849200</v>
       </c>
       <c r="L191" s="5" t="n">
-        <v>22635</v>
+        <v>23371</v>
       </c>
       <c r="M191" s="3" t="inlineStr">
         <is>
@@ -12472,7 +12471,7 @@
     <row r="192">
       <c r="A192" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>5座</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
@@ -12482,16 +12481,16 @@
       </c>
       <c r="C192" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D192" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E192" s="4" t="n">
-        <v>1738</v>
+        <v>1160</v>
       </c>
       <c r="F192" s="3" t="inlineStr">
         <is>
@@ -12500,14 +12499,14 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2016-04-28</t>
+          <t>2016-05-16</t>
         </is>
       </c>
       <c r="H192" s="5" t="n">
-        <v>37898700</v>
+        <v>28749300</v>
       </c>
       <c r="I192" s="5" t="n">
-        <v>21806</v>
+        <v>24784</v>
       </c>
       <c r="J192" s="3" t="inlineStr">
         <is>
@@ -12515,10 +12514,10 @@
         </is>
       </c>
       <c r="K192" s="5" t="n">
-        <v>37898700</v>
+        <v>28749300</v>
       </c>
       <c r="L192" s="5" t="n">
-        <v>21806</v>
+        <v>24784</v>
       </c>
       <c r="M192" s="3" t="inlineStr">
         <is>
@@ -12534,7 +12533,7 @@
     <row r="193">
       <c r="A193" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>5座</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
@@ -12544,7 +12543,7 @@
       </c>
       <c r="C193" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D193" s="3" t="inlineStr">
@@ -12553,7 +12552,7 @@
         </is>
       </c>
       <c r="E193" s="4" t="n">
-        <v>1708</v>
+        <v>1723</v>
       </c>
       <c r="F193" s="3" t="inlineStr">
         <is>
@@ -12562,14 +12561,14 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2019-01-11</t>
+          <t>2019-01-04</t>
         </is>
       </c>
       <c r="H193" s="5" t="n">
-        <v>51885000</v>
+        <v>48712000</v>
       </c>
       <c r="I193" s="5" t="n">
-        <v>30378</v>
+        <v>28272</v>
       </c>
       <c r="J193" s="3" t="inlineStr">
         <is>
@@ -12577,10 +12576,10 @@
         </is>
       </c>
       <c r="K193" s="5" t="n">
-        <v>51885000</v>
+        <v>48712000</v>
       </c>
       <c r="L193" s="5" t="n">
-        <v>30378</v>
+        <v>28272</v>
       </c>
       <c r="M193" s="3" t="inlineStr">
         <is>
@@ -12596,17 +12595,17 @@
     <row r="194">
       <c r="A194" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>5座</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C194" s="3" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D194" s="3" t="inlineStr">
@@ -12615,7 +12614,7 @@
         </is>
       </c>
       <c r="E194" s="4" t="n">
-        <v>1428</v>
+        <v>1316</v>
       </c>
       <c r="F194" s="3" t="inlineStr">
         <is>
@@ -12624,14 +12623,14 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2016-04-20</t>
+          <t>2016-04-28</t>
         </is>
       </c>
       <c r="H194" s="5" t="n">
-        <v>24990300</v>
+        <v>29016400</v>
       </c>
       <c r="I194" s="5" t="n">
-        <v>17500</v>
+        <v>22049</v>
       </c>
       <c r="J194" s="3" t="inlineStr">
         <is>
@@ -12639,10 +12638,10 @@
         </is>
       </c>
       <c r="K194" s="5" t="n">
-        <v>24990300</v>
+        <v>29016400</v>
       </c>
       <c r="L194" s="5" t="n">
-        <v>17500</v>
+        <v>22049</v>
       </c>
       <c r="M194" s="3" t="inlineStr">
         <is>
@@ -12658,26 +12657,26 @@
     <row r="195">
       <c r="A195" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>5座</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C195" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D195" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E195" s="4" t="n">
-        <v>1237</v>
+        <v>1320</v>
       </c>
       <c r="F195" s="3" t="inlineStr">
         <is>
@@ -12686,14 +12685,14 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2016-04-19</t>
+          <t>2016-04-15</t>
         </is>
       </c>
       <c r="H195" s="5" t="n">
-        <v>20820400</v>
+        <v>30664100</v>
       </c>
       <c r="I195" s="5" t="n">
-        <v>16831</v>
+        <v>23230</v>
       </c>
       <c r="J195" s="3" t="inlineStr">
         <is>
@@ -12701,10 +12700,10 @@
         </is>
       </c>
       <c r="K195" s="5" t="n">
-        <v>20820400</v>
+        <v>30664100</v>
       </c>
       <c r="L195" s="5" t="n">
-        <v>16831</v>
+        <v>23230</v>
       </c>
       <c r="M195" s="3" t="inlineStr">
         <is>
@@ -12720,7 +12719,7 @@
     <row r="196">
       <c r="A196" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>5座</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
@@ -12730,16 +12729,16 @@
       </c>
       <c r="C196" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D196" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E196" s="4" t="n">
-        <v>1738</v>
+        <v>1160</v>
       </c>
       <c r="F196" s="3" t="inlineStr">
         <is>
@@ -12748,14 +12747,14 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2016-04-20</t>
+          <t>2016-05-16</t>
         </is>
       </c>
       <c r="H196" s="5" t="n">
-        <v>31266400</v>
+        <v>23286900</v>
       </c>
       <c r="I196" s="5" t="n">
-        <v>17990</v>
+        <v>20075</v>
       </c>
       <c r="J196" s="3" t="inlineStr">
         <is>
@@ -12763,10 +12762,10 @@
         </is>
       </c>
       <c r="K196" s="5" t="n">
-        <v>31266400</v>
+        <v>23286900</v>
       </c>
       <c r="L196" s="5" t="n">
-        <v>17990</v>
+        <v>20075</v>
       </c>
       <c r="M196" s="3" t="inlineStr">
         <is>
@@ -12782,7 +12781,7 @@
     <row r="197">
       <c r="A197" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>5座</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
@@ -12792,7 +12791,7 @@
       </c>
       <c r="C197" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D197" s="3" t="inlineStr">
@@ -12801,7 +12800,7 @@
         </is>
       </c>
       <c r="E197" s="4" t="n">
-        <v>1708</v>
+        <v>1723</v>
       </c>
       <c r="F197" s="3" t="inlineStr">
         <is>
@@ -12810,14 +12809,14 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>2019-01-15</t>
+          <t>2016-05-13</t>
         </is>
       </c>
       <c r="H197" s="5" t="n">
-        <v>50488888</v>
+        <v>38956200</v>
       </c>
       <c r="I197" s="5" t="n">
-        <v>29560</v>
+        <v>22610</v>
       </c>
       <c r="J197" s="3" t="inlineStr">
         <is>
@@ -12825,10 +12824,10 @@
         </is>
       </c>
       <c r="K197" s="5" t="n">
-        <v>50488888</v>
+        <v>38956200</v>
       </c>
       <c r="L197" s="5" t="n">
-        <v>29560</v>
+        <v>22610</v>
       </c>
       <c r="M197" s="3" t="inlineStr">
         <is>
@@ -12844,17 +12843,17 @@
     <row r="198">
       <c r="A198" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>5座</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C198" s="3" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D198" s="3" t="inlineStr">
@@ -12863,7 +12862,7 @@
         </is>
       </c>
       <c r="E198" s="4" t="n">
-        <v>1412</v>
+        <v>1221</v>
       </c>
       <c r="F198" s="3" t="inlineStr">
         <is>
@@ -12872,14 +12871,14 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2016-04-22</t>
+          <t>2016-04-27</t>
         </is>
       </c>
       <c r="H198" s="5" t="n">
-        <v>24209100</v>
+        <v>22105600</v>
       </c>
       <c r="I198" s="5" t="n">
-        <v>17145</v>
+        <v>18105</v>
       </c>
       <c r="J198" s="3" t="inlineStr">
         <is>
@@ -12887,10 +12886,10 @@
         </is>
       </c>
       <c r="K198" s="5" t="n">
-        <v>24209100</v>
+        <v>22105600</v>
       </c>
       <c r="L198" s="5" t="n">
-        <v>17145</v>
+        <v>18105</v>
       </c>
       <c r="M198" s="3" t="inlineStr">
         <is>
@@ -12906,26 +12905,26 @@
     <row r="199">
       <c r="A199" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>5座</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C199" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D199" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E199" s="4" t="n">
-        <v>1221</v>
+        <v>1320</v>
       </c>
       <c r="F199" s="3" t="inlineStr">
         <is>
@@ -12934,14 +12933,14 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2016-04-22</t>
+          <t>2016-05-19</t>
         </is>
       </c>
       <c r="H199" s="5" t="n">
-        <v>21984300</v>
+        <v>25293900</v>
       </c>
       <c r="I199" s="5" t="n">
-        <v>18005</v>
+        <v>19162</v>
       </c>
       <c r="J199" s="3" t="inlineStr">
         <is>
@@ -12949,10 +12948,10 @@
         </is>
       </c>
       <c r="K199" s="5" t="n">
-        <v>21984300</v>
+        <v>25293900</v>
       </c>
       <c r="L199" s="5" t="n">
-        <v>18005</v>
+        <v>19162</v>
       </c>
       <c r="M199" s="3" t="inlineStr">
         <is>
@@ -12968,7 +12967,7 @@
     <row r="200">
       <c r="A200" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>5座</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
@@ -12978,16 +12977,16 @@
       </c>
       <c r="C200" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D200" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E200" s="4" t="n">
-        <v>1722</v>
+        <v>1143</v>
       </c>
       <c r="F200" s="3" t="inlineStr">
         <is>
@@ -12996,14 +12995,14 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2016-05-18</t>
+          <t>2016-05-16</t>
         </is>
       </c>
       <c r="H200" s="5" t="n">
-        <v>30613100</v>
+        <v>21729500</v>
       </c>
       <c r="I200" s="5" t="n">
-        <v>17778</v>
+        <v>19011</v>
       </c>
       <c r="J200" s="3" t="inlineStr">
         <is>
@@ -13011,10 +13010,10 @@
         </is>
       </c>
       <c r="K200" s="5" t="n">
-        <v>30613100</v>
+        <v>21729500</v>
       </c>
       <c r="L200" s="5" t="n">
-        <v>17778</v>
+        <v>19011</v>
       </c>
       <c r="M200" s="3" t="inlineStr">
         <is>
@@ -13030,7 +13029,7 @@
     <row r="201">
       <c r="A201" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>5座</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr">
@@ -13040,16 +13039,16 @@
       </c>
       <c r="C201" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D201" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E201" s="4" t="n">
-        <v>1691</v>
+        <v>1723</v>
       </c>
       <c r="F201" s="3" t="inlineStr">
         <is>
@@ -13058,14 +13057,14 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2016-05-04</t>
+          <t>2016-05-16</t>
         </is>
       </c>
       <c r="H201" s="5" t="n">
-        <v>31662800</v>
+        <v>39094700</v>
       </c>
       <c r="I201" s="5" t="n">
-        <v>18724</v>
+        <v>22690</v>
       </c>
       <c r="J201" s="3" t="inlineStr">
         <is>
@@ -13073,10 +13072,10 @@
         </is>
       </c>
       <c r="K201" s="5" t="n">
-        <v>31662800</v>
+        <v>39094700</v>
       </c>
       <c r="L201" s="5" t="n">
-        <v>18724</v>
+        <v>22690</v>
       </c>
       <c r="M201" s="3" t="inlineStr">
         <is>
@@ -13097,12 +13096,12 @@
       </c>
       <c r="B202" s="3" t="inlineStr">
         <is>
-          <t>25&amp;26</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C202" s="3" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D202" s="3" t="inlineStr">
@@ -13111,7 +13110,7 @@
         </is>
       </c>
       <c r="E202" s="4" t="n">
-        <v>2187</v>
+        <v>1300</v>
       </c>
       <c r="F202" s="3" t="inlineStr">
         <is>
@@ -13120,14 +13119,14 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2016-04-15</t>
+          <t>2016-05-17</t>
         </is>
       </c>
       <c r="H202" s="5" t="n">
-        <v>151799500</v>
+        <v>25059000</v>
       </c>
       <c r="I202" s="5" t="n">
-        <v>69410</v>
+        <v>19276</v>
       </c>
       <c r="J202" s="3" t="inlineStr">
         <is>
@@ -13135,10 +13134,10 @@
         </is>
       </c>
       <c r="K202" s="5" t="n">
-        <v>151799500</v>
+        <v>25059000</v>
       </c>
       <c r="L202" s="5" t="n">
-        <v>69410</v>
+        <v>19276</v>
       </c>
       <c r="M202" s="3" t="inlineStr">
         <is>
@@ -13159,12 +13158,12 @@
       </c>
       <c r="B203" s="3" t="inlineStr">
         <is>
-          <t>25&amp;26</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C203" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D203" s="3" t="inlineStr">
@@ -13173,7 +13172,7 @@
         </is>
       </c>
       <c r="E203" s="4" t="n">
-        <v>2130</v>
+        <v>1150</v>
       </c>
       <c r="F203" s="3" t="inlineStr">
         <is>
@@ -13182,14 +13181,14 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2016-04-22</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="H203" s="5" t="n">
-        <v>91650000</v>
+        <v>36231000</v>
       </c>
       <c r="I203" s="5" t="n">
-        <v>43028</v>
+        <v>31505</v>
       </c>
       <c r="J203" s="3" t="inlineStr">
         <is>
@@ -13197,10 +13196,10 @@
         </is>
       </c>
       <c r="K203" s="5" t="n">
-        <v>91650000</v>
+        <v>36231000</v>
       </c>
       <c r="L203" s="5" t="n">
-        <v>43028</v>
+        <v>31505</v>
       </c>
       <c r="M203" s="3" t="inlineStr">
         <is>
@@ -13221,21 +13220,21 @@
       </c>
       <c r="B204" s="3" t="inlineStr">
         <is>
-          <t>25&amp;26</t>
+          <t>3&amp;4</t>
         </is>
       </c>
       <c r="C204" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D204" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E204" s="4" t="n">
-        <v>2733</v>
+        <v>1970</v>
       </c>
       <c r="F204" s="3" t="inlineStr">
         <is>
@@ -13244,14 +13243,14 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2019-02-15</t>
+          <t>2016-05-19</t>
         </is>
       </c>
       <c r="H204" s="5" t="n">
-        <v>213912000</v>
+        <v>62774600</v>
       </c>
       <c r="I204" s="5" t="n">
-        <v>78270</v>
+        <v>31865</v>
       </c>
       <c r="J204" s="3" t="inlineStr">
         <is>
@@ -13259,10 +13258,10 @@
         </is>
       </c>
       <c r="K204" s="5" t="n">
-        <v>213912000</v>
+        <v>62774600</v>
       </c>
       <c r="L204" s="5" t="n">
-        <v>78270</v>
+        <v>31865</v>
       </c>
       <c r="M204" s="3" t="inlineStr">
         <is>
@@ -13283,12 +13282,12 @@
       </c>
       <c r="B205" s="3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>3&amp;4</t>
         </is>
       </c>
       <c r="C205" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D205" s="3" t="inlineStr">
@@ -13297,7 +13296,7 @@
         </is>
       </c>
       <c r="E205" s="4" t="n">
-        <v>2044</v>
+        <v>1929</v>
       </c>
       <c r="F205" s="3" t="inlineStr">
         <is>
@@ -13306,14 +13305,14 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>2020-02-21</t>
+          <t>2016-04-08</t>
         </is>
       </c>
       <c r="H205" s="5" t="n">
-        <v>128601000</v>
+        <v>45931400</v>
       </c>
       <c r="I205" s="5" t="n">
-        <v>62916</v>
+        <v>23811</v>
       </c>
       <c r="J205" s="3" t="inlineStr">
         <is>
@@ -13321,10 +13320,10 @@
         </is>
       </c>
       <c r="K205" s="5" t="n">
-        <v>128601000</v>
+        <v>45931400</v>
       </c>
       <c r="L205" s="5" t="n">
-        <v>62916</v>
+        <v>23811</v>
       </c>
       <c r="M205" s="3" t="inlineStr">
         <is>
@@ -13332,4222 +13331,6 @@
         </is>
       </c>
       <c r="N205" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" s="3" t="inlineStr">
-        <is>
-          <t>5座</t>
-        </is>
-      </c>
-      <c r="B206" s="3" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="C206" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D206" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E206" s="4" t="n">
-        <v>1316</v>
-      </c>
-      <c r="F206" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G206" s="3" t="inlineStr">
-        <is>
-          <t>2016-04-27</t>
-        </is>
-      </c>
-      <c r="H206" s="5" t="n">
-        <v>39981600</v>
-      </c>
-      <c r="I206" s="5" t="n">
-        <v>30381</v>
-      </c>
-      <c r="J206" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K206" s="5" t="n">
-        <v>39981600</v>
-      </c>
-      <c r="L206" s="5" t="n">
-        <v>30381</v>
-      </c>
-      <c r="M206" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N206" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" s="3" t="inlineStr">
-        <is>
-          <t>5座</t>
-        </is>
-      </c>
-      <c r="B207" s="3" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="C207" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D207" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E207" s="4" t="n">
-        <v>1320</v>
-      </c>
-      <c r="F207" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G207" s="3" t="inlineStr">
-        <is>
-          <t>2016-05-09</t>
-        </is>
-      </c>
-      <c r="H207" s="5" t="n">
-        <v>43077300</v>
-      </c>
-      <c r="I207" s="5" t="n">
-        <v>32634</v>
-      </c>
-      <c r="J207" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K207" s="5" t="n">
-        <v>43077300</v>
-      </c>
-      <c r="L207" s="5" t="n">
-        <v>32634</v>
-      </c>
-      <c r="M207" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N207" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" s="3" t="inlineStr">
-        <is>
-          <t>5座</t>
-        </is>
-      </c>
-      <c r="B208" s="3" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="C208" s="3" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D208" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E208" s="4" t="n">
-        <v>1160</v>
-      </c>
-      <c r="F208" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G208" s="3" t="inlineStr">
-        <is>
-          <t>2016-05-11</t>
-        </is>
-      </c>
-      <c r="H208" s="5" t="n">
-        <v>38618900</v>
-      </c>
-      <c r="I208" s="5" t="n">
-        <v>33292</v>
-      </c>
-      <c r="J208" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K208" s="5" t="n">
-        <v>38618900</v>
-      </c>
-      <c r="L208" s="5" t="n">
-        <v>33292</v>
-      </c>
-      <c r="M208" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N208" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" s="3" t="inlineStr">
-        <is>
-          <t>5座</t>
-        </is>
-      </c>
-      <c r="B209" s="3" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="C209" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D209" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E209" s="4" t="n">
-        <v>1723</v>
-      </c>
-      <c r="F209" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G209" s="3" t="inlineStr">
-        <is>
-          <t>2016-04-28</t>
-        </is>
-      </c>
-      <c r="H209" s="5" t="n">
-        <v>70738800</v>
-      </c>
-      <c r="I209" s="5" t="n">
-        <v>41056</v>
-      </c>
-      <c r="J209" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K209" s="5" t="n">
-        <v>70738800</v>
-      </c>
-      <c r="L209" s="5" t="n">
-        <v>41056</v>
-      </c>
-      <c r="M209" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N209" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" s="3" t="inlineStr">
-        <is>
-          <t>5座</t>
-        </is>
-      </c>
-      <c r="B210" s="3" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="C210" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D210" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E210" s="4" t="n">
-        <v>1221</v>
-      </c>
-      <c r="F210" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G210" s="3" t="inlineStr">
-        <is>
-          <t>2016-05-05</t>
-        </is>
-      </c>
-      <c r="H210" s="5" t="n">
-        <v>39468600</v>
-      </c>
-      <c r="I210" s="5" t="n">
-        <v>32325</v>
-      </c>
-      <c r="J210" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K210" s="5" t="n">
-        <v>39468600</v>
-      </c>
-      <c r="L210" s="5" t="n">
-        <v>32325</v>
-      </c>
-      <c r="M210" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N210" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" s="3" t="inlineStr">
-        <is>
-          <t>5座</t>
-        </is>
-      </c>
-      <c r="B211" s="3" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="C211" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D211" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E211" s="4" t="n">
-        <v>1320</v>
-      </c>
-      <c r="F211" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G211" s="3" t="inlineStr">
-        <is>
-          <t>2016-05-13</t>
-        </is>
-      </c>
-      <c r="H211" s="5" t="n">
-        <v>42946400</v>
-      </c>
-      <c r="I211" s="5" t="n">
-        <v>32535</v>
-      </c>
-      <c r="J211" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K211" s="5" t="n">
-        <v>42946400</v>
-      </c>
-      <c r="L211" s="5" t="n">
-        <v>32535</v>
-      </c>
-      <c r="M211" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N211" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" s="3" t="inlineStr">
-        <is>
-          <t>5座</t>
-        </is>
-      </c>
-      <c r="B212" s="3" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="C212" s="3" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D212" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E212" s="4" t="n">
-        <v>1160</v>
-      </c>
-      <c r="F212" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G212" s="3" t="inlineStr">
-        <is>
-          <t>2016-05-11</t>
-        </is>
-      </c>
-      <c r="H212" s="5" t="n">
-        <v>38407700</v>
-      </c>
-      <c r="I212" s="5" t="n">
-        <v>33110</v>
-      </c>
-      <c r="J212" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K212" s="5" t="n">
-        <v>38407700</v>
-      </c>
-      <c r="L212" s="5" t="n">
-        <v>33110</v>
-      </c>
-      <c r="M212" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N212" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" s="3" t="inlineStr">
-        <is>
-          <t>5座</t>
-        </is>
-      </c>
-      <c r="B213" s="3" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="C213" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D213" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E213" s="4" t="n">
-        <v>1723</v>
-      </c>
-      <c r="F213" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G213" s="3" t="inlineStr">
-        <is>
-          <t>2019-01-31</t>
-        </is>
-      </c>
-      <c r="H213" s="5" t="n">
-        <v>71444000</v>
-      </c>
-      <c r="I213" s="5" t="n">
-        <v>41465</v>
-      </c>
-      <c r="J213" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K213" s="5" t="n">
-        <v>71444000</v>
-      </c>
-      <c r="L213" s="5" t="n">
-        <v>41465</v>
-      </c>
-      <c r="M213" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N213" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" s="3" t="inlineStr">
-        <is>
-          <t>5座</t>
-        </is>
-      </c>
-      <c r="B214" s="3" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="C214" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D214" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E214" s="4" t="n">
-        <v>1221</v>
-      </c>
-      <c r="F214" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G214" s="3" t="inlineStr">
-        <is>
-          <t>2016-04-29</t>
-        </is>
-      </c>
-      <c r="H214" s="5" t="n">
-        <v>38962000</v>
-      </c>
-      <c r="I214" s="5" t="n">
-        <v>31910</v>
-      </c>
-      <c r="J214" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K214" s="5" t="n">
-        <v>38962000</v>
-      </c>
-      <c r="L214" s="5" t="n">
-        <v>31910</v>
-      </c>
-      <c r="M214" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N214" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" s="3" t="inlineStr">
-        <is>
-          <t>5座</t>
-        </is>
-      </c>
-      <c r="B215" s="3" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="C215" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D215" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E215" s="4" t="n">
-        <v>1320</v>
-      </c>
-      <c r="F215" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G215" s="3" t="inlineStr">
-        <is>
-          <t>2016-05-12</t>
-        </is>
-      </c>
-      <c r="H215" s="5" t="n">
-        <v>42732700</v>
-      </c>
-      <c r="I215" s="5" t="n">
-        <v>32373</v>
-      </c>
-      <c r="J215" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K215" s="5" t="n">
-        <v>42732700</v>
-      </c>
-      <c r="L215" s="5" t="n">
-        <v>32373</v>
-      </c>
-      <c r="M215" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N215" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" s="3" t="inlineStr">
-        <is>
-          <t>5座</t>
-        </is>
-      </c>
-      <c r="B216" s="3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="C216" s="3" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D216" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E216" s="4" t="n">
-        <v>1160</v>
-      </c>
-      <c r="F216" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G216" s="3" t="inlineStr">
-        <is>
-          <t>2016-05-12</t>
-        </is>
-      </c>
-      <c r="H216" s="5" t="n">
-        <v>38197600</v>
-      </c>
-      <c r="I216" s="5" t="n">
-        <v>32929</v>
-      </c>
-      <c r="J216" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K216" s="5" t="n">
-        <v>38197600</v>
-      </c>
-      <c r="L216" s="5" t="n">
-        <v>32929</v>
-      </c>
-      <c r="M216" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N216" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" s="3" t="inlineStr">
-        <is>
-          <t>5座</t>
-        </is>
-      </c>
-      <c r="B217" s="3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="C217" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D217" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E217" s="4" t="n">
-        <v>1723</v>
-      </c>
-      <c r="F217" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G217" s="3" t="inlineStr">
-        <is>
-          <t>2019-01-15</t>
-        </is>
-      </c>
-      <c r="H217" s="5" t="n">
-        <v>63585000</v>
-      </c>
-      <c r="I217" s="5" t="n">
-        <v>36904</v>
-      </c>
-      <c r="J217" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K217" s="5" t="n">
-        <v>63585000</v>
-      </c>
-      <c r="L217" s="5" t="n">
-        <v>36904</v>
-      </c>
-      <c r="M217" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N217" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" s="3" t="inlineStr">
-        <is>
-          <t>5座</t>
-        </is>
-      </c>
-      <c r="B218" s="3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="C218" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D218" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E218" s="4" t="n">
-        <v>1316</v>
-      </c>
-      <c r="F218" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G218" s="3" t="inlineStr">
-        <is>
-          <t>2016-04-15</t>
-        </is>
-      </c>
-      <c r="H218" s="5" t="n">
-        <v>76431800</v>
-      </c>
-      <c r="I218" s="5" t="n">
-        <v>58079</v>
-      </c>
-      <c r="J218" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K218" s="5" t="n">
-        <v>76431800</v>
-      </c>
-      <c r="L218" s="5" t="n">
-        <v>58079</v>
-      </c>
-      <c r="M218" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N218" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" s="3" t="inlineStr">
-        <is>
-          <t>5座</t>
-        </is>
-      </c>
-      <c r="B219" s="3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="C219" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D219" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E219" s="4" t="n">
-        <v>1320</v>
-      </c>
-      <c r="F219" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G219" s="3" t="inlineStr">
-        <is>
-          <t>2016-04-29</t>
-        </is>
-      </c>
-      <c r="H219" s="5" t="n">
-        <v>41895500</v>
-      </c>
-      <c r="I219" s="5" t="n">
-        <v>31739</v>
-      </c>
-      <c r="J219" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K219" s="5" t="n">
-        <v>41895500</v>
-      </c>
-      <c r="L219" s="5" t="n">
-        <v>31739</v>
-      </c>
-      <c r="M219" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N219" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" s="3" t="inlineStr">
-        <is>
-          <t>5座</t>
-        </is>
-      </c>
-      <c r="B220" s="3" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="C220" s="3" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D220" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E220" s="4" t="n">
-        <v>1160</v>
-      </c>
-      <c r="F220" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G220" s="3" t="inlineStr">
-        <is>
-          <t>2016-04-15</t>
-        </is>
-      </c>
-      <c r="H220" s="5" t="n">
-        <v>76431800</v>
-      </c>
-      <c r="I220" s="5" t="n">
-        <v>65889</v>
-      </c>
-      <c r="J220" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K220" s="5" t="n">
-        <v>76431800</v>
-      </c>
-      <c r="L220" s="5" t="n">
-        <v>65889</v>
-      </c>
-      <c r="M220" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N220" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" s="3" t="inlineStr">
-        <is>
-          <t>5座</t>
-        </is>
-      </c>
-      <c r="B221" s="3" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="C221" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D221" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E221" s="4" t="n">
-        <v>1723</v>
-      </c>
-      <c r="F221" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G221" s="3" t="inlineStr">
-        <is>
-          <t>2024-06-24</t>
-        </is>
-      </c>
-      <c r="H221" s="5" t="n">
-        <v>53423338</v>
-      </c>
-      <c r="I221" s="5" t="n">
-        <v>31006</v>
-      </c>
-      <c r="J221" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K221" s="5" t="n">
-        <v>53423338</v>
-      </c>
-      <c r="L221" s="5" t="n">
-        <v>31006</v>
-      </c>
-      <c r="M221" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N221" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" s="3" t="inlineStr">
-        <is>
-          <t>5座</t>
-        </is>
-      </c>
-      <c r="B222" s="3" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="C222" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D222" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E222" s="4" t="n">
-        <v>1316</v>
-      </c>
-      <c r="F222" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G222" s="3" t="inlineStr">
-        <is>
-          <t>2016-05-09</t>
-        </is>
-      </c>
-      <c r="H222" s="5" t="n">
-        <v>37968500</v>
-      </c>
-      <c r="I222" s="5" t="n">
-        <v>28851</v>
-      </c>
-      <c r="J222" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K222" s="5" t="n">
-        <v>37968500</v>
-      </c>
-      <c r="L222" s="5" t="n">
-        <v>28851</v>
-      </c>
-      <c r="M222" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N222" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" s="3" t="inlineStr">
-        <is>
-          <t>5座</t>
-        </is>
-      </c>
-      <c r="B223" s="3" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="C223" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D223" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E223" s="4" t="n">
-        <v>1320</v>
-      </c>
-      <c r="F223" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G223" s="3" t="inlineStr">
-        <is>
-          <t>2016-05-17</t>
-        </is>
-      </c>
-      <c r="H223" s="5" t="n">
-        <v>41964900</v>
-      </c>
-      <c r="I223" s="5" t="n">
-        <v>31792</v>
-      </c>
-      <c r="J223" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K223" s="5" t="n">
-        <v>41964900</v>
-      </c>
-      <c r="L223" s="5" t="n">
-        <v>31792</v>
-      </c>
-      <c r="M223" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N223" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" s="3" t="inlineStr">
-        <is>
-          <t>5座</t>
-        </is>
-      </c>
-      <c r="B224" s="3" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="C224" s="3" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D224" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E224" s="4" t="n">
-        <v>1160</v>
-      </c>
-      <c r="F224" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G224" s="3" t="inlineStr">
-        <is>
-          <t>2016-05-18</t>
-        </is>
-      </c>
-      <c r="H224" s="5" t="n">
-        <v>37816800</v>
-      </c>
-      <c r="I224" s="5" t="n">
-        <v>32601</v>
-      </c>
-      <c r="J224" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K224" s="5" t="n">
-        <v>37816800</v>
-      </c>
-      <c r="L224" s="5" t="n">
-        <v>32601</v>
-      </c>
-      <c r="M224" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N224" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" s="3" t="inlineStr">
-        <is>
-          <t>5座</t>
-        </is>
-      </c>
-      <c r="B225" s="3" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="C225" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D225" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E225" s="4" t="n">
-        <v>1723</v>
-      </c>
-      <c r="F225" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G225" s="3" t="inlineStr">
-        <is>
-          <t>2019-01-07</t>
-        </is>
-      </c>
-      <c r="H225" s="5" t="n">
-        <v>62677000</v>
-      </c>
-      <c r="I225" s="5" t="n">
-        <v>36377</v>
-      </c>
-      <c r="J225" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K225" s="5" t="n">
-        <v>62677000</v>
-      </c>
-      <c r="L225" s="5" t="n">
-        <v>36377</v>
-      </c>
-      <c r="M225" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N225" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" s="3" t="inlineStr">
-        <is>
-          <t>5座</t>
-        </is>
-      </c>
-      <c r="B226" s="3" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="C226" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D226" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E226" s="4" t="n">
-        <v>1316</v>
-      </c>
-      <c r="F226" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G226" s="3" t="inlineStr">
-        <is>
-          <t>2016-05-09</t>
-        </is>
-      </c>
-      <c r="H226" s="5" t="n">
-        <v>37592500</v>
-      </c>
-      <c r="I226" s="5" t="n">
-        <v>28566</v>
-      </c>
-      <c r="J226" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K226" s="5" t="n">
-        <v>37592500</v>
-      </c>
-      <c r="L226" s="5" t="n">
-        <v>28566</v>
-      </c>
-      <c r="M226" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N226" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" s="3" t="inlineStr">
-        <is>
-          <t>5座</t>
-        </is>
-      </c>
-      <c r="B227" s="3" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="C227" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D227" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E227" s="4" t="n">
-        <v>1320</v>
-      </c>
-      <c r="F227" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G227" s="3" t="inlineStr">
-        <is>
-          <t>2016-05-13</t>
-        </is>
-      </c>
-      <c r="H227" s="5" t="n">
-        <v>41549400</v>
-      </c>
-      <c r="I227" s="5" t="n">
-        <v>31477</v>
-      </c>
-      <c r="J227" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K227" s="5" t="n">
-        <v>41549400</v>
-      </c>
-      <c r="L227" s="5" t="n">
-        <v>31477</v>
-      </c>
-      <c r="M227" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N227" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" s="3" t="inlineStr">
-        <is>
-          <t>5座</t>
-        </is>
-      </c>
-      <c r="B228" s="3" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="C228" s="3" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D228" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E228" s="4" t="n">
-        <v>1160</v>
-      </c>
-      <c r="F228" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G228" s="3" t="inlineStr">
-        <is>
-          <t>2016-05-13</t>
-        </is>
-      </c>
-      <c r="H228" s="5" t="n">
-        <v>36529200</v>
-      </c>
-      <c r="I228" s="5" t="n">
-        <v>31491</v>
-      </c>
-      <c r="J228" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K228" s="5" t="n">
-        <v>36529200</v>
-      </c>
-      <c r="L228" s="5" t="n">
-        <v>31491</v>
-      </c>
-      <c r="M228" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N228" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" s="3" t="inlineStr">
-        <is>
-          <t>5座</t>
-        </is>
-      </c>
-      <c r="B229" s="3" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="C229" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D229" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E229" s="4" t="n">
-        <v>1723</v>
-      </c>
-      <c r="F229" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G229" s="3" t="inlineStr">
-        <is>
-          <t>2019-01-17</t>
-        </is>
-      </c>
-      <c r="H229" s="5" t="n">
-        <v>64512640</v>
-      </c>
-      <c r="I229" s="5" t="n">
-        <v>37442</v>
-      </c>
-      <c r="J229" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K229" s="5" t="n">
-        <v>64512640</v>
-      </c>
-      <c r="L229" s="5" t="n">
-        <v>37442</v>
-      </c>
-      <c r="M229" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N229" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" s="3" t="inlineStr">
-        <is>
-          <t>5座</t>
-        </is>
-      </c>
-      <c r="B230" s="3" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="C230" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D230" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E230" s="4" t="n">
-        <v>1221</v>
-      </c>
-      <c r="F230" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G230" s="3" t="inlineStr">
-        <is>
-          <t>2016-05-17</t>
-        </is>
-      </c>
-      <c r="H230" s="5" t="n">
-        <v>37000500</v>
-      </c>
-      <c r="I230" s="5" t="n">
-        <v>30303</v>
-      </c>
-      <c r="J230" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K230" s="5" t="n">
-        <v>37000500</v>
-      </c>
-      <c r="L230" s="5" t="n">
-        <v>30303</v>
-      </c>
-      <c r="M230" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N230" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" s="3" t="inlineStr">
-        <is>
-          <t>5座</t>
-        </is>
-      </c>
-      <c r="B231" s="3" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="C231" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D231" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E231" s="4" t="n">
-        <v>1320</v>
-      </c>
-      <c r="F231" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G231" s="3" t="inlineStr">
-        <is>
-          <t>2016-05-05</t>
-        </is>
-      </c>
-      <c r="H231" s="5" t="n">
-        <v>40105600</v>
-      </c>
-      <c r="I231" s="5" t="n">
-        <v>30383</v>
-      </c>
-      <c r="J231" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K231" s="5" t="n">
-        <v>40105600</v>
-      </c>
-      <c r="L231" s="5" t="n">
-        <v>30383</v>
-      </c>
-      <c r="M231" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N231" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" s="3" t="inlineStr">
-        <is>
-          <t>5座</t>
-        </is>
-      </c>
-      <c r="B232" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="C232" s="3" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D232" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E232" s="4" t="n">
-        <v>1160</v>
-      </c>
-      <c r="F232" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G232" s="3" t="inlineStr">
-        <is>
-          <t>2016-05-16</t>
-        </is>
-      </c>
-      <c r="H232" s="5" t="n">
-        <v>35396400</v>
-      </c>
-      <c r="I232" s="5" t="n">
-        <v>30514</v>
-      </c>
-      <c r="J232" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K232" s="5" t="n">
-        <v>35396400</v>
-      </c>
-      <c r="L232" s="5" t="n">
-        <v>30514</v>
-      </c>
-      <c r="M232" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N232" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" s="3" t="inlineStr">
-        <is>
-          <t>5座</t>
-        </is>
-      </c>
-      <c r="B233" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="C233" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D233" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E233" s="4" t="n">
-        <v>1723</v>
-      </c>
-      <c r="F233" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G233" s="3" t="inlineStr">
-        <is>
-          <t>2019-01-17</t>
-        </is>
-      </c>
-      <c r="H233" s="5" t="n">
-        <v>68018820</v>
-      </c>
-      <c r="I233" s="5" t="n">
-        <v>39477</v>
-      </c>
-      <c r="J233" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K233" s="5" t="n">
-        <v>68018820</v>
-      </c>
-      <c r="L233" s="5" t="n">
-        <v>39477</v>
-      </c>
-      <c r="M233" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N233" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" s="3" t="inlineStr">
-        <is>
-          <t>5座</t>
-        </is>
-      </c>
-      <c r="B234" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="C234" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D234" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E234" s="4" t="n">
-        <v>1316</v>
-      </c>
-      <c r="F234" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G234" s="3" t="inlineStr">
-        <is>
-          <t>2016-05-13</t>
-        </is>
-      </c>
-      <c r="H234" s="5" t="n">
-        <v>36525700</v>
-      </c>
-      <c r="I234" s="5" t="n">
-        <v>27755</v>
-      </c>
-      <c r="J234" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K234" s="5" t="n">
-        <v>36525700</v>
-      </c>
-      <c r="L234" s="5" t="n">
-        <v>27755</v>
-      </c>
-      <c r="M234" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N234" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" s="3" t="inlineStr">
-        <is>
-          <t>5座</t>
-        </is>
-      </c>
-      <c r="B235" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="C235" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D235" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E235" s="4" t="n">
-        <v>1320</v>
-      </c>
-      <c r="F235" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G235" s="3" t="inlineStr">
-        <is>
-          <t>2016-05-06</t>
-        </is>
-      </c>
-      <c r="H235" s="5" t="n">
-        <v>39396400</v>
-      </c>
-      <c r="I235" s="5" t="n">
-        <v>29846</v>
-      </c>
-      <c r="J235" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K235" s="5" t="n">
-        <v>39396400</v>
-      </c>
-      <c r="L235" s="5" t="n">
-        <v>29846</v>
-      </c>
-      <c r="M235" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N235" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" s="3" t="inlineStr">
-        <is>
-          <t>5座</t>
-        </is>
-      </c>
-      <c r="B236" s="3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="C236" s="3" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D236" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E236" s="4" t="n">
-        <v>1065</v>
-      </c>
-      <c r="F236" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G236" s="3" t="inlineStr">
-        <is>
-          <t>2016-05-13</t>
-        </is>
-      </c>
-      <c r="H236" s="5" t="n">
-        <v>35290300</v>
-      </c>
-      <c r="I236" s="5" t="n">
-        <v>33136</v>
-      </c>
-      <c r="J236" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K236" s="5" t="n">
-        <v>35290300</v>
-      </c>
-      <c r="L236" s="5" t="n">
-        <v>33136</v>
-      </c>
-      <c r="M236" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N236" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" s="3" t="inlineStr">
-        <is>
-          <t>5座</t>
-        </is>
-      </c>
-      <c r="B237" s="3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="C237" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D237" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E237" s="4" t="n">
-        <v>1723</v>
-      </c>
-      <c r="F237" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G237" s="3" t="inlineStr">
-        <is>
-          <t>2019-01-07</t>
-        </is>
-      </c>
-      <c r="H237" s="5" t="n">
-        <v>58143200</v>
-      </c>
-      <c r="I237" s="5" t="n">
-        <v>33745</v>
-      </c>
-      <c r="J237" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K237" s="5" t="n">
-        <v>58143200</v>
-      </c>
-      <c r="L237" s="5" t="n">
-        <v>33745</v>
-      </c>
-      <c r="M237" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N237" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" s="3" t="inlineStr">
-        <is>
-          <t>5座</t>
-        </is>
-      </c>
-      <c r="B238" s="3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="C238" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D238" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E238" s="4" t="n">
-        <v>1316</v>
-      </c>
-      <c r="F238" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G238" s="3" t="inlineStr">
-        <is>
-          <t>2016-05-17</t>
-        </is>
-      </c>
-      <c r="H238" s="5" t="n">
-        <v>36416100</v>
-      </c>
-      <c r="I238" s="5" t="n">
-        <v>27672</v>
-      </c>
-      <c r="J238" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K238" s="5" t="n">
-        <v>36416100</v>
-      </c>
-      <c r="L238" s="5" t="n">
-        <v>27672</v>
-      </c>
-      <c r="M238" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N238" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" s="3" t="inlineStr">
-        <is>
-          <t>5座</t>
-        </is>
-      </c>
-      <c r="B239" s="3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="C239" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D239" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E239" s="4" t="n">
-        <v>1320</v>
-      </c>
-      <c r="F239" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G239" s="3" t="inlineStr">
-        <is>
-          <t>2016-05-05</t>
-        </is>
-      </c>
-      <c r="H239" s="5" t="n">
-        <v>39278300</v>
-      </c>
-      <c r="I239" s="5" t="n">
-        <v>29756</v>
-      </c>
-      <c r="J239" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K239" s="5" t="n">
-        <v>39278300</v>
-      </c>
-      <c r="L239" s="5" t="n">
-        <v>29756</v>
-      </c>
-      <c r="M239" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N239" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" s="3" t="inlineStr">
-        <is>
-          <t>5座</t>
-        </is>
-      </c>
-      <c r="B240" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="C240" s="3" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D240" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E240" s="4" t="n">
-        <v>1160</v>
-      </c>
-      <c r="F240" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G240" s="3" t="inlineStr">
-        <is>
-          <t>2016-05-12</t>
-        </is>
-      </c>
-      <c r="H240" s="5" t="n">
-        <v>35007900</v>
-      </c>
-      <c r="I240" s="5" t="n">
-        <v>30179</v>
-      </c>
-      <c r="J240" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K240" s="5" t="n">
-        <v>35007900</v>
-      </c>
-      <c r="L240" s="5" t="n">
-        <v>30179</v>
-      </c>
-      <c r="M240" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N240" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" s="3" t="inlineStr">
-        <is>
-          <t>5座</t>
-        </is>
-      </c>
-      <c r="B241" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="C241" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D241" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E241" s="4" t="n">
-        <v>1723</v>
-      </c>
-      <c r="F241" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G241" s="3" t="inlineStr">
-        <is>
-          <t>2019-01-17</t>
-        </is>
-      </c>
-      <c r="H241" s="5" t="n">
-        <v>58150600</v>
-      </c>
-      <c r="I241" s="5" t="n">
-        <v>33750</v>
-      </c>
-      <c r="J241" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K241" s="5" t="n">
-        <v>58150600</v>
-      </c>
-      <c r="L241" s="5" t="n">
-        <v>33750</v>
-      </c>
-      <c r="M241" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N241" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" s="3" t="inlineStr">
-        <is>
-          <t>5座</t>
-        </is>
-      </c>
-      <c r="B242" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="C242" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D242" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E242" s="4" t="n">
-        <v>1316</v>
-      </c>
-      <c r="F242" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G242" s="3" t="inlineStr">
-        <is>
-          <t>2016-04-28</t>
-        </is>
-      </c>
-      <c r="H242" s="5" t="n">
-        <v>35760600</v>
-      </c>
-      <c r="I242" s="5" t="n">
-        <v>27174</v>
-      </c>
-      <c r="J242" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K242" s="5" t="n">
-        <v>35760600</v>
-      </c>
-      <c r="L242" s="5" t="n">
-        <v>27174</v>
-      </c>
-      <c r="M242" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N242" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" s="3" t="inlineStr">
-        <is>
-          <t>5座</t>
-        </is>
-      </c>
-      <c r="B243" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="C243" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D243" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E243" s="4" t="n">
-        <v>1320</v>
-      </c>
-      <c r="F243" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G243" s="3" t="inlineStr">
-        <is>
-          <t>2016-04-28</t>
-        </is>
-      </c>
-      <c r="H243" s="5" t="n">
-        <v>38374900</v>
-      </c>
-      <c r="I243" s="5" t="n">
-        <v>29072</v>
-      </c>
-      <c r="J243" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K243" s="5" t="n">
-        <v>38374900</v>
-      </c>
-      <c r="L243" s="5" t="n">
-        <v>29072</v>
-      </c>
-      <c r="M243" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N243" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" s="3" t="inlineStr">
-        <is>
-          <t>5座</t>
-        </is>
-      </c>
-      <c r="B244" s="3" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="C244" s="3" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D244" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E244" s="4" t="n">
-        <v>1160</v>
-      </c>
-      <c r="F244" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G244" s="3" t="inlineStr">
-        <is>
-          <t>2016-05-11</t>
-        </is>
-      </c>
-      <c r="H244" s="5" t="n">
-        <v>34031200</v>
-      </c>
-      <c r="I244" s="5" t="n">
-        <v>29337</v>
-      </c>
-      <c r="J244" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K244" s="5" t="n">
-        <v>34031200</v>
-      </c>
-      <c r="L244" s="5" t="n">
-        <v>29337</v>
-      </c>
-      <c r="M244" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N244" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" s="3" t="inlineStr">
-        <is>
-          <t>5座</t>
-        </is>
-      </c>
-      <c r="B245" s="3" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="C245" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D245" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E245" s="4" t="n">
-        <v>1723</v>
-      </c>
-      <c r="F245" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G245" s="3" t="inlineStr">
-        <is>
-          <t>2016-05-09</t>
-        </is>
-      </c>
-      <c r="H245" s="5" t="n">
-        <v>56633900</v>
-      </c>
-      <c r="I245" s="5" t="n">
-        <v>32869</v>
-      </c>
-      <c r="J245" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K245" s="5" t="n">
-        <v>56633900</v>
-      </c>
-      <c r="L245" s="5" t="n">
-        <v>32869</v>
-      </c>
-      <c r="M245" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N245" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" s="3" t="inlineStr">
-        <is>
-          <t>5座</t>
-        </is>
-      </c>
-      <c r="B246" s="3" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="C246" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D246" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E246" s="4" t="n">
-        <v>1316</v>
-      </c>
-      <c r="F246" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G246" s="3" t="inlineStr">
-        <is>
-          <t>2016-04-29</t>
-        </is>
-      </c>
-      <c r="H246" s="5" t="n">
-        <v>35117000</v>
-      </c>
-      <c r="I246" s="5" t="n">
-        <v>26685</v>
-      </c>
-      <c r="J246" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K246" s="5" t="n">
-        <v>35117000</v>
-      </c>
-      <c r="L246" s="5" t="n">
-        <v>26685</v>
-      </c>
-      <c r="M246" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N246" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" s="3" t="inlineStr">
-        <is>
-          <t>5座</t>
-        </is>
-      </c>
-      <c r="B247" s="3" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="C247" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D247" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E247" s="4" t="n">
-        <v>1320</v>
-      </c>
-      <c r="F247" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G247" s="3" t="inlineStr">
-        <is>
-          <t>2016-04-27</t>
-        </is>
-      </c>
-      <c r="H247" s="5" t="n">
-        <v>37108500</v>
-      </c>
-      <c r="I247" s="5" t="n">
-        <v>28112</v>
-      </c>
-      <c r="J247" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K247" s="5" t="n">
-        <v>37108500</v>
-      </c>
-      <c r="L247" s="5" t="n">
-        <v>28112</v>
-      </c>
-      <c r="M247" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N247" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" s="3" t="inlineStr">
-        <is>
-          <t>5座</t>
-        </is>
-      </c>
-      <c r="B248" s="3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C248" s="3" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D248" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E248" s="4" t="n">
-        <v>1065</v>
-      </c>
-      <c r="F248" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G248" s="3" t="inlineStr">
-        <is>
-          <t>2016-05-12</t>
-        </is>
-      </c>
-      <c r="H248" s="5" t="n">
-        <v>33078400</v>
-      </c>
-      <c r="I248" s="5" t="n">
-        <v>31060</v>
-      </c>
-      <c r="J248" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K248" s="5" t="n">
-        <v>33078400</v>
-      </c>
-      <c r="L248" s="5" t="n">
-        <v>31060</v>
-      </c>
-      <c r="M248" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N248" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" s="3" t="inlineStr">
-        <is>
-          <t>5座</t>
-        </is>
-      </c>
-      <c r="B249" s="3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C249" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D249" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E249" s="4" t="n">
-        <v>1723</v>
-      </c>
-      <c r="F249" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G249" s="3" t="inlineStr">
-        <is>
-          <t>2016-05-10</t>
-        </is>
-      </c>
-      <c r="H249" s="5" t="n">
-        <v>54481700</v>
-      </c>
-      <c r="I249" s="5" t="n">
-        <v>31620</v>
-      </c>
-      <c r="J249" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K249" s="5" t="n">
-        <v>54481700</v>
-      </c>
-      <c r="L249" s="5" t="n">
-        <v>31620</v>
-      </c>
-      <c r="M249" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N249" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" s="3" t="inlineStr">
-        <is>
-          <t>5座</t>
-        </is>
-      </c>
-      <c r="B250" s="3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C250" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D250" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E250" s="4" t="n">
-        <v>1221</v>
-      </c>
-      <c r="F250" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G250" s="3" t="inlineStr">
-        <is>
-          <t>2016-04-15</t>
-        </is>
-      </c>
-      <c r="H250" s="5" t="n">
-        <v>33606900</v>
-      </c>
-      <c r="I250" s="5" t="n">
-        <v>27524</v>
-      </c>
-      <c r="J250" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K250" s="5" t="n">
-        <v>33606900</v>
-      </c>
-      <c r="L250" s="5" t="n">
-        <v>27524</v>
-      </c>
-      <c r="M250" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N250" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" s="3" t="inlineStr">
-        <is>
-          <t>5座</t>
-        </is>
-      </c>
-      <c r="B251" s="3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C251" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D251" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E251" s="4" t="n">
-        <v>1320</v>
-      </c>
-      <c r="F251" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G251" s="3" t="inlineStr">
-        <is>
-          <t>2016-05-12</t>
-        </is>
-      </c>
-      <c r="H251" s="5" t="n">
-        <v>34770700</v>
-      </c>
-      <c r="I251" s="5" t="n">
-        <v>26341</v>
-      </c>
-      <c r="J251" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K251" s="5" t="n">
-        <v>34770700</v>
-      </c>
-      <c r="L251" s="5" t="n">
-        <v>26341</v>
-      </c>
-      <c r="M251" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N251" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" s="3" t="inlineStr">
-        <is>
-          <t>5座</t>
-        </is>
-      </c>
-      <c r="B252" s="3" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="C252" s="3" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D252" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E252" s="4" t="n">
-        <v>1160</v>
-      </c>
-      <c r="F252" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G252" s="3" t="inlineStr">
-        <is>
-          <t>2016-05-17</t>
-        </is>
-      </c>
-      <c r="H252" s="5" t="n">
-        <v>31556800</v>
-      </c>
-      <c r="I252" s="5" t="n">
-        <v>27204</v>
-      </c>
-      <c r="J252" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K252" s="5" t="n">
-        <v>31556800</v>
-      </c>
-      <c r="L252" s="5" t="n">
-        <v>27204</v>
-      </c>
-      <c r="M252" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N252" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" s="3" t="inlineStr">
-        <is>
-          <t>5座</t>
-        </is>
-      </c>
-      <c r="B253" s="3" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="C253" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D253" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E253" s="4" t="n">
-        <v>1723</v>
-      </c>
-      <c r="F253" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G253" s="3" t="inlineStr">
-        <is>
-          <t>2016-05-20</t>
-        </is>
-      </c>
-      <c r="H253" s="5" t="n">
-        <v>52792900</v>
-      </c>
-      <c r="I253" s="5" t="n">
-        <v>30640</v>
-      </c>
-      <c r="J253" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K253" s="5" t="n">
-        <v>52792900</v>
-      </c>
-      <c r="L253" s="5" t="n">
-        <v>30640</v>
-      </c>
-      <c r="M253" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N253" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" s="3" t="inlineStr">
-        <is>
-          <t>5座</t>
-        </is>
-      </c>
-      <c r="B254" s="3" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="C254" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D254" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E254" s="4" t="n">
-        <v>1316</v>
-      </c>
-      <c r="F254" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G254" s="3" t="inlineStr">
-        <is>
-          <t>2016-05-03</t>
-        </is>
-      </c>
-      <c r="H254" s="5" t="n">
-        <v>31388900</v>
-      </c>
-      <c r="I254" s="5" t="n">
-        <v>23852</v>
-      </c>
-      <c r="J254" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K254" s="5" t="n">
-        <v>31388900</v>
-      </c>
-      <c r="L254" s="5" t="n">
-        <v>23852</v>
-      </c>
-      <c r="M254" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N254" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" s="3" t="inlineStr">
-        <is>
-          <t>5座</t>
-        </is>
-      </c>
-      <c r="B255" s="3" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="C255" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D255" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E255" s="4" t="n">
-        <v>1320</v>
-      </c>
-      <c r="F255" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G255" s="3" t="inlineStr">
-        <is>
-          <t>2016-05-16</t>
-        </is>
-      </c>
-      <c r="H255" s="5" t="n">
-        <v>33171200</v>
-      </c>
-      <c r="I255" s="5" t="n">
-        <v>25130</v>
-      </c>
-      <c r="J255" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K255" s="5" t="n">
-        <v>33171200</v>
-      </c>
-      <c r="L255" s="5" t="n">
-        <v>25130</v>
-      </c>
-      <c r="M255" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N255" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" s="3" t="inlineStr">
-        <is>
-          <t>5座</t>
-        </is>
-      </c>
-      <c r="B256" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C256" s="3" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D256" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E256" s="4" t="n">
-        <v>1065</v>
-      </c>
-      <c r="F256" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G256" s="3" t="inlineStr">
-        <is>
-          <t>2016-05-18</t>
-        </is>
-      </c>
-      <c r="H256" s="5" t="n">
-        <v>30454700</v>
-      </c>
-      <c r="I256" s="5" t="n">
-        <v>28596</v>
-      </c>
-      <c r="J256" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K256" s="5" t="n">
-        <v>30454700</v>
-      </c>
-      <c r="L256" s="5" t="n">
-        <v>28596</v>
-      </c>
-      <c r="M256" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N256" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" s="3" t="inlineStr">
-        <is>
-          <t>5座</t>
-        </is>
-      </c>
-      <c r="B257" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C257" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D257" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E257" s="4" t="n">
-        <v>1723</v>
-      </c>
-      <c r="F257" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G257" s="3" t="inlineStr">
-        <is>
-          <t>2019-01-16</t>
-        </is>
-      </c>
-      <c r="H257" s="5" t="n">
-        <v>55342040</v>
-      </c>
-      <c r="I257" s="5" t="n">
-        <v>32120</v>
-      </c>
-      <c r="J257" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K257" s="5" t="n">
-        <v>55342040</v>
-      </c>
-      <c r="L257" s="5" t="n">
-        <v>32120</v>
-      </c>
-      <c r="M257" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N257" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" s="3" t="inlineStr">
-        <is>
-          <t>5座</t>
-        </is>
-      </c>
-      <c r="B258" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C258" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D258" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E258" s="4" t="n">
-        <v>1316</v>
-      </c>
-      <c r="F258" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G258" s="3" t="inlineStr">
-        <is>
-          <t>2016-04-29</t>
-        </is>
-      </c>
-      <c r="H258" s="5" t="n">
-        <v>29191600</v>
-      </c>
-      <c r="I258" s="5" t="n">
-        <v>22182</v>
-      </c>
-      <c r="J258" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K258" s="5" t="n">
-        <v>29191600</v>
-      </c>
-      <c r="L258" s="5" t="n">
-        <v>22182</v>
-      </c>
-      <c r="M258" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N258" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" s="3" t="inlineStr">
-        <is>
-          <t>5座</t>
-        </is>
-      </c>
-      <c r="B259" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C259" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D259" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E259" s="4" t="n">
-        <v>1320</v>
-      </c>
-      <c r="F259" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G259" s="3" t="inlineStr">
-        <is>
-          <t>2016-05-10</t>
-        </is>
-      </c>
-      <c r="H259" s="5" t="n">
-        <v>30849200</v>
-      </c>
-      <c r="I259" s="5" t="n">
-        <v>23371</v>
-      </c>
-      <c r="J259" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K259" s="5" t="n">
-        <v>30849200</v>
-      </c>
-      <c r="L259" s="5" t="n">
-        <v>23371</v>
-      </c>
-      <c r="M259" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N259" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" s="3" t="inlineStr">
-        <is>
-          <t>5座</t>
-        </is>
-      </c>
-      <c r="B260" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C260" s="3" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D260" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E260" s="4" t="n">
-        <v>1160</v>
-      </c>
-      <c r="F260" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G260" s="3" t="inlineStr">
-        <is>
-          <t>2016-05-16</t>
-        </is>
-      </c>
-      <c r="H260" s="5" t="n">
-        <v>28749300</v>
-      </c>
-      <c r="I260" s="5" t="n">
-        <v>24784</v>
-      </c>
-      <c r="J260" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K260" s="5" t="n">
-        <v>28749300</v>
-      </c>
-      <c r="L260" s="5" t="n">
-        <v>24784</v>
-      </c>
-      <c r="M260" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N260" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" s="3" t="inlineStr">
-        <is>
-          <t>5座</t>
-        </is>
-      </c>
-      <c r="B261" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C261" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D261" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E261" s="4" t="n">
-        <v>1723</v>
-      </c>
-      <c r="F261" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G261" s="3" t="inlineStr">
-        <is>
-          <t>2019-01-04</t>
-        </is>
-      </c>
-      <c r="H261" s="5" t="n">
-        <v>48712000</v>
-      </c>
-      <c r="I261" s="5" t="n">
-        <v>28272</v>
-      </c>
-      <c r="J261" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K261" s="5" t="n">
-        <v>48712000</v>
-      </c>
-      <c r="L261" s="5" t="n">
-        <v>28272</v>
-      </c>
-      <c r="M261" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N261" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" s="3" t="inlineStr">
-        <is>
-          <t>5座</t>
-        </is>
-      </c>
-      <c r="B262" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C262" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D262" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E262" s="4" t="n">
-        <v>1316</v>
-      </c>
-      <c r="F262" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G262" s="3" t="inlineStr">
-        <is>
-          <t>2016-04-28</t>
-        </is>
-      </c>
-      <c r="H262" s="5" t="n">
-        <v>29016400</v>
-      </c>
-      <c r="I262" s="5" t="n">
-        <v>22049</v>
-      </c>
-      <c r="J262" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K262" s="5" t="n">
-        <v>29016400</v>
-      </c>
-      <c r="L262" s="5" t="n">
-        <v>22049</v>
-      </c>
-      <c r="M262" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N262" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" s="3" t="inlineStr">
-        <is>
-          <t>5座</t>
-        </is>
-      </c>
-      <c r="B263" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C263" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D263" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E263" s="4" t="n">
-        <v>1320</v>
-      </c>
-      <c r="F263" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G263" s="3" t="inlineStr">
-        <is>
-          <t>2016-04-15</t>
-        </is>
-      </c>
-      <c r="H263" s="5" t="n">
-        <v>30664100</v>
-      </c>
-      <c r="I263" s="5" t="n">
-        <v>23230</v>
-      </c>
-      <c r="J263" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K263" s="5" t="n">
-        <v>30664100</v>
-      </c>
-      <c r="L263" s="5" t="n">
-        <v>23230</v>
-      </c>
-      <c r="M263" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N263" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" s="3" t="inlineStr">
-        <is>
-          <t>5座</t>
-        </is>
-      </c>
-      <c r="B264" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C264" s="3" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D264" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E264" s="4" t="n">
-        <v>1160</v>
-      </c>
-      <c r="F264" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G264" s="3" t="inlineStr">
-        <is>
-          <t>2016-05-16</t>
-        </is>
-      </c>
-      <c r="H264" s="5" t="n">
-        <v>23286900</v>
-      </c>
-      <c r="I264" s="5" t="n">
-        <v>20075</v>
-      </c>
-      <c r="J264" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K264" s="5" t="n">
-        <v>23286900</v>
-      </c>
-      <c r="L264" s="5" t="n">
-        <v>20075</v>
-      </c>
-      <c r="M264" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N264" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" s="3" t="inlineStr">
-        <is>
-          <t>5座</t>
-        </is>
-      </c>
-      <c r="B265" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C265" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D265" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E265" s="4" t="n">
-        <v>1723</v>
-      </c>
-      <c r="F265" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G265" s="3" t="inlineStr">
-        <is>
-          <t>2016-05-13</t>
-        </is>
-      </c>
-      <c r="H265" s="5" t="n">
-        <v>38956200</v>
-      </c>
-      <c r="I265" s="5" t="n">
-        <v>22610</v>
-      </c>
-      <c r="J265" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K265" s="5" t="n">
-        <v>38956200</v>
-      </c>
-      <c r="L265" s="5" t="n">
-        <v>22610</v>
-      </c>
-      <c r="M265" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N265" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" s="3" t="inlineStr">
-        <is>
-          <t>5座</t>
-        </is>
-      </c>
-      <c r="B266" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C266" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D266" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E266" s="4" t="n">
-        <v>1221</v>
-      </c>
-      <c r="F266" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G266" s="3" t="inlineStr">
-        <is>
-          <t>2016-04-27</t>
-        </is>
-      </c>
-      <c r="H266" s="5" t="n">
-        <v>22105600</v>
-      </c>
-      <c r="I266" s="5" t="n">
-        <v>18105</v>
-      </c>
-      <c r="J266" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K266" s="5" t="n">
-        <v>22105600</v>
-      </c>
-      <c r="L266" s="5" t="n">
-        <v>18105</v>
-      </c>
-      <c r="M266" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N266" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" s="3" t="inlineStr">
-        <is>
-          <t>5座</t>
-        </is>
-      </c>
-      <c r="B267" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C267" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D267" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E267" s="4" t="n">
-        <v>1320</v>
-      </c>
-      <c r="F267" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G267" s="3" t="inlineStr">
-        <is>
-          <t>2016-05-19</t>
-        </is>
-      </c>
-      <c r="H267" s="5" t="n">
-        <v>25293900</v>
-      </c>
-      <c r="I267" s="5" t="n">
-        <v>19162</v>
-      </c>
-      <c r="J267" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K267" s="5" t="n">
-        <v>25293900</v>
-      </c>
-      <c r="L267" s="5" t="n">
-        <v>19162</v>
-      </c>
-      <c r="M267" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N267" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" s="3" t="inlineStr">
-        <is>
-          <t>5座</t>
-        </is>
-      </c>
-      <c r="B268" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C268" s="3" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D268" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E268" s="4" t="n">
-        <v>1143</v>
-      </c>
-      <c r="F268" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G268" s="3" t="inlineStr">
-        <is>
-          <t>2016-05-16</t>
-        </is>
-      </c>
-      <c r="H268" s="5" t="n">
-        <v>21729500</v>
-      </c>
-      <c r="I268" s="5" t="n">
-        <v>19011</v>
-      </c>
-      <c r="J268" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K268" s="5" t="n">
-        <v>21729500</v>
-      </c>
-      <c r="L268" s="5" t="n">
-        <v>19011</v>
-      </c>
-      <c r="M268" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N268" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" s="3" t="inlineStr">
-        <is>
-          <t>5座</t>
-        </is>
-      </c>
-      <c r="B269" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C269" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D269" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E269" s="4" t="n">
-        <v>1723</v>
-      </c>
-      <c r="F269" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G269" s="3" t="inlineStr">
-        <is>
-          <t>2016-05-16</t>
-        </is>
-      </c>
-      <c r="H269" s="5" t="n">
-        <v>39094700</v>
-      </c>
-      <c r="I269" s="5" t="n">
-        <v>22690</v>
-      </c>
-      <c r="J269" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K269" s="5" t="n">
-        <v>39094700</v>
-      </c>
-      <c r="L269" s="5" t="n">
-        <v>22690</v>
-      </c>
-      <c r="M269" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N269" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" s="3" t="inlineStr">
-        <is>
-          <t>5座</t>
-        </is>
-      </c>
-      <c r="B270" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C270" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D270" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E270" s="4" t="n">
-        <v>1300</v>
-      </c>
-      <c r="F270" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G270" s="3" t="inlineStr">
-        <is>
-          <t>2016-05-17</t>
-        </is>
-      </c>
-      <c r="H270" s="5" t="n">
-        <v>25059000</v>
-      </c>
-      <c r="I270" s="5" t="n">
-        <v>19276</v>
-      </c>
-      <c r="J270" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K270" s="5" t="n">
-        <v>25059000</v>
-      </c>
-      <c r="L270" s="5" t="n">
-        <v>19276</v>
-      </c>
-      <c r="M270" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N270" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" s="3" t="inlineStr">
-        <is>
-          <t>5座</t>
-        </is>
-      </c>
-      <c r="B271" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C271" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D271" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E271" s="4" t="n">
-        <v>1150</v>
-      </c>
-      <c r="F271" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G271" s="3" t="inlineStr">
-        <is>
-          <t>2024-05-30</t>
-        </is>
-      </c>
-      <c r="H271" s="5" t="n">
-        <v>36231000</v>
-      </c>
-      <c r="I271" s="5" t="n">
-        <v>31505</v>
-      </c>
-      <c r="J271" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K271" s="5" t="n">
-        <v>36231000</v>
-      </c>
-      <c r="L271" s="5" t="n">
-        <v>31505</v>
-      </c>
-      <c r="M271" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N271" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" s="3" t="inlineStr">
-        <is>
-          <t>5座</t>
-        </is>
-      </c>
-      <c r="B272" s="3" t="inlineStr">
-        <is>
-          <t>3&amp;4</t>
-        </is>
-      </c>
-      <c r="C272" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D272" s="3" t="inlineStr">
-        <is>
-          <t>2房</t>
-        </is>
-      </c>
-      <c r="E272" s="4" t="n">
-        <v>1970</v>
-      </c>
-      <c r="F272" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G272" s="3" t="inlineStr">
-        <is>
-          <t>2016-05-19</t>
-        </is>
-      </c>
-      <c r="H272" s="5" t="n">
-        <v>62774600</v>
-      </c>
-      <c r="I272" s="5" t="n">
-        <v>31865</v>
-      </c>
-      <c r="J272" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K272" s="5" t="n">
-        <v>62774600</v>
-      </c>
-      <c r="L272" s="5" t="n">
-        <v>31865</v>
-      </c>
-      <c r="M272" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N272" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" s="3" t="inlineStr">
-        <is>
-          <t>5座</t>
-        </is>
-      </c>
-      <c r="B273" s="3" t="inlineStr">
-        <is>
-          <t>3&amp;4</t>
-        </is>
-      </c>
-      <c r="C273" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D273" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E273" s="4" t="n">
-        <v>1929</v>
-      </c>
-      <c r="F273" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G273" s="3" t="inlineStr">
-        <is>
-          <t>2016-04-08</t>
-        </is>
-      </c>
-      <c r="H273" s="5" t="n">
-        <v>45931400</v>
-      </c>
-      <c r="I273" s="5" t="n">
-        <v>23811</v>
-      </c>
-      <c r="J273" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K273" s="5" t="n">
-        <v>45931400</v>
-      </c>
-      <c r="L273" s="5" t="n">
-        <v>23811</v>
-      </c>
-      <c r="M273" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N273" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -19140,814 +14923,6 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>3座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="8" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="9" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="10" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="11" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="12" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="13" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="B3" s="14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" s="18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="19" t="inlineStr">
-        <is>
-          <t>楼层</t>
-        </is>
-      </c>
-      <c r="B4" s="19" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C4" s="19" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D4" s="19" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E4" s="19" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="58" customHeight="1">
-      <c r="A5" s="19" t="inlineStr">
-        <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B5" s="22" t="inlineStr">
-        <is>
-          <t>A | 2681呎 (4+房)
-$15227万
-$56,795/呎
-(25年-11月-25日)</t>
-        </is>
-      </c>
-      <c r="C5" s="21" t="inlineStr"/>
-      <c r="D5" s="22" t="inlineStr">
-        <is>
-          <t>C | 1990呎 (3房)
-$12540万
-$63,015/呎
-(19年-11月-04日)</t>
-        </is>
-      </c>
-      <c r="E5" s="22" t="inlineStr">
-        <is>
-          <t>D | 2173呎 (3房)
-$7670万
-$35,298/呎
-(16年-05月-17日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr"/>
-      <c r="C6" s="21" t="inlineStr"/>
-      <c r="D6" s="22" t="inlineStr">
-        <is>
-          <t>C | 2128呎 (3房)
-$8248万
-$38,761/呎
-(16年-05月-16日)</t>
-        </is>
-      </c>
-      <c r="E6" s="21" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>22&amp;23</t>
-        </is>
-      </c>
-      <c r="B7" s="22" t="inlineStr">
-        <is>
-          <t>A | 2265呎 (4+房)
-$15583万
-$68,797/呎
-(19年-07月-30日)</t>
-        </is>
-      </c>
-      <c r="C7" s="22" t="inlineStr">
-        <is>
-          <t>B | 2199呎 (4+房)
-$14260万
-$64,849/呎
-(19年-02月-21日)</t>
-        </is>
-      </c>
-      <c r="D7" s="21" t="inlineStr"/>
-      <c r="E7" s="21" t="inlineStr"/>
-    </row>
-    <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="B8" s="21" t="inlineStr"/>
-      <c r="C8" s="21" t="inlineStr"/>
-      <c r="D8" s="22" t="inlineStr">
-        <is>
-          <t>C | 1237呎 (3房)
-$3250万
-$26,273/呎
-(24年-04月-16日)</t>
-        </is>
-      </c>
-      <c r="E8" s="22" t="inlineStr">
-        <is>
-          <t>D | 1428呎 (4+房)
-$4251万
-$29,770/呎
-(16年-04月-27日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="B9" s="22" t="inlineStr">
-        <is>
-          <t>A | 1708呎 (4+房)
-$7567万
-$44,304/呎
-(19年-02月-26日)</t>
-        </is>
-      </c>
-      <c r="C9" s="22" t="inlineStr">
-        <is>
-          <t>B | 1738呎 (4+房)
-$6650万
-$38,262/呎
-(16年-04月-25日)</t>
-        </is>
-      </c>
-      <c r="D9" s="22" t="inlineStr">
-        <is>
-          <t>C | 1237呎 (3房)
-$7133万
-$57,666/呎
-(16年-04月-01日)</t>
-        </is>
-      </c>
-      <c r="E9" s="22" t="inlineStr">
-        <is>
-          <t>D | 1428呎 (4+房)
-$4238万
-$29,681/呎
-(16年-04月-27日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B10" s="22" t="inlineStr">
-        <is>
-          <t>A | 1708呎 (4+房)
-$7472万
-$43,746/呎
-(19年-01月-31日)</t>
-        </is>
-      </c>
-      <c r="C10" s="22" t="inlineStr">
-        <is>
-          <t>B | 1738呎 (4+房)
-$6532万
-$37,585/呎
-(16年-05月-17日)</t>
-        </is>
-      </c>
-      <c r="D10" s="22" t="inlineStr">
-        <is>
-          <t>C | 1237呎 (3房)
-$3556万
-$28,747/呎
-(16年-04月-21日)</t>
-        </is>
-      </c>
-      <c r="E10" s="22" t="inlineStr">
-        <is>
-          <t>D | 1428呎 (4+房)
-$4226万
-$29,592/呎
-(16年-04月-27日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B11" s="22" t="inlineStr">
-        <is>
-          <t>A | 1708呎 (4+房)
-$6764万
-$39,600/呎
-(19年-01月-25日)</t>
-        </is>
-      </c>
-      <c r="C11" s="22" t="inlineStr">
-        <is>
-          <t>B | 1738呎 (4+房)
-$6417万
-$36,921/呎
-(16年-05月-10日)</t>
-        </is>
-      </c>
-      <c r="D11" s="22" t="inlineStr">
-        <is>
-          <t>C | 1237呎 (3房)
-$3549万
-$28,689/呎
-(16年-04月-27日)</t>
-        </is>
-      </c>
-      <c r="E11" s="22" t="inlineStr">
-        <is>
-          <t>D | 1428呎 (4+房)
-$4213万
-$29,503/呎
-(16年-04月-27日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B12" s="22" t="inlineStr">
-        <is>
-          <t>A | 1708呎 (4+房)
-$13498万
-$79,030/呎
-(16年-04月-15日)</t>
-        </is>
-      </c>
-      <c r="C12" s="22" t="inlineStr">
-        <is>
-          <t>B | 1738呎 (4+房)
-$13498万
-$77,666/呎
-(16年-04月-15日)</t>
-        </is>
-      </c>
-      <c r="D12" s="22" t="inlineStr">
-        <is>
-          <t>C | 1237呎 (3房)
-$3549万
-$28,689/呎
-(16年-05月-04日)</t>
-        </is>
-      </c>
-      <c r="E12" s="22" t="inlineStr">
-        <is>
-          <t>D | 1428呎 (4+房)
-$4213万
-$29,503/呎
-(16年-05月-09日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B13" s="22" t="inlineStr">
-        <is>
-          <t>A | 1708呎 (4+房)
-$6662万
-$39,006/呎
-(23年-05月-05日)</t>
-        </is>
-      </c>
-      <c r="C13" s="22" t="inlineStr">
-        <is>
-          <t>B | 1738呎 (4+房)
-$6192万
-$35,627/呎
-(16年-04月-21日)</t>
-        </is>
-      </c>
-      <c r="D13" s="22" t="inlineStr">
-        <is>
-          <t>C | 1237呎 (3房)
-$3535万
-$28,575/呎
-(16年-04月-21日)</t>
-        </is>
-      </c>
-      <c r="E13" s="22" t="inlineStr">
-        <is>
-          <t>D | 1428呎 (4+房)
-$4188万
-$29,328/呎
-(16年-04月-21日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B14" s="22" t="inlineStr">
-        <is>
-          <t>A | 1708呎 (4+房)
-$6663万
-$39,009/呎
-(19年-01月-21日)</t>
-        </is>
-      </c>
-      <c r="C14" s="22" t="inlineStr">
-        <is>
-          <t>B | 1738呎 (4+房)
-$6082万
-$34,997/呎
-(16年-05月-16日)</t>
-        </is>
-      </c>
-      <c r="D14" s="22" t="inlineStr">
-        <is>
-          <t>C | 1237呎 (3房)
-$3528万
-$28,518/呎
-(16年-04月-26日)</t>
-        </is>
-      </c>
-      <c r="E14" s="22" t="inlineStr">
-        <is>
-          <t>D | 1428呎 (4+房)
-$4175万
-$29,240/呎
-(16年-04月-19日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="19" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B15" s="22" t="inlineStr">
-        <is>
-          <t>A | 1708呎 (4+房)
-$6483万
-$37,957/呎
-(19年-01月-18日)</t>
-        </is>
-      </c>
-      <c r="C15" s="22" t="inlineStr">
-        <is>
-          <t>B | 1738呎 (4+房)
-$6064万
-$34,892/呎
-(16年-04月-29日)</t>
-        </is>
-      </c>
-      <c r="D15" s="22" t="inlineStr">
-        <is>
-          <t>C | 1237呎 (3房)
-$3517万
-$28,432/呎
-(16年-04月-29日)</t>
-        </is>
-      </c>
-      <c r="E15" s="22" t="inlineStr">
-        <is>
-          <t>D | 1428呎 (4+房)
-$4163万
-$29,152/呎
-(16年-05月-17日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B16" s="22" t="inlineStr">
-        <is>
-          <t>A | 1708呎 (4+房)
-$6290万
-$36,827/呎
-(16年-05月-09日)</t>
-        </is>
-      </c>
-      <c r="C16" s="22" t="inlineStr">
-        <is>
-          <t>B | 1738呎 (4+房)
-$5864万
-$33,740/呎
-(16年-04月-25日)</t>
-        </is>
-      </c>
-      <c r="D16" s="22" t="inlineStr">
-        <is>
-          <t>C | 1237呎 (3房)
-$3454万
-$27,921/呎
-(16年-05月-13日)</t>
-        </is>
-      </c>
-      <c r="E16" s="22" t="inlineStr">
-        <is>
-          <t>D | 1428呎 (4+房)
-$4067万
-$28,482/呎
-(16年-04月-22日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B17" s="22" t="inlineStr">
-        <is>
-          <t>A | 1708呎 (4+房)
-$5890万
-$34,483/呎
-(19年-01月-22日)</t>
-        </is>
-      </c>
-      <c r="C17" s="22" t="inlineStr">
-        <is>
-          <t>B | 1738呎 (4+房)
-$5436万
-$31,277/呎
-(16年-04月-28日)</t>
-        </is>
-      </c>
-      <c r="D17" s="22" t="inlineStr">
-        <is>
-          <t>C | 1237呎 (3房)
-$3340万
-$26,999/呎
-(16年-05月-05日)</t>
-        </is>
-      </c>
-      <c r="E17" s="22" t="inlineStr">
-        <is>
-          <t>D | 1428呎 (4+房)
-$3933万
-$27,542/呎
-(16年-05月-05日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="58" customHeight="1">
-      <c r="A18" s="19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B18" s="22" t="inlineStr">
-        <is>
-          <t>A | 1708呎 (4+房)
-$5567万
-$32,593/呎
-(19年-03月-04日)</t>
-        </is>
-      </c>
-      <c r="C18" s="22" t="inlineStr">
-        <is>
-          <t>B | 1738呎 (4+房)
-$4441万
-$25,554/呎
-(16年-05月-03日)</t>
-        </is>
-      </c>
-      <c r="D18" s="22" t="inlineStr">
-        <is>
-          <t>C | 1237呎 (3房)
-$3263万
-$26,378/呎
-(16年-04月-20日)</t>
-        </is>
-      </c>
-      <c r="E18" s="22" t="inlineStr">
-        <is>
-          <t>D | 1428呎 (4+房)
-$3842万
-$26,908/呎
-(16年-04月-26日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="58" customHeight="1">
-      <c r="A19" s="19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B19" s="22" t="inlineStr">
-        <is>
-          <t>A | 1708呎 (4+房)
-$8063万
-$47,206/呎
-(16年-04月-01日)</t>
-        </is>
-      </c>
-      <c r="C19" s="22" t="inlineStr">
-        <is>
-          <t>B | 1738呎 (4+房)
-$8063万
-$46,391/呎
-(16年-04月-01日)</t>
-        </is>
-      </c>
-      <c r="D19" s="22" t="inlineStr">
-        <is>
-          <t>C | 1237呎 (3房)
-$3178万
-$25,692/呎
-(16年-04月-26日)</t>
-        </is>
-      </c>
-      <c r="E19" s="22" t="inlineStr">
-        <is>
-          <t>D | 1428呎 (4+房)
-$3743万
-$26,209/呎
-(16年-04月-21日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="58" customHeight="1">
-      <c r="A20" s="19" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B20" s="22" t="inlineStr">
-        <is>
-          <t>A | 1708呎 (4+房)
-$5332万
-$31,220/呎
-(19年-02月-01日)</t>
-        </is>
-      </c>
-      <c r="C20" s="22" t="inlineStr">
-        <is>
-          <t>B | 1738呎 (4+房)
-$3891万
-$22,388/呎
-(16年-04月-22日)</t>
-        </is>
-      </c>
-      <c r="D20" s="22" t="inlineStr">
-        <is>
-          <t>C | 1237呎 (3房)
-$3115万
-$25,179/呎
-(16年-04月-25日)</t>
-        </is>
-      </c>
-      <c r="E20" s="22" t="inlineStr">
-        <is>
-          <t>D | 1428呎 (4+房)
-$3630万
-$25,422/呎
-(16年-04月-25日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="58" customHeight="1">
-      <c r="A21" s="19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B21" s="22" t="inlineStr">
-        <is>
-          <t>A | 1708呎 (4+房)
-$5188万
-$30,378/呎
-(19年-01月-11日)</t>
-        </is>
-      </c>
-      <c r="C21" s="22" t="inlineStr">
-        <is>
-          <t>B | 1738呎 (4+房)
-$3790万
-$21,806/呎
-(16年-04月-28日)</t>
-        </is>
-      </c>
-      <c r="D21" s="22" t="inlineStr">
-        <is>
-          <t>C | 1237呎 (3房)
-$2800万
-$22,635/呎
-(16年-04月-20日)</t>
-        </is>
-      </c>
-      <c r="E21" s="22" t="inlineStr">
-        <is>
-          <t>D | 1428呎 (4+房)
-$3227万
-$22,600/呎
-(16年-04月-20日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="58" customHeight="1">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B22" s="22" t="inlineStr">
-        <is>
-          <t>A | 1708呎 (4+房)
-$5049万
-$29,560/呎
-(19年-01月-15日)</t>
-        </is>
-      </c>
-      <c r="C22" s="22" t="inlineStr">
-        <is>
-          <t>B | 1738呎 (4+房)
-$3127万
-$17,990/呎
-(16年-04月-20日)</t>
-        </is>
-      </c>
-      <c r="D22" s="22" t="inlineStr">
-        <is>
-          <t>C | 1237呎 (3房)
-$2082万
-$16,831/呎
-(16年-04月-19日)</t>
-        </is>
-      </c>
-      <c r="E22" s="22" t="inlineStr">
-        <is>
-          <t>D | 1428呎 (4+房)
-$2499万
-$17,500/呎
-(16年-04月-20日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="58" customHeight="1">
-      <c r="A23" s="19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B23" s="22" t="inlineStr">
-        <is>
-          <t>A | 1691呎 (4+房)
-$3166万
-$18,724/呎
-(16年-05月-04日)</t>
-        </is>
-      </c>
-      <c r="C23" s="22" t="inlineStr">
-        <is>
-          <t>B | 1722呎 (4+房)
-$3061万
-$17,778/呎
-(16年-05月-18日)</t>
-        </is>
-      </c>
-      <c r="D23" s="22" t="inlineStr">
-        <is>
-          <t>C | 1221呎 (3房)
-$2198万
-$18,005/呎
-(16年-04月-22日)</t>
-        </is>
-      </c>
-      <c r="E23" s="22" t="inlineStr">
-        <is>
-          <t>D | 1412呎 (4+房)
-$2421万
-$17,145/呎
-(16年-04月-22日)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F23"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
           <t>5座 销控网格图</t>
         </is>
       </c>

--- a/web/files/九龙-何文田-天铸 (第2期).xlsx
+++ b/web/files/九龙-何文田-天铸 (第2期).xlsx
@@ -10,7 +10,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5座" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3座" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5座" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -636,7 +637,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N205"/>
+  <dimension ref="A1:N273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -8875,7 +8876,7 @@
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>5座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
@@ -8890,11 +8891,11 @@
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E134" s="4" t="n">
-        <v>2187</v>
+        <v>2173</v>
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
@@ -8903,14 +8904,14 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2016-04-15</t>
+          <t>2016-05-17</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
-        <v>151799500</v>
+        <v>76702500</v>
       </c>
       <c r="I134" s="5" t="n">
-        <v>69410</v>
+        <v>35298</v>
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
@@ -8918,10 +8919,10 @@
         </is>
       </c>
       <c r="K134" s="5" t="n">
-        <v>151799500</v>
+        <v>76702500</v>
       </c>
       <c r="L134" s="5" t="n">
-        <v>69410</v>
+        <v>35298</v>
       </c>
       <c r="M134" s="3" t="inlineStr">
         <is>
@@ -8937,7 +8938,7 @@
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>5座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
@@ -8952,11 +8953,11 @@
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E135" s="4" t="n">
-        <v>2130</v>
+        <v>1990</v>
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
@@ -8965,14 +8966,14 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2016-04-22</t>
+          <t>2019-11-04</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
-        <v>91650000</v>
+        <v>125400000</v>
       </c>
       <c r="I135" s="5" t="n">
-        <v>43028</v>
+        <v>63015</v>
       </c>
       <c r="J135" s="3" t="inlineStr">
         <is>
@@ -8980,10 +8981,10 @@
         </is>
       </c>
       <c r="K135" s="5" t="n">
-        <v>91650000</v>
+        <v>125400000</v>
       </c>
       <c r="L135" s="5" t="n">
-        <v>43028</v>
+        <v>63015</v>
       </c>
       <c r="M135" s="3" t="inlineStr">
         <is>
@@ -8999,7 +9000,7 @@
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
         <is>
-          <t>5座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
@@ -9018,7 +9019,7 @@
         </is>
       </c>
       <c r="E136" s="4" t="n">
-        <v>2733</v>
+        <v>2681</v>
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
@@ -9027,14 +9028,14 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2019-02-15</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="H136" s="5" t="n">
-        <v>213912000</v>
+        <v>152267800</v>
       </c>
       <c r="I136" s="5" t="n">
-        <v>78270</v>
+        <v>56795</v>
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
@@ -9042,10 +9043,10 @@
         </is>
       </c>
       <c r="K136" s="5" t="n">
-        <v>213912000</v>
+        <v>152267800</v>
       </c>
       <c r="L136" s="5" t="n">
-        <v>78270</v>
+        <v>56795</v>
       </c>
       <c r="M136" s="3" t="inlineStr">
         <is>
@@ -9061,7 +9062,7 @@
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
         <is>
-          <t>5座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
@@ -9080,7 +9081,7 @@
         </is>
       </c>
       <c r="E137" s="4" t="n">
-        <v>2044</v>
+        <v>2128</v>
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
@@ -9089,14 +9090,14 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2020-02-21</t>
+          <t>2016-05-16</t>
         </is>
       </c>
       <c r="H137" s="5" t="n">
-        <v>128601000</v>
+        <v>82484200</v>
       </c>
       <c r="I137" s="5" t="n">
-        <v>62916</v>
+        <v>38761</v>
       </c>
       <c r="J137" s="3" t="inlineStr">
         <is>
@@ -9104,10 +9105,10 @@
         </is>
       </c>
       <c r="K137" s="5" t="n">
-        <v>128601000</v>
+        <v>82484200</v>
       </c>
       <c r="L137" s="5" t="n">
-        <v>62916</v>
+        <v>38761</v>
       </c>
       <c r="M137" s="3" t="inlineStr">
         <is>
@@ -9123,17 +9124,17 @@
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
         <is>
-          <t>5座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D138" s="3" t="inlineStr">
@@ -9142,7 +9143,7 @@
         </is>
       </c>
       <c r="E138" s="4" t="n">
-        <v>1316</v>
+        <v>1428</v>
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
@@ -9155,10 +9156,10 @@
         </is>
       </c>
       <c r="H138" s="5" t="n">
-        <v>39981600</v>
+        <v>42511300</v>
       </c>
       <c r="I138" s="5" t="n">
-        <v>30381</v>
+        <v>29770</v>
       </c>
       <c r="J138" s="3" t="inlineStr">
         <is>
@@ -9166,10 +9167,10 @@
         </is>
       </c>
       <c r="K138" s="5" t="n">
-        <v>39981600</v>
+        <v>42511300</v>
       </c>
       <c r="L138" s="5" t="n">
-        <v>30381</v>
+        <v>29770</v>
       </c>
       <c r="M138" s="3" t="inlineStr">
         <is>
@@ -9185,26 +9186,26 @@
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
         <is>
-          <t>5座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E139" s="4" t="n">
-        <v>1320</v>
+        <v>1237</v>
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
@@ -9213,14 +9214,14 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2016-05-09</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="H139" s="5" t="n">
-        <v>43077300</v>
+        <v>32500000</v>
       </c>
       <c r="I139" s="5" t="n">
-        <v>32634</v>
+        <v>26273</v>
       </c>
       <c r="J139" s="3" t="inlineStr">
         <is>
@@ -9228,10 +9229,10 @@
         </is>
       </c>
       <c r="K139" s="5" t="n">
-        <v>43077300</v>
+        <v>32500000</v>
       </c>
       <c r="L139" s="5" t="n">
-        <v>32634</v>
+        <v>26273</v>
       </c>
       <c r="M139" s="3" t="inlineStr">
         <is>
@@ -9247,26 +9248,26 @@
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
         <is>
-          <t>5座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>22&amp;23</t>
         </is>
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E140" s="4" t="n">
-        <v>1160</v>
+        <v>2199</v>
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
@@ -9275,14 +9276,14 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2016-05-11</t>
+          <t>2019-02-21</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
-        <v>38618900</v>
+        <v>142602800</v>
       </c>
       <c r="I140" s="5" t="n">
-        <v>33292</v>
+        <v>64849</v>
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
@@ -9290,10 +9291,10 @@
         </is>
       </c>
       <c r="K140" s="5" t="n">
-        <v>38618900</v>
+        <v>142602800</v>
       </c>
       <c r="L140" s="5" t="n">
-        <v>33292</v>
+        <v>64849</v>
       </c>
       <c r="M140" s="3" t="inlineStr">
         <is>
@@ -9309,17 +9310,17 @@
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
         <is>
-          <t>5座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>22&amp;23</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D141" s="3" t="inlineStr">
@@ -9328,7 +9329,7 @@
         </is>
       </c>
       <c r="E141" s="4" t="n">
-        <v>1723</v>
+        <v>2265</v>
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
@@ -9337,14 +9338,14 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2016-04-28</t>
+          <t>2019-07-30</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
-        <v>70738800</v>
+        <v>155826000</v>
       </c>
       <c r="I141" s="5" t="n">
-        <v>41056</v>
+        <v>68797</v>
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
@@ -9352,10 +9353,10 @@
         </is>
       </c>
       <c r="K141" s="5" t="n">
-        <v>70738800</v>
+        <v>155826000</v>
       </c>
       <c r="L141" s="5" t="n">
-        <v>41056</v>
+        <v>68797</v>
       </c>
       <c r="M141" s="3" t="inlineStr">
         <is>
@@ -9371,17 +9372,17 @@
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
         <is>
-          <t>5座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D142" s="3" t="inlineStr">
@@ -9390,7 +9391,7 @@
         </is>
       </c>
       <c r="E142" s="4" t="n">
-        <v>1221</v>
+        <v>1428</v>
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
@@ -9399,14 +9400,14 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2016-05-05</t>
+          <t>2016-04-27</t>
         </is>
       </c>
       <c r="H142" s="5" t="n">
-        <v>39468600</v>
+        <v>42384100</v>
       </c>
       <c r="I142" s="5" t="n">
-        <v>32325</v>
+        <v>29681</v>
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
@@ -9414,10 +9415,10 @@
         </is>
       </c>
       <c r="K142" s="5" t="n">
-        <v>39468600</v>
+        <v>42384100</v>
       </c>
       <c r="L142" s="5" t="n">
-        <v>32325</v>
+        <v>29681</v>
       </c>
       <c r="M142" s="3" t="inlineStr">
         <is>
@@ -9433,26 +9434,26 @@
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
         <is>
-          <t>5座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E143" s="4" t="n">
-        <v>1320</v>
+        <v>1237</v>
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
@@ -9461,14 +9462,14 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2016-05-13</t>
+          <t>2016-04-01</t>
         </is>
       </c>
       <c r="H143" s="5" t="n">
-        <v>42946400</v>
+        <v>71332700</v>
       </c>
       <c r="I143" s="5" t="n">
-        <v>32535</v>
+        <v>57666</v>
       </c>
       <c r="J143" s="3" t="inlineStr">
         <is>
@@ -9476,10 +9477,10 @@
         </is>
       </c>
       <c r="K143" s="5" t="n">
-        <v>42946400</v>
+        <v>71332700</v>
       </c>
       <c r="L143" s="5" t="n">
-        <v>32535</v>
+        <v>57666</v>
       </c>
       <c r="M143" s="3" t="inlineStr">
         <is>
@@ -9495,7 +9496,7 @@
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
         <is>
-          <t>5座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
@@ -9505,16 +9506,16 @@
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E144" s="4" t="n">
-        <v>1160</v>
+        <v>1738</v>
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
@@ -9523,14 +9524,14 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2016-05-11</t>
+          <t>2016-04-25</t>
         </is>
       </c>
       <c r="H144" s="5" t="n">
-        <v>38407700</v>
+        <v>66498900</v>
       </c>
       <c r="I144" s="5" t="n">
-        <v>33110</v>
+        <v>38262</v>
       </c>
       <c r="J144" s="3" t="inlineStr">
         <is>
@@ -9538,10 +9539,10 @@
         </is>
       </c>
       <c r="K144" s="5" t="n">
-        <v>38407700</v>
+        <v>66498900</v>
       </c>
       <c r="L144" s="5" t="n">
-        <v>33110</v>
+        <v>38262</v>
       </c>
       <c r="M144" s="3" t="inlineStr">
         <is>
@@ -9557,7 +9558,7 @@
     <row r="145">
       <c r="A145" s="3" t="inlineStr">
         <is>
-          <t>5座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
@@ -9567,7 +9568,7 @@
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr">
@@ -9576,7 +9577,7 @@
         </is>
       </c>
       <c r="E145" s="4" t="n">
-        <v>1723</v>
+        <v>1708</v>
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
@@ -9585,14 +9586,14 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2019-01-31</t>
+          <t>2019-02-26</t>
         </is>
       </c>
       <c r="H145" s="5" t="n">
-        <v>71444000</v>
+        <v>75670800</v>
       </c>
       <c r="I145" s="5" t="n">
-        <v>41465</v>
+        <v>44304</v>
       </c>
       <c r="J145" s="3" t="inlineStr">
         <is>
@@ -9600,10 +9601,10 @@
         </is>
       </c>
       <c r="K145" s="5" t="n">
-        <v>71444000</v>
+        <v>75670800</v>
       </c>
       <c r="L145" s="5" t="n">
-        <v>41465</v>
+        <v>44304</v>
       </c>
       <c r="M145" s="3" t="inlineStr">
         <is>
@@ -9619,17 +9620,17 @@
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
         <is>
-          <t>5座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D146" s="3" t="inlineStr">
@@ -9638,7 +9639,7 @@
         </is>
       </c>
       <c r="E146" s="4" t="n">
-        <v>1221</v>
+        <v>1428</v>
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
@@ -9647,14 +9648,14 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2016-04-29</t>
+          <t>2016-04-27</t>
         </is>
       </c>
       <c r="H146" s="5" t="n">
-        <v>38962000</v>
+        <v>42257300</v>
       </c>
       <c r="I146" s="5" t="n">
-        <v>31910</v>
+        <v>29592</v>
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
@@ -9662,10 +9663,10 @@
         </is>
       </c>
       <c r="K146" s="5" t="n">
-        <v>38962000</v>
+        <v>42257300</v>
       </c>
       <c r="L146" s="5" t="n">
-        <v>31910</v>
+        <v>29592</v>
       </c>
       <c r="M146" s="3" t="inlineStr">
         <is>
@@ -9681,26 +9682,26 @@
     <row r="147">
       <c r="A147" s="3" t="inlineStr">
         <is>
-          <t>5座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E147" s="4" t="n">
-        <v>1320</v>
+        <v>1237</v>
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
@@ -9709,14 +9710,14 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2016-05-12</t>
+          <t>2016-04-21</t>
         </is>
       </c>
       <c r="H147" s="5" t="n">
-        <v>42732700</v>
+        <v>35559600</v>
       </c>
       <c r="I147" s="5" t="n">
-        <v>32373</v>
+        <v>28747</v>
       </c>
       <c r="J147" s="3" t="inlineStr">
         <is>
@@ -9724,10 +9725,10 @@
         </is>
       </c>
       <c r="K147" s="5" t="n">
-        <v>42732700</v>
+        <v>35559600</v>
       </c>
       <c r="L147" s="5" t="n">
-        <v>32373</v>
+        <v>28747</v>
       </c>
       <c r="M147" s="3" t="inlineStr">
         <is>
@@ -9743,7 +9744,7 @@
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
         <is>
-          <t>5座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
@@ -9753,16 +9754,16 @@
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E148" s="4" t="n">
-        <v>1160</v>
+        <v>1738</v>
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
@@ -9771,14 +9772,14 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2016-05-12</t>
+          <t>2016-05-17</t>
         </is>
       </c>
       <c r="H148" s="5" t="n">
-        <v>38197600</v>
+        <v>65323000</v>
       </c>
       <c r="I148" s="5" t="n">
-        <v>32929</v>
+        <v>37585</v>
       </c>
       <c r="J148" s="3" t="inlineStr">
         <is>
@@ -9786,10 +9787,10 @@
         </is>
       </c>
       <c r="K148" s="5" t="n">
-        <v>38197600</v>
+        <v>65323000</v>
       </c>
       <c r="L148" s="5" t="n">
-        <v>32929</v>
+        <v>37585</v>
       </c>
       <c r="M148" s="3" t="inlineStr">
         <is>
@@ -9805,7 +9806,7 @@
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
         <is>
-          <t>5座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
@@ -9815,7 +9816,7 @@
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D149" s="3" t="inlineStr">
@@ -9824,7 +9825,7 @@
         </is>
       </c>
       <c r="E149" s="4" t="n">
-        <v>1723</v>
+        <v>1708</v>
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
@@ -9833,14 +9834,14 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>2019-01-15</t>
+          <t>2019-01-31</t>
         </is>
       </c>
       <c r="H149" s="5" t="n">
-        <v>63585000</v>
+        <v>74718000</v>
       </c>
       <c r="I149" s="5" t="n">
-        <v>36904</v>
+        <v>43746</v>
       </c>
       <c r="J149" s="3" t="inlineStr">
         <is>
@@ -9848,10 +9849,10 @@
         </is>
       </c>
       <c r="K149" s="5" t="n">
-        <v>63585000</v>
+        <v>74718000</v>
       </c>
       <c r="L149" s="5" t="n">
-        <v>36904</v>
+        <v>43746</v>
       </c>
       <c r="M149" s="3" t="inlineStr">
         <is>
@@ -9867,17 +9868,17 @@
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
         <is>
-          <t>5座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D150" s="3" t="inlineStr">
@@ -9886,7 +9887,7 @@
         </is>
       </c>
       <c r="E150" s="4" t="n">
-        <v>1316</v>
+        <v>1428</v>
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
@@ -9895,14 +9896,14 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2016-04-15</t>
+          <t>2016-04-27</t>
         </is>
       </c>
       <c r="H150" s="5" t="n">
-        <v>76431800</v>
+        <v>42130900</v>
       </c>
       <c r="I150" s="5" t="n">
-        <v>58079</v>
+        <v>29503</v>
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
@@ -9910,10 +9911,10 @@
         </is>
       </c>
       <c r="K150" s="5" t="n">
-        <v>76431800</v>
+        <v>42130900</v>
       </c>
       <c r="L150" s="5" t="n">
-        <v>58079</v>
+        <v>29503</v>
       </c>
       <c r="M150" s="3" t="inlineStr">
         <is>
@@ -9929,26 +9930,26 @@
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
         <is>
-          <t>5座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E151" s="4" t="n">
-        <v>1320</v>
+        <v>1237</v>
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
@@ -9957,14 +9958,14 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2016-04-29</t>
+          <t>2016-04-27</t>
         </is>
       </c>
       <c r="H151" s="5" t="n">
-        <v>41895500</v>
+        <v>35488600</v>
       </c>
       <c r="I151" s="5" t="n">
-        <v>31739</v>
+        <v>28689</v>
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
@@ -9972,10 +9973,10 @@
         </is>
       </c>
       <c r="K151" s="5" t="n">
-        <v>41895500</v>
+        <v>35488600</v>
       </c>
       <c r="L151" s="5" t="n">
-        <v>31739</v>
+        <v>28689</v>
       </c>
       <c r="M151" s="3" t="inlineStr">
         <is>
@@ -9991,7 +9992,7 @@
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
         <is>
-          <t>5座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
@@ -10001,16 +10002,16 @@
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E152" s="4" t="n">
-        <v>1160</v>
+        <v>1738</v>
       </c>
       <c r="F152" s="3" t="inlineStr">
         <is>
@@ -10019,14 +10020,14 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2016-04-15</t>
+          <t>2016-05-10</t>
         </is>
       </c>
       <c r="H152" s="5" t="n">
-        <v>76431800</v>
+        <v>64168100</v>
       </c>
       <c r="I152" s="5" t="n">
-        <v>65889</v>
+        <v>36921</v>
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
@@ -10034,10 +10035,10 @@
         </is>
       </c>
       <c r="K152" s="5" t="n">
-        <v>76431800</v>
+        <v>64168100</v>
       </c>
       <c r="L152" s="5" t="n">
-        <v>65889</v>
+        <v>36921</v>
       </c>
       <c r="M152" s="3" t="inlineStr">
         <is>
@@ -10053,7 +10054,7 @@
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
         <is>
-          <t>5座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
@@ -10063,7 +10064,7 @@
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
@@ -10072,7 +10073,7 @@
         </is>
       </c>
       <c r="E153" s="4" t="n">
-        <v>1723</v>
+        <v>1708</v>
       </c>
       <c r="F153" s="3" t="inlineStr">
         <is>
@@ -10081,14 +10082,14 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2019-01-25</t>
         </is>
       </c>
       <c r="H153" s="5" t="n">
-        <v>53423338</v>
+        <v>67636800</v>
       </c>
       <c r="I153" s="5" t="n">
-        <v>31006</v>
+        <v>39600</v>
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
@@ -10096,10 +10097,10 @@
         </is>
       </c>
       <c r="K153" s="5" t="n">
-        <v>53423338</v>
+        <v>67636800</v>
       </c>
       <c r="L153" s="5" t="n">
-        <v>31006</v>
+        <v>39600</v>
       </c>
       <c r="M153" s="3" t="inlineStr">
         <is>
@@ -10115,17 +10116,17 @@
     <row r="154">
       <c r="A154" s="3" t="inlineStr">
         <is>
-          <t>5座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D154" s="3" t="inlineStr">
@@ -10134,7 +10135,7 @@
         </is>
       </c>
       <c r="E154" s="4" t="n">
-        <v>1316</v>
+        <v>1428</v>
       </c>
       <c r="F154" s="3" t="inlineStr">
         <is>
@@ -10147,10 +10148,10 @@
         </is>
       </c>
       <c r="H154" s="5" t="n">
-        <v>37968500</v>
+        <v>42130900</v>
       </c>
       <c r="I154" s="5" t="n">
-        <v>28851</v>
+        <v>29503</v>
       </c>
       <c r="J154" s="3" t="inlineStr">
         <is>
@@ -10158,10 +10159,10 @@
         </is>
       </c>
       <c r="K154" s="5" t="n">
-        <v>37968500</v>
+        <v>42130900</v>
       </c>
       <c r="L154" s="5" t="n">
-        <v>28851</v>
+        <v>29503</v>
       </c>
       <c r="M154" s="3" t="inlineStr">
         <is>
@@ -10177,26 +10178,26 @@
     <row r="155">
       <c r="A155" s="3" t="inlineStr">
         <is>
-          <t>5座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E155" s="4" t="n">
-        <v>1320</v>
+        <v>1237</v>
       </c>
       <c r="F155" s="3" t="inlineStr">
         <is>
@@ -10205,14 +10206,14 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2016-05-17</t>
+          <t>2016-05-04</t>
         </is>
       </c>
       <c r="H155" s="5" t="n">
-        <v>41964900</v>
+        <v>35488600</v>
       </c>
       <c r="I155" s="5" t="n">
-        <v>31792</v>
+        <v>28689</v>
       </c>
       <c r="J155" s="3" t="inlineStr">
         <is>
@@ -10220,10 +10221,10 @@
         </is>
       </c>
       <c r="K155" s="5" t="n">
-        <v>41964900</v>
+        <v>35488600</v>
       </c>
       <c r="L155" s="5" t="n">
-        <v>31792</v>
+        <v>28689</v>
       </c>
       <c r="M155" s="3" t="inlineStr">
         <is>
@@ -10239,7 +10240,7 @@
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
         <is>
-          <t>5座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
@@ -10249,16 +10250,16 @@
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E156" s="4" t="n">
-        <v>1160</v>
+        <v>1738</v>
       </c>
       <c r="F156" s="3" t="inlineStr">
         <is>
@@ -10267,14 +10268,14 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2016-05-18</t>
+          <t>2016-04-15</t>
         </is>
       </c>
       <c r="H156" s="5" t="n">
-        <v>37816800</v>
+        <v>134983100</v>
       </c>
       <c r="I156" s="5" t="n">
-        <v>32601</v>
+        <v>77666</v>
       </c>
       <c r="J156" s="3" t="inlineStr">
         <is>
@@ -10282,10 +10283,10 @@
         </is>
       </c>
       <c r="K156" s="5" t="n">
-        <v>37816800</v>
+        <v>134983100</v>
       </c>
       <c r="L156" s="5" t="n">
-        <v>32601</v>
+        <v>77666</v>
       </c>
       <c r="M156" s="3" t="inlineStr">
         <is>
@@ -10301,7 +10302,7 @@
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
         <is>
-          <t>5座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
@@ -10311,7 +10312,7 @@
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D157" s="3" t="inlineStr">
@@ -10320,7 +10321,7 @@
         </is>
       </c>
       <c r="E157" s="4" t="n">
-        <v>1723</v>
+        <v>1708</v>
       </c>
       <c r="F157" s="3" t="inlineStr">
         <is>
@@ -10329,14 +10330,14 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2019-01-07</t>
+          <t>2016-04-15</t>
         </is>
       </c>
       <c r="H157" s="5" t="n">
-        <v>62677000</v>
+        <v>134983100</v>
       </c>
       <c r="I157" s="5" t="n">
-        <v>36377</v>
+        <v>79030</v>
       </c>
       <c r="J157" s="3" t="inlineStr">
         <is>
@@ -10344,10 +10345,10 @@
         </is>
       </c>
       <c r="K157" s="5" t="n">
-        <v>62677000</v>
+        <v>134983100</v>
       </c>
       <c r="L157" s="5" t="n">
-        <v>36377</v>
+        <v>79030</v>
       </c>
       <c r="M157" s="3" t="inlineStr">
         <is>
@@ -10363,17 +10364,17 @@
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
         <is>
-          <t>5座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D158" s="3" t="inlineStr">
@@ -10382,7 +10383,7 @@
         </is>
       </c>
       <c r="E158" s="4" t="n">
-        <v>1316</v>
+        <v>1428</v>
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
@@ -10391,14 +10392,14 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2016-05-09</t>
+          <t>2016-04-21</t>
         </is>
       </c>
       <c r="H158" s="5" t="n">
-        <v>37592500</v>
+        <v>41879700</v>
       </c>
       <c r="I158" s="5" t="n">
-        <v>28566</v>
+        <v>29328</v>
       </c>
       <c r="J158" s="3" t="inlineStr">
         <is>
@@ -10406,10 +10407,10 @@
         </is>
       </c>
       <c r="K158" s="5" t="n">
-        <v>37592500</v>
+        <v>41879700</v>
       </c>
       <c r="L158" s="5" t="n">
-        <v>28566</v>
+        <v>29328</v>
       </c>
       <c r="M158" s="3" t="inlineStr">
         <is>
@@ -10425,26 +10426,26 @@
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
         <is>
-          <t>5座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E159" s="4" t="n">
-        <v>1320</v>
+        <v>1237</v>
       </c>
       <c r="F159" s="3" t="inlineStr">
         <is>
@@ -10453,14 +10454,14 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2016-05-13</t>
+          <t>2016-04-21</t>
         </is>
       </c>
       <c r="H159" s="5" t="n">
-        <v>41549400</v>
+        <v>35347200</v>
       </c>
       <c r="I159" s="5" t="n">
-        <v>31477</v>
+        <v>28575</v>
       </c>
       <c r="J159" s="3" t="inlineStr">
         <is>
@@ -10468,10 +10469,10 @@
         </is>
       </c>
       <c r="K159" s="5" t="n">
-        <v>41549400</v>
+        <v>35347200</v>
       </c>
       <c r="L159" s="5" t="n">
-        <v>31477</v>
+        <v>28575</v>
       </c>
       <c r="M159" s="3" t="inlineStr">
         <is>
@@ -10487,7 +10488,7 @@
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
         <is>
-          <t>5座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
@@ -10497,16 +10498,16 @@
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D160" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E160" s="4" t="n">
-        <v>1160</v>
+        <v>1738</v>
       </c>
       <c r="F160" s="3" t="inlineStr">
         <is>
@@ -10515,14 +10516,14 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2016-05-13</t>
+          <t>2016-04-21</t>
         </is>
       </c>
       <c r="H160" s="5" t="n">
-        <v>36529200</v>
+        <v>61919400</v>
       </c>
       <c r="I160" s="5" t="n">
-        <v>31491</v>
+        <v>35627</v>
       </c>
       <c r="J160" s="3" t="inlineStr">
         <is>
@@ -10530,10 +10531,10 @@
         </is>
       </c>
       <c r="K160" s="5" t="n">
-        <v>36529200</v>
+        <v>61919400</v>
       </c>
       <c r="L160" s="5" t="n">
-        <v>31491</v>
+        <v>35627</v>
       </c>
       <c r="M160" s="3" t="inlineStr">
         <is>
@@ -10549,7 +10550,7 @@
     <row r="161">
       <c r="A161" s="3" t="inlineStr">
         <is>
-          <t>5座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
@@ -10559,7 +10560,7 @@
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr">
@@ -10568,7 +10569,7 @@
         </is>
       </c>
       <c r="E161" s="4" t="n">
-        <v>1723</v>
+        <v>1708</v>
       </c>
       <c r="F161" s="3" t="inlineStr">
         <is>
@@ -10577,14 +10578,14 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2019-01-17</t>
+          <t>2023-05-05</t>
         </is>
       </c>
       <c r="H161" s="5" t="n">
-        <v>64512640</v>
+        <v>66622000</v>
       </c>
       <c r="I161" s="5" t="n">
-        <v>37442</v>
+        <v>39006</v>
       </c>
       <c r="J161" s="3" t="inlineStr">
         <is>
@@ -10592,10 +10593,10 @@
         </is>
       </c>
       <c r="K161" s="5" t="n">
-        <v>64512640</v>
+        <v>66622000</v>
       </c>
       <c r="L161" s="5" t="n">
-        <v>37442</v>
+        <v>39006</v>
       </c>
       <c r="M161" s="3" t="inlineStr">
         <is>
@@ -10611,17 +10612,17 @@
     <row r="162">
       <c r="A162" s="3" t="inlineStr">
         <is>
-          <t>5座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D162" s="3" t="inlineStr">
@@ -10630,7 +10631,7 @@
         </is>
       </c>
       <c r="E162" s="4" t="n">
-        <v>1221</v>
+        <v>1428</v>
       </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
@@ -10639,14 +10640,14 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2016-05-17</t>
+          <t>2016-04-19</t>
         </is>
       </c>
       <c r="H162" s="5" t="n">
-        <v>37000500</v>
+        <v>41754400</v>
       </c>
       <c r="I162" s="5" t="n">
-        <v>30303</v>
+        <v>29240</v>
       </c>
       <c r="J162" s="3" t="inlineStr">
         <is>
@@ -10654,10 +10655,10 @@
         </is>
       </c>
       <c r="K162" s="5" t="n">
-        <v>37000500</v>
+        <v>41754400</v>
       </c>
       <c r="L162" s="5" t="n">
-        <v>30303</v>
+        <v>29240</v>
       </c>
       <c r="M162" s="3" t="inlineStr">
         <is>
@@ -10673,26 +10674,26 @@
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
         <is>
-          <t>5座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D163" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E163" s="4" t="n">
-        <v>1320</v>
+        <v>1237</v>
       </c>
       <c r="F163" s="3" t="inlineStr">
         <is>
@@ -10701,14 +10702,14 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2016-05-05</t>
+          <t>2016-04-26</t>
         </is>
       </c>
       <c r="H163" s="5" t="n">
-        <v>40105600</v>
+        <v>35276700</v>
       </c>
       <c r="I163" s="5" t="n">
-        <v>30383</v>
+        <v>28518</v>
       </c>
       <c r="J163" s="3" t="inlineStr">
         <is>
@@ -10716,10 +10717,10 @@
         </is>
       </c>
       <c r="K163" s="5" t="n">
-        <v>40105600</v>
+        <v>35276700</v>
       </c>
       <c r="L163" s="5" t="n">
-        <v>30383</v>
+        <v>28518</v>
       </c>
       <c r="M163" s="3" t="inlineStr">
         <is>
@@ -10735,7 +10736,7 @@
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
         <is>
-          <t>5座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
@@ -10745,16 +10746,16 @@
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E164" s="4" t="n">
-        <v>1160</v>
+        <v>1738</v>
       </c>
       <c r="F164" s="3" t="inlineStr">
         <is>
@@ -10767,10 +10768,10 @@
         </is>
       </c>
       <c r="H164" s="5" t="n">
-        <v>35396400</v>
+        <v>60824600</v>
       </c>
       <c r="I164" s="5" t="n">
-        <v>30514</v>
+        <v>34997</v>
       </c>
       <c r="J164" s="3" t="inlineStr">
         <is>
@@ -10778,10 +10779,10 @@
         </is>
       </c>
       <c r="K164" s="5" t="n">
-        <v>35396400</v>
+        <v>60824600</v>
       </c>
       <c r="L164" s="5" t="n">
-        <v>30514</v>
+        <v>34997</v>
       </c>
       <c r="M164" s="3" t="inlineStr">
         <is>
@@ -10797,7 +10798,7 @@
     <row r="165">
       <c r="A165" s="3" t="inlineStr">
         <is>
-          <t>5座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
@@ -10807,7 +10808,7 @@
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D165" s="3" t="inlineStr">
@@ -10816,7 +10817,7 @@
         </is>
       </c>
       <c r="E165" s="4" t="n">
-        <v>1723</v>
+        <v>1708</v>
       </c>
       <c r="F165" s="3" t="inlineStr">
         <is>
@@ -10825,14 +10826,14 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2019-01-17</t>
+          <t>2019-01-21</t>
         </is>
       </c>
       <c r="H165" s="5" t="n">
-        <v>68018820</v>
+        <v>66628000</v>
       </c>
       <c r="I165" s="5" t="n">
-        <v>39477</v>
+        <v>39009</v>
       </c>
       <c r="J165" s="3" t="inlineStr">
         <is>
@@ -10840,10 +10841,10 @@
         </is>
       </c>
       <c r="K165" s="5" t="n">
-        <v>68018820</v>
+        <v>66628000</v>
       </c>
       <c r="L165" s="5" t="n">
-        <v>39477</v>
+        <v>39009</v>
       </c>
       <c r="M165" s="3" t="inlineStr">
         <is>
@@ -10859,17 +10860,17 @@
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
         <is>
-          <t>5座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D166" s="3" t="inlineStr">
@@ -10878,7 +10879,7 @@
         </is>
       </c>
       <c r="E166" s="4" t="n">
-        <v>1316</v>
+        <v>1428</v>
       </c>
       <c r="F166" s="3" t="inlineStr">
         <is>
@@ -10887,14 +10888,14 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2016-05-13</t>
+          <t>2016-05-17</t>
         </is>
       </c>
       <c r="H166" s="5" t="n">
-        <v>36525700</v>
+        <v>41629100</v>
       </c>
       <c r="I166" s="5" t="n">
-        <v>27755</v>
+        <v>29152</v>
       </c>
       <c r="J166" s="3" t="inlineStr">
         <is>
@@ -10902,10 +10903,10 @@
         </is>
       </c>
       <c r="K166" s="5" t="n">
-        <v>36525700</v>
+        <v>41629100</v>
       </c>
       <c r="L166" s="5" t="n">
-        <v>27755</v>
+        <v>29152</v>
       </c>
       <c r="M166" s="3" t="inlineStr">
         <is>
@@ -10921,26 +10922,26 @@
     <row r="167">
       <c r="A167" s="3" t="inlineStr">
         <is>
-          <t>5座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D167" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E167" s="4" t="n">
-        <v>1320</v>
+        <v>1237</v>
       </c>
       <c r="F167" s="3" t="inlineStr">
         <is>
@@ -10949,14 +10950,14 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2016-05-06</t>
+          <t>2016-04-29</t>
         </is>
       </c>
       <c r="H167" s="5" t="n">
-        <v>39396400</v>
+        <v>35170800</v>
       </c>
       <c r="I167" s="5" t="n">
-        <v>29846</v>
+        <v>28432</v>
       </c>
       <c r="J167" s="3" t="inlineStr">
         <is>
@@ -10964,10 +10965,10 @@
         </is>
       </c>
       <c r="K167" s="5" t="n">
-        <v>39396400</v>
+        <v>35170800</v>
       </c>
       <c r="L167" s="5" t="n">
-        <v>29846</v>
+        <v>28432</v>
       </c>
       <c r="M167" s="3" t="inlineStr">
         <is>
@@ -10983,7 +10984,7 @@
     <row r="168">
       <c r="A168" s="3" t="inlineStr">
         <is>
-          <t>5座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
@@ -10993,16 +10994,16 @@
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D168" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E168" s="4" t="n">
-        <v>1065</v>
+        <v>1738</v>
       </c>
       <c r="F168" s="3" t="inlineStr">
         <is>
@@ -11011,14 +11012,14 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2016-05-13</t>
+          <t>2016-04-29</t>
         </is>
       </c>
       <c r="H168" s="5" t="n">
-        <v>35290300</v>
+        <v>60642100</v>
       </c>
       <c r="I168" s="5" t="n">
-        <v>33136</v>
+        <v>34892</v>
       </c>
       <c r="J168" s="3" t="inlineStr">
         <is>
@@ -11026,10 +11027,10 @@
         </is>
       </c>
       <c r="K168" s="5" t="n">
-        <v>35290300</v>
+        <v>60642100</v>
       </c>
       <c r="L168" s="5" t="n">
-        <v>33136</v>
+        <v>34892</v>
       </c>
       <c r="M168" s="3" t="inlineStr">
         <is>
@@ -11045,7 +11046,7 @@
     <row r="169">
       <c r="A169" s="3" t="inlineStr">
         <is>
-          <t>5座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
@@ -11055,7 +11056,7 @@
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D169" s="3" t="inlineStr">
@@ -11064,7 +11065,7 @@
         </is>
       </c>
       <c r="E169" s="4" t="n">
-        <v>1723</v>
+        <v>1708</v>
       </c>
       <c r="F169" s="3" t="inlineStr">
         <is>
@@ -11073,14 +11074,14 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2019-01-07</t>
+          <t>2019-01-18</t>
         </is>
       </c>
       <c r="H169" s="5" t="n">
-        <v>58143200</v>
+        <v>64830000</v>
       </c>
       <c r="I169" s="5" t="n">
-        <v>33745</v>
+        <v>37957</v>
       </c>
       <c r="J169" s="3" t="inlineStr">
         <is>
@@ -11088,10 +11089,10 @@
         </is>
       </c>
       <c r="K169" s="5" t="n">
-        <v>58143200</v>
+        <v>64830000</v>
       </c>
       <c r="L169" s="5" t="n">
-        <v>33745</v>
+        <v>37957</v>
       </c>
       <c r="M169" s="3" t="inlineStr">
         <is>
@@ -11107,17 +11108,17 @@
     <row r="170">
       <c r="A170" s="3" t="inlineStr">
         <is>
-          <t>5座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D170" s="3" t="inlineStr">
@@ -11126,7 +11127,7 @@
         </is>
       </c>
       <c r="E170" s="4" t="n">
-        <v>1316</v>
+        <v>1428</v>
       </c>
       <c r="F170" s="3" t="inlineStr">
         <is>
@@ -11135,14 +11136,14 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2016-05-17</t>
+          <t>2016-04-22</t>
         </is>
       </c>
       <c r="H170" s="5" t="n">
-        <v>36416100</v>
+        <v>40671700</v>
       </c>
       <c r="I170" s="5" t="n">
-        <v>27672</v>
+        <v>28482</v>
       </c>
       <c r="J170" s="3" t="inlineStr">
         <is>
@@ -11150,10 +11151,10 @@
         </is>
       </c>
       <c r="K170" s="5" t="n">
-        <v>36416100</v>
+        <v>40671700</v>
       </c>
       <c r="L170" s="5" t="n">
-        <v>27672</v>
+        <v>28482</v>
       </c>
       <c r="M170" s="3" t="inlineStr">
         <is>
@@ -11169,26 +11170,26 @@
     <row r="171">
       <c r="A171" s="3" t="inlineStr">
         <is>
-          <t>5座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D171" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E171" s="4" t="n">
-        <v>1320</v>
+        <v>1237</v>
       </c>
       <c r="F171" s="3" t="inlineStr">
         <is>
@@ -11197,14 +11198,14 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2016-05-05</t>
+          <t>2016-05-13</t>
         </is>
       </c>
       <c r="H171" s="5" t="n">
-        <v>39278300</v>
+        <v>34537800</v>
       </c>
       <c r="I171" s="5" t="n">
-        <v>29756</v>
+        <v>27921</v>
       </c>
       <c r="J171" s="3" t="inlineStr">
         <is>
@@ -11212,10 +11213,10 @@
         </is>
       </c>
       <c r="K171" s="5" t="n">
-        <v>39278300</v>
+        <v>34537800</v>
       </c>
       <c r="L171" s="5" t="n">
-        <v>29756</v>
+        <v>27921</v>
       </c>
       <c r="M171" s="3" t="inlineStr">
         <is>
@@ -11231,7 +11232,7 @@
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
         <is>
-          <t>5座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
@@ -11241,16 +11242,16 @@
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D172" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E172" s="4" t="n">
-        <v>1160</v>
+        <v>1738</v>
       </c>
       <c r="F172" s="3" t="inlineStr">
         <is>
@@ -11259,14 +11260,14 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2016-05-12</t>
+          <t>2016-04-25</t>
         </is>
       </c>
       <c r="H172" s="5" t="n">
-        <v>35007900</v>
+        <v>58640900</v>
       </c>
       <c r="I172" s="5" t="n">
-        <v>30179</v>
+        <v>33740</v>
       </c>
       <c r="J172" s="3" t="inlineStr">
         <is>
@@ -11274,10 +11275,10 @@
         </is>
       </c>
       <c r="K172" s="5" t="n">
-        <v>35007900</v>
+        <v>58640900</v>
       </c>
       <c r="L172" s="5" t="n">
-        <v>30179</v>
+        <v>33740</v>
       </c>
       <c r="M172" s="3" t="inlineStr">
         <is>
@@ -11293,7 +11294,7 @@
     <row r="173">
       <c r="A173" s="3" t="inlineStr">
         <is>
-          <t>5座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
@@ -11303,7 +11304,7 @@
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D173" s="3" t="inlineStr">
@@ -11312,7 +11313,7 @@
         </is>
       </c>
       <c r="E173" s="4" t="n">
-        <v>1723</v>
+        <v>1708</v>
       </c>
       <c r="F173" s="3" t="inlineStr">
         <is>
@@ -11321,14 +11322,14 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2019-01-17</t>
+          <t>2016-05-09</t>
         </is>
       </c>
       <c r="H173" s="5" t="n">
-        <v>58150600</v>
+        <v>62900600</v>
       </c>
       <c r="I173" s="5" t="n">
-        <v>33750</v>
+        <v>36827</v>
       </c>
       <c r="J173" s="3" t="inlineStr">
         <is>
@@ -11336,10 +11337,10 @@
         </is>
       </c>
       <c r="K173" s="5" t="n">
-        <v>58150600</v>
+        <v>62900600</v>
       </c>
       <c r="L173" s="5" t="n">
-        <v>33750</v>
+        <v>36827</v>
       </c>
       <c r="M173" s="3" t="inlineStr">
         <is>
@@ -11355,17 +11356,17 @@
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
         <is>
-          <t>5座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C174" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D174" s="3" t="inlineStr">
@@ -11374,7 +11375,7 @@
         </is>
       </c>
       <c r="E174" s="4" t="n">
-        <v>1316</v>
+        <v>1428</v>
       </c>
       <c r="F174" s="3" t="inlineStr">
         <is>
@@ -11383,14 +11384,14 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2016-04-28</t>
+          <t>2016-05-05</t>
         </is>
       </c>
       <c r="H174" s="5" t="n">
-        <v>35760600</v>
+        <v>39329500</v>
       </c>
       <c r="I174" s="5" t="n">
-        <v>27174</v>
+        <v>27542</v>
       </c>
       <c r="J174" s="3" t="inlineStr">
         <is>
@@ -11398,10 +11399,10 @@
         </is>
       </c>
       <c r="K174" s="5" t="n">
-        <v>35760600</v>
+        <v>39329500</v>
       </c>
       <c r="L174" s="5" t="n">
-        <v>27174</v>
+        <v>27542</v>
       </c>
       <c r="M174" s="3" t="inlineStr">
         <is>
@@ -11417,26 +11418,26 @@
     <row r="175">
       <c r="A175" s="3" t="inlineStr">
         <is>
-          <t>5座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C175" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D175" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E175" s="4" t="n">
-        <v>1320</v>
+        <v>1237</v>
       </c>
       <c r="F175" s="3" t="inlineStr">
         <is>
@@ -11445,14 +11446,14 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2016-04-28</t>
+          <t>2016-05-05</t>
         </is>
       </c>
       <c r="H175" s="5" t="n">
-        <v>38374900</v>
+        <v>33398000</v>
       </c>
       <c r="I175" s="5" t="n">
-        <v>29072</v>
+        <v>26999</v>
       </c>
       <c r="J175" s="3" t="inlineStr">
         <is>
@@ -11460,10 +11461,10 @@
         </is>
       </c>
       <c r="K175" s="5" t="n">
-        <v>38374900</v>
+        <v>33398000</v>
       </c>
       <c r="L175" s="5" t="n">
-        <v>29072</v>
+        <v>26999</v>
       </c>
       <c r="M175" s="3" t="inlineStr">
         <is>
@@ -11479,7 +11480,7 @@
     <row r="176">
       <c r="A176" s="3" t="inlineStr">
         <is>
-          <t>5座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
@@ -11489,16 +11490,16 @@
       </c>
       <c r="C176" s="3" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D176" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E176" s="4" t="n">
-        <v>1160</v>
+        <v>1738</v>
       </c>
       <c r="F176" s="3" t="inlineStr">
         <is>
@@ -11507,14 +11508,14 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2016-05-11</t>
+          <t>2016-04-28</t>
         </is>
       </c>
       <c r="H176" s="5" t="n">
-        <v>34031200</v>
+        <v>54360100</v>
       </c>
       <c r="I176" s="5" t="n">
-        <v>29337</v>
+        <v>31277</v>
       </c>
       <c r="J176" s="3" t="inlineStr">
         <is>
@@ -11522,10 +11523,10 @@
         </is>
       </c>
       <c r="K176" s="5" t="n">
-        <v>34031200</v>
+        <v>54360100</v>
       </c>
       <c r="L176" s="5" t="n">
-        <v>29337</v>
+        <v>31277</v>
       </c>
       <c r="M176" s="3" t="inlineStr">
         <is>
@@ -11541,7 +11542,7 @@
     <row r="177">
       <c r="A177" s="3" t="inlineStr">
         <is>
-          <t>5座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
@@ -11551,7 +11552,7 @@
       </c>
       <c r="C177" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D177" s="3" t="inlineStr">
@@ -11560,7 +11561,7 @@
         </is>
       </c>
       <c r="E177" s="4" t="n">
-        <v>1723</v>
+        <v>1708</v>
       </c>
       <c r="F177" s="3" t="inlineStr">
         <is>
@@ -11569,14 +11570,14 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2016-05-09</t>
+          <t>2019-01-22</t>
         </is>
       </c>
       <c r="H177" s="5" t="n">
-        <v>56633900</v>
+        <v>58896440</v>
       </c>
       <c r="I177" s="5" t="n">
-        <v>32869</v>
+        <v>34483</v>
       </c>
       <c r="J177" s="3" t="inlineStr">
         <is>
@@ -11584,10 +11585,10 @@
         </is>
       </c>
       <c r="K177" s="5" t="n">
-        <v>56633900</v>
+        <v>58896440</v>
       </c>
       <c r="L177" s="5" t="n">
-        <v>32869</v>
+        <v>34483</v>
       </c>
       <c r="M177" s="3" t="inlineStr">
         <is>
@@ -11603,17 +11604,17 @@
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
         <is>
-          <t>5座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C178" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D178" s="3" t="inlineStr">
@@ -11622,7 +11623,7 @@
         </is>
       </c>
       <c r="E178" s="4" t="n">
-        <v>1316</v>
+        <v>1428</v>
       </c>
       <c r="F178" s="3" t="inlineStr">
         <is>
@@ -11631,14 +11632,14 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2016-04-29</t>
+          <t>2016-04-26</t>
         </is>
       </c>
       <c r="H178" s="5" t="n">
-        <v>35117000</v>
+        <v>38424900</v>
       </c>
       <c r="I178" s="5" t="n">
-        <v>26685</v>
+        <v>26908</v>
       </c>
       <c r="J178" s="3" t="inlineStr">
         <is>
@@ -11646,10 +11647,10 @@
         </is>
       </c>
       <c r="K178" s="5" t="n">
-        <v>35117000</v>
+        <v>38424900</v>
       </c>
       <c r="L178" s="5" t="n">
-        <v>26685</v>
+        <v>26908</v>
       </c>
       <c r="M178" s="3" t="inlineStr">
         <is>
@@ -11665,26 +11666,26 @@
     <row r="179">
       <c r="A179" s="3" t="inlineStr">
         <is>
-          <t>5座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C179" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D179" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E179" s="4" t="n">
-        <v>1320</v>
+        <v>1237</v>
       </c>
       <c r="F179" s="3" t="inlineStr">
         <is>
@@ -11693,14 +11694,14 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2016-04-27</t>
+          <t>2016-04-20</t>
         </is>
       </c>
       <c r="H179" s="5" t="n">
-        <v>37108500</v>
+        <v>32629900</v>
       </c>
       <c r="I179" s="5" t="n">
-        <v>28112</v>
+        <v>26378</v>
       </c>
       <c r="J179" s="3" t="inlineStr">
         <is>
@@ -11708,10 +11709,10 @@
         </is>
       </c>
       <c r="K179" s="5" t="n">
-        <v>37108500</v>
+        <v>32629900</v>
       </c>
       <c r="L179" s="5" t="n">
-        <v>28112</v>
+        <v>26378</v>
       </c>
       <c r="M179" s="3" t="inlineStr">
         <is>
@@ -11727,7 +11728,7 @@
     <row r="180">
       <c r="A180" s="3" t="inlineStr">
         <is>
-          <t>5座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
@@ -11737,16 +11738,16 @@
       </c>
       <c r="C180" s="3" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D180" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E180" s="4" t="n">
-        <v>1065</v>
+        <v>1738</v>
       </c>
       <c r="F180" s="3" t="inlineStr">
         <is>
@@ -11755,14 +11756,14 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2016-05-12</t>
+          <t>2016-05-03</t>
         </is>
       </c>
       <c r="H180" s="5" t="n">
-        <v>33078400</v>
+        <v>44412200</v>
       </c>
       <c r="I180" s="5" t="n">
-        <v>31060</v>
+        <v>25554</v>
       </c>
       <c r="J180" s="3" t="inlineStr">
         <is>
@@ -11770,10 +11771,10 @@
         </is>
       </c>
       <c r="K180" s="5" t="n">
-        <v>33078400</v>
+        <v>44412200</v>
       </c>
       <c r="L180" s="5" t="n">
-        <v>31060</v>
+        <v>25554</v>
       </c>
       <c r="M180" s="3" t="inlineStr">
         <is>
@@ -11789,7 +11790,7 @@
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
         <is>
-          <t>5座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
@@ -11799,7 +11800,7 @@
       </c>
       <c r="C181" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D181" s="3" t="inlineStr">
@@ -11808,7 +11809,7 @@
         </is>
       </c>
       <c r="E181" s="4" t="n">
-        <v>1723</v>
+        <v>1708</v>
       </c>
       <c r="F181" s="3" t="inlineStr">
         <is>
@@ -11817,14 +11818,14 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2016-05-10</t>
+          <t>2019-03-04</t>
         </is>
       </c>
       <c r="H181" s="5" t="n">
-        <v>54481700</v>
+        <v>55668000</v>
       </c>
       <c r="I181" s="5" t="n">
-        <v>31620</v>
+        <v>32593</v>
       </c>
       <c r="J181" s="3" t="inlineStr">
         <is>
@@ -11832,10 +11833,10 @@
         </is>
       </c>
       <c r="K181" s="5" t="n">
-        <v>54481700</v>
+        <v>55668000</v>
       </c>
       <c r="L181" s="5" t="n">
-        <v>31620</v>
+        <v>32593</v>
       </c>
       <c r="M181" s="3" t="inlineStr">
         <is>
@@ -11851,17 +11852,17 @@
     <row r="182">
       <c r="A182" s="3" t="inlineStr">
         <is>
-          <t>5座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C182" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D182" s="3" t="inlineStr">
@@ -11870,7 +11871,7 @@
         </is>
       </c>
       <c r="E182" s="4" t="n">
-        <v>1221</v>
+        <v>1428</v>
       </c>
       <c r="F182" s="3" t="inlineStr">
         <is>
@@ -11879,14 +11880,14 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2016-04-15</t>
+          <t>2016-04-21</t>
         </is>
       </c>
       <c r="H182" s="5" t="n">
-        <v>33606900</v>
+        <v>37425800</v>
       </c>
       <c r="I182" s="5" t="n">
-        <v>27524</v>
+        <v>26209</v>
       </c>
       <c r="J182" s="3" t="inlineStr">
         <is>
@@ -11894,10 +11895,10 @@
         </is>
       </c>
       <c r="K182" s="5" t="n">
-        <v>33606900</v>
+        <v>37425800</v>
       </c>
       <c r="L182" s="5" t="n">
-        <v>27524</v>
+        <v>26209</v>
       </c>
       <c r="M182" s="3" t="inlineStr">
         <is>
@@ -11913,26 +11914,26 @@
     <row r="183">
       <c r="A183" s="3" t="inlineStr">
         <is>
-          <t>5座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C183" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D183" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E183" s="4" t="n">
-        <v>1320</v>
+        <v>1237</v>
       </c>
       <c r="F183" s="3" t="inlineStr">
         <is>
@@ -11941,14 +11942,14 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2016-05-12</t>
+          <t>2016-04-26</t>
         </is>
       </c>
       <c r="H183" s="5" t="n">
-        <v>34770700</v>
+        <v>31781500</v>
       </c>
       <c r="I183" s="5" t="n">
-        <v>26341</v>
+        <v>25692</v>
       </c>
       <c r="J183" s="3" t="inlineStr">
         <is>
@@ -11956,10 +11957,10 @@
         </is>
       </c>
       <c r="K183" s="5" t="n">
-        <v>34770700</v>
+        <v>31781500</v>
       </c>
       <c r="L183" s="5" t="n">
-        <v>26341</v>
+        <v>25692</v>
       </c>
       <c r="M183" s="3" t="inlineStr">
         <is>
@@ -11975,7 +11976,7 @@
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
         <is>
-          <t>5座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
@@ -11985,16 +11986,16 @@
       </c>
       <c r="C184" s="3" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D184" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E184" s="4" t="n">
-        <v>1160</v>
+        <v>1738</v>
       </c>
       <c r="F184" s="3" t="inlineStr">
         <is>
@@ -12003,14 +12004,14 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2016-05-17</t>
+          <t>2016-04-01</t>
         </is>
       </c>
       <c r="H184" s="5" t="n">
-        <v>31556800</v>
+        <v>80627200</v>
       </c>
       <c r="I184" s="5" t="n">
-        <v>27204</v>
+        <v>46391</v>
       </c>
       <c r="J184" s="3" t="inlineStr">
         <is>
@@ -12018,10 +12019,10 @@
         </is>
       </c>
       <c r="K184" s="5" t="n">
-        <v>31556800</v>
+        <v>80627200</v>
       </c>
       <c r="L184" s="5" t="n">
-        <v>27204</v>
+        <v>46391</v>
       </c>
       <c r="M184" s="3" t="inlineStr">
         <is>
@@ -12037,7 +12038,7 @@
     <row r="185">
       <c r="A185" s="3" t="inlineStr">
         <is>
-          <t>5座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
@@ -12047,7 +12048,7 @@
       </c>
       <c r="C185" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D185" s="3" t="inlineStr">
@@ -12056,7 +12057,7 @@
         </is>
       </c>
       <c r="E185" s="4" t="n">
-        <v>1723</v>
+        <v>1708</v>
       </c>
       <c r="F185" s="3" t="inlineStr">
         <is>
@@ -12065,14 +12066,14 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2016-05-20</t>
+          <t>2016-04-01</t>
         </is>
       </c>
       <c r="H185" s="5" t="n">
-        <v>52792900</v>
+        <v>80627200</v>
       </c>
       <c r="I185" s="5" t="n">
-        <v>30640</v>
+        <v>47206</v>
       </c>
       <c r="J185" s="3" t="inlineStr">
         <is>
@@ -12080,10 +12081,10 @@
         </is>
       </c>
       <c r="K185" s="5" t="n">
-        <v>52792900</v>
+        <v>80627200</v>
       </c>
       <c r="L185" s="5" t="n">
-        <v>30640</v>
+        <v>47206</v>
       </c>
       <c r="M185" s="3" t="inlineStr">
         <is>
@@ -12099,17 +12100,17 @@
     <row r="186">
       <c r="A186" s="3" t="inlineStr">
         <is>
-          <t>5座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C186" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D186" s="3" t="inlineStr">
@@ -12118,7 +12119,7 @@
         </is>
       </c>
       <c r="E186" s="4" t="n">
-        <v>1316</v>
+        <v>1428</v>
       </c>
       <c r="F186" s="3" t="inlineStr">
         <is>
@@ -12127,14 +12128,14 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2016-05-03</t>
+          <t>2016-04-25</t>
         </is>
       </c>
       <c r="H186" s="5" t="n">
-        <v>31388900</v>
+        <v>36303100</v>
       </c>
       <c r="I186" s="5" t="n">
-        <v>23852</v>
+        <v>25422</v>
       </c>
       <c r="J186" s="3" t="inlineStr">
         <is>
@@ -12142,10 +12143,10 @@
         </is>
       </c>
       <c r="K186" s="5" t="n">
-        <v>31388900</v>
+        <v>36303100</v>
       </c>
       <c r="L186" s="5" t="n">
-        <v>23852</v>
+        <v>25422</v>
       </c>
       <c r="M186" s="3" t="inlineStr">
         <is>
@@ -12161,26 +12162,26 @@
     <row r="187">
       <c r="A187" s="3" t="inlineStr">
         <is>
-          <t>5座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C187" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D187" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E187" s="4" t="n">
-        <v>1320</v>
+        <v>1237</v>
       </c>
       <c r="F187" s="3" t="inlineStr">
         <is>
@@ -12189,14 +12190,14 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>2016-05-16</t>
+          <t>2016-04-25</t>
         </is>
       </c>
       <c r="H187" s="5" t="n">
-        <v>33171200</v>
+        <v>31145900</v>
       </c>
       <c r="I187" s="5" t="n">
-        <v>25130</v>
+        <v>25179</v>
       </c>
       <c r="J187" s="3" t="inlineStr">
         <is>
@@ -12204,10 +12205,10 @@
         </is>
       </c>
       <c r="K187" s="5" t="n">
-        <v>33171200</v>
+        <v>31145900</v>
       </c>
       <c r="L187" s="5" t="n">
-        <v>25130</v>
+        <v>25179</v>
       </c>
       <c r="M187" s="3" t="inlineStr">
         <is>
@@ -12223,7 +12224,7 @@
     <row r="188">
       <c r="A188" s="3" t="inlineStr">
         <is>
-          <t>5座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
@@ -12233,16 +12234,16 @@
       </c>
       <c r="C188" s="3" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D188" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E188" s="4" t="n">
-        <v>1065</v>
+        <v>1738</v>
       </c>
       <c r="F188" s="3" t="inlineStr">
         <is>
@@ -12251,14 +12252,14 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2016-05-18</t>
+          <t>2016-04-22</t>
         </is>
       </c>
       <c r="H188" s="5" t="n">
-        <v>30454700</v>
+        <v>38910400</v>
       </c>
       <c r="I188" s="5" t="n">
-        <v>28596</v>
+        <v>22388</v>
       </c>
       <c r="J188" s="3" t="inlineStr">
         <is>
@@ -12266,10 +12267,10 @@
         </is>
       </c>
       <c r="K188" s="5" t="n">
-        <v>30454700</v>
+        <v>38910400</v>
       </c>
       <c r="L188" s="5" t="n">
-        <v>28596</v>
+        <v>22388</v>
       </c>
       <c r="M188" s="3" t="inlineStr">
         <is>
@@ -12285,7 +12286,7 @@
     <row r="189">
       <c r="A189" s="3" t="inlineStr">
         <is>
-          <t>5座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
@@ -12295,7 +12296,7 @@
       </c>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D189" s="3" t="inlineStr">
@@ -12304,7 +12305,7 @@
         </is>
       </c>
       <c r="E189" s="4" t="n">
-        <v>1723</v>
+        <v>1708</v>
       </c>
       <c r="F189" s="3" t="inlineStr">
         <is>
@@ -12313,14 +12314,14 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2019-01-16</t>
+          <t>2019-02-01</t>
         </is>
       </c>
       <c r="H189" s="5" t="n">
-        <v>55342040</v>
+        <v>53323000</v>
       </c>
       <c r="I189" s="5" t="n">
-        <v>32120</v>
+        <v>31220</v>
       </c>
       <c r="J189" s="3" t="inlineStr">
         <is>
@@ -12328,10 +12329,10 @@
         </is>
       </c>
       <c r="K189" s="5" t="n">
-        <v>55342040</v>
+        <v>53323000</v>
       </c>
       <c r="L189" s="5" t="n">
-        <v>32120</v>
+        <v>31220</v>
       </c>
       <c r="M189" s="3" t="inlineStr">
         <is>
@@ -12347,17 +12348,17 @@
     <row r="190">
       <c r="A190" s="3" t="inlineStr">
         <is>
-          <t>5座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C190" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D190" s="3" t="inlineStr">
@@ -12366,7 +12367,7 @@
         </is>
       </c>
       <c r="E190" s="4" t="n">
-        <v>1316</v>
+        <v>1428</v>
       </c>
       <c r="F190" s="3" t="inlineStr">
         <is>
@@ -12375,14 +12376,14 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2016-04-29</t>
+          <t>2016-04-20</t>
         </is>
       </c>
       <c r="H190" s="5" t="n">
-        <v>29191600</v>
+        <v>32273500</v>
       </c>
       <c r="I190" s="5" t="n">
-        <v>22182</v>
+        <v>22600</v>
       </c>
       <c r="J190" s="3" t="inlineStr">
         <is>
@@ -12390,10 +12391,10 @@
         </is>
       </c>
       <c r="K190" s="5" t="n">
-        <v>29191600</v>
+        <v>32273500</v>
       </c>
       <c r="L190" s="5" t="n">
-        <v>22182</v>
+        <v>22600</v>
       </c>
       <c r="M190" s="3" t="inlineStr">
         <is>
@@ -12409,26 +12410,26 @@
     <row r="191">
       <c r="A191" s="3" t="inlineStr">
         <is>
-          <t>5座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C191" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D191" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E191" s="4" t="n">
-        <v>1320</v>
+        <v>1237</v>
       </c>
       <c r="F191" s="3" t="inlineStr">
         <is>
@@ -12437,14 +12438,14 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2016-05-10</t>
+          <t>2016-04-20</t>
         </is>
       </c>
       <c r="H191" s="5" t="n">
-        <v>30849200</v>
+        <v>28000100</v>
       </c>
       <c r="I191" s="5" t="n">
-        <v>23371</v>
+        <v>22635</v>
       </c>
       <c r="J191" s="3" t="inlineStr">
         <is>
@@ -12452,10 +12453,10 @@
         </is>
       </c>
       <c r="K191" s="5" t="n">
-        <v>30849200</v>
+        <v>28000100</v>
       </c>
       <c r="L191" s="5" t="n">
-        <v>23371</v>
+        <v>22635</v>
       </c>
       <c r="M191" s="3" t="inlineStr">
         <is>
@@ -12471,7 +12472,7 @@
     <row r="192">
       <c r="A192" s="3" t="inlineStr">
         <is>
-          <t>5座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
@@ -12481,16 +12482,16 @@
       </c>
       <c r="C192" s="3" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D192" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E192" s="4" t="n">
-        <v>1160</v>
+        <v>1738</v>
       </c>
       <c r="F192" s="3" t="inlineStr">
         <is>
@@ -12499,14 +12500,14 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2016-05-16</t>
+          <t>2016-04-28</t>
         </is>
       </c>
       <c r="H192" s="5" t="n">
-        <v>28749300</v>
+        <v>37898700</v>
       </c>
       <c r="I192" s="5" t="n">
-        <v>24784</v>
+        <v>21806</v>
       </c>
       <c r="J192" s="3" t="inlineStr">
         <is>
@@ -12514,10 +12515,10 @@
         </is>
       </c>
       <c r="K192" s="5" t="n">
-        <v>28749300</v>
+        <v>37898700</v>
       </c>
       <c r="L192" s="5" t="n">
-        <v>24784</v>
+        <v>21806</v>
       </c>
       <c r="M192" s="3" t="inlineStr">
         <is>
@@ -12533,7 +12534,7 @@
     <row r="193">
       <c r="A193" s="3" t="inlineStr">
         <is>
-          <t>5座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
@@ -12543,7 +12544,7 @@
       </c>
       <c r="C193" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D193" s="3" t="inlineStr">
@@ -12552,7 +12553,7 @@
         </is>
       </c>
       <c r="E193" s="4" t="n">
-        <v>1723</v>
+        <v>1708</v>
       </c>
       <c r="F193" s="3" t="inlineStr">
         <is>
@@ -12561,14 +12562,14 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2019-01-04</t>
+          <t>2019-01-11</t>
         </is>
       </c>
       <c r="H193" s="5" t="n">
-        <v>48712000</v>
+        <v>51885000</v>
       </c>
       <c r="I193" s="5" t="n">
-        <v>28272</v>
+        <v>30378</v>
       </c>
       <c r="J193" s="3" t="inlineStr">
         <is>
@@ -12576,10 +12577,10 @@
         </is>
       </c>
       <c r="K193" s="5" t="n">
-        <v>48712000</v>
+        <v>51885000</v>
       </c>
       <c r="L193" s="5" t="n">
-        <v>28272</v>
+        <v>30378</v>
       </c>
       <c r="M193" s="3" t="inlineStr">
         <is>
@@ -12595,17 +12596,17 @@
     <row r="194">
       <c r="A194" s="3" t="inlineStr">
         <is>
-          <t>5座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C194" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D194" s="3" t="inlineStr">
@@ -12614,7 +12615,7 @@
         </is>
       </c>
       <c r="E194" s="4" t="n">
-        <v>1316</v>
+        <v>1428</v>
       </c>
       <c r="F194" s="3" t="inlineStr">
         <is>
@@ -12623,14 +12624,14 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2016-04-28</t>
+          <t>2016-04-20</t>
         </is>
       </c>
       <c r="H194" s="5" t="n">
-        <v>29016400</v>
+        <v>24990300</v>
       </c>
       <c r="I194" s="5" t="n">
-        <v>22049</v>
+        <v>17500</v>
       </c>
       <c r="J194" s="3" t="inlineStr">
         <is>
@@ -12638,10 +12639,10 @@
         </is>
       </c>
       <c r="K194" s="5" t="n">
-        <v>29016400</v>
+        <v>24990300</v>
       </c>
       <c r="L194" s="5" t="n">
-        <v>22049</v>
+        <v>17500</v>
       </c>
       <c r="M194" s="3" t="inlineStr">
         <is>
@@ -12657,26 +12658,26 @@
     <row r="195">
       <c r="A195" s="3" t="inlineStr">
         <is>
-          <t>5座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C195" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D195" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E195" s="4" t="n">
-        <v>1320</v>
+        <v>1237</v>
       </c>
       <c r="F195" s="3" t="inlineStr">
         <is>
@@ -12685,14 +12686,14 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2016-04-15</t>
+          <t>2016-04-19</t>
         </is>
       </c>
       <c r="H195" s="5" t="n">
-        <v>30664100</v>
+        <v>20820400</v>
       </c>
       <c r="I195" s="5" t="n">
-        <v>23230</v>
+        <v>16831</v>
       </c>
       <c r="J195" s="3" t="inlineStr">
         <is>
@@ -12700,10 +12701,10 @@
         </is>
       </c>
       <c r="K195" s="5" t="n">
-        <v>30664100</v>
+        <v>20820400</v>
       </c>
       <c r="L195" s="5" t="n">
-        <v>23230</v>
+        <v>16831</v>
       </c>
       <c r="M195" s="3" t="inlineStr">
         <is>
@@ -12719,7 +12720,7 @@
     <row r="196">
       <c r="A196" s="3" t="inlineStr">
         <is>
-          <t>5座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
@@ -12729,16 +12730,16 @@
       </c>
       <c r="C196" s="3" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D196" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E196" s="4" t="n">
-        <v>1160</v>
+        <v>1738</v>
       </c>
       <c r="F196" s="3" t="inlineStr">
         <is>
@@ -12747,14 +12748,14 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2016-05-16</t>
+          <t>2016-04-20</t>
         </is>
       </c>
       <c r="H196" s="5" t="n">
-        <v>23286900</v>
+        <v>31266400</v>
       </c>
       <c r="I196" s="5" t="n">
-        <v>20075</v>
+        <v>17990</v>
       </c>
       <c r="J196" s="3" t="inlineStr">
         <is>
@@ -12762,10 +12763,10 @@
         </is>
       </c>
       <c r="K196" s="5" t="n">
-        <v>23286900</v>
+        <v>31266400</v>
       </c>
       <c r="L196" s="5" t="n">
-        <v>20075</v>
+        <v>17990</v>
       </c>
       <c r="M196" s="3" t="inlineStr">
         <is>
@@ -12781,7 +12782,7 @@
     <row r="197">
       <c r="A197" s="3" t="inlineStr">
         <is>
-          <t>5座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
@@ -12791,7 +12792,7 @@
       </c>
       <c r="C197" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D197" s="3" t="inlineStr">
@@ -12800,7 +12801,7 @@
         </is>
       </c>
       <c r="E197" s="4" t="n">
-        <v>1723</v>
+        <v>1708</v>
       </c>
       <c r="F197" s="3" t="inlineStr">
         <is>
@@ -12809,14 +12810,14 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>2016-05-13</t>
+          <t>2019-01-15</t>
         </is>
       </c>
       <c r="H197" s="5" t="n">
-        <v>38956200</v>
+        <v>50488888</v>
       </c>
       <c r="I197" s="5" t="n">
-        <v>22610</v>
+        <v>29560</v>
       </c>
       <c r="J197" s="3" t="inlineStr">
         <is>
@@ -12824,10 +12825,10 @@
         </is>
       </c>
       <c r="K197" s="5" t="n">
-        <v>38956200</v>
+        <v>50488888</v>
       </c>
       <c r="L197" s="5" t="n">
-        <v>22610</v>
+        <v>29560</v>
       </c>
       <c r="M197" s="3" t="inlineStr">
         <is>
@@ -12843,17 +12844,17 @@
     <row r="198">
       <c r="A198" s="3" t="inlineStr">
         <is>
-          <t>5座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C198" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D198" s="3" t="inlineStr">
@@ -12862,7 +12863,7 @@
         </is>
       </c>
       <c r="E198" s="4" t="n">
-        <v>1221</v>
+        <v>1412</v>
       </c>
       <c r="F198" s="3" t="inlineStr">
         <is>
@@ -12871,14 +12872,14 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2016-04-27</t>
+          <t>2016-04-22</t>
         </is>
       </c>
       <c r="H198" s="5" t="n">
-        <v>22105600</v>
+        <v>24209100</v>
       </c>
       <c r="I198" s="5" t="n">
-        <v>18105</v>
+        <v>17145</v>
       </c>
       <c r="J198" s="3" t="inlineStr">
         <is>
@@ -12886,10 +12887,10 @@
         </is>
       </c>
       <c r="K198" s="5" t="n">
-        <v>22105600</v>
+        <v>24209100</v>
       </c>
       <c r="L198" s="5" t="n">
-        <v>18105</v>
+        <v>17145</v>
       </c>
       <c r="M198" s="3" t="inlineStr">
         <is>
@@ -12905,26 +12906,26 @@
     <row r="199">
       <c r="A199" s="3" t="inlineStr">
         <is>
-          <t>5座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C199" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D199" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E199" s="4" t="n">
-        <v>1320</v>
+        <v>1221</v>
       </c>
       <c r="F199" s="3" t="inlineStr">
         <is>
@@ -12933,14 +12934,14 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2016-05-19</t>
+          <t>2016-04-22</t>
         </is>
       </c>
       <c r="H199" s="5" t="n">
-        <v>25293900</v>
+        <v>21984300</v>
       </c>
       <c r="I199" s="5" t="n">
-        <v>19162</v>
+        <v>18005</v>
       </c>
       <c r="J199" s="3" t="inlineStr">
         <is>
@@ -12948,10 +12949,10 @@
         </is>
       </c>
       <c r="K199" s="5" t="n">
-        <v>25293900</v>
+        <v>21984300</v>
       </c>
       <c r="L199" s="5" t="n">
-        <v>19162</v>
+        <v>18005</v>
       </c>
       <c r="M199" s="3" t="inlineStr">
         <is>
@@ -12967,7 +12968,7 @@
     <row r="200">
       <c r="A200" s="3" t="inlineStr">
         <is>
-          <t>5座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
@@ -12977,16 +12978,16 @@
       </c>
       <c r="C200" s="3" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D200" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E200" s="4" t="n">
-        <v>1143</v>
+        <v>1722</v>
       </c>
       <c r="F200" s="3" t="inlineStr">
         <is>
@@ -12995,14 +12996,14 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2016-05-16</t>
+          <t>2016-05-18</t>
         </is>
       </c>
       <c r="H200" s="5" t="n">
-        <v>21729500</v>
+        <v>30613100</v>
       </c>
       <c r="I200" s="5" t="n">
-        <v>19011</v>
+        <v>17778</v>
       </c>
       <c r="J200" s="3" t="inlineStr">
         <is>
@@ -13010,10 +13011,10 @@
         </is>
       </c>
       <c r="K200" s="5" t="n">
-        <v>21729500</v>
+        <v>30613100</v>
       </c>
       <c r="L200" s="5" t="n">
-        <v>19011</v>
+        <v>17778</v>
       </c>
       <c r="M200" s="3" t="inlineStr">
         <is>
@@ -13029,7 +13030,7 @@
     <row r="201">
       <c r="A201" s="3" t="inlineStr">
         <is>
-          <t>5座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr">
@@ -13039,16 +13040,16 @@
       </c>
       <c r="C201" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D201" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E201" s="4" t="n">
-        <v>1723</v>
+        <v>1691</v>
       </c>
       <c r="F201" s="3" t="inlineStr">
         <is>
@@ -13057,14 +13058,14 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2016-05-16</t>
+          <t>2016-05-04</t>
         </is>
       </c>
       <c r="H201" s="5" t="n">
-        <v>39094700</v>
+        <v>31662800</v>
       </c>
       <c r="I201" s="5" t="n">
-        <v>22690</v>
+        <v>18724</v>
       </c>
       <c r="J201" s="3" t="inlineStr">
         <is>
@@ -13072,10 +13073,10 @@
         </is>
       </c>
       <c r="K201" s="5" t="n">
-        <v>39094700</v>
+        <v>31662800</v>
       </c>
       <c r="L201" s="5" t="n">
-        <v>22690</v>
+        <v>18724</v>
       </c>
       <c r="M201" s="3" t="inlineStr">
         <is>
@@ -13096,12 +13097,12 @@
       </c>
       <c r="B202" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25&amp;26</t>
         </is>
       </c>
       <c r="C202" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D202" s="3" t="inlineStr">
@@ -13110,7 +13111,7 @@
         </is>
       </c>
       <c r="E202" s="4" t="n">
-        <v>1300</v>
+        <v>2187</v>
       </c>
       <c r="F202" s="3" t="inlineStr">
         <is>
@@ -13119,14 +13120,14 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2016-05-17</t>
+          <t>2016-04-15</t>
         </is>
       </c>
       <c r="H202" s="5" t="n">
-        <v>25059000</v>
+        <v>151799500</v>
       </c>
       <c r="I202" s="5" t="n">
-        <v>19276</v>
+        <v>69410</v>
       </c>
       <c r="J202" s="3" t="inlineStr">
         <is>
@@ -13134,10 +13135,10 @@
         </is>
       </c>
       <c r="K202" s="5" t="n">
-        <v>25059000</v>
+        <v>151799500</v>
       </c>
       <c r="L202" s="5" t="n">
-        <v>19276</v>
+        <v>69410</v>
       </c>
       <c r="M202" s="3" t="inlineStr">
         <is>
@@ -13158,12 +13159,12 @@
       </c>
       <c r="B203" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25&amp;26</t>
         </is>
       </c>
       <c r="C203" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D203" s="3" t="inlineStr">
@@ -13172,7 +13173,7 @@
         </is>
       </c>
       <c r="E203" s="4" t="n">
-        <v>1150</v>
+        <v>2130</v>
       </c>
       <c r="F203" s="3" t="inlineStr">
         <is>
@@ -13181,14 +13182,14 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2016-04-22</t>
         </is>
       </c>
       <c r="H203" s="5" t="n">
-        <v>36231000</v>
+        <v>91650000</v>
       </c>
       <c r="I203" s="5" t="n">
-        <v>31505</v>
+        <v>43028</v>
       </c>
       <c r="J203" s="3" t="inlineStr">
         <is>
@@ -13196,10 +13197,10 @@
         </is>
       </c>
       <c r="K203" s="5" t="n">
-        <v>36231000</v>
+        <v>91650000</v>
       </c>
       <c r="L203" s="5" t="n">
-        <v>31505</v>
+        <v>43028</v>
       </c>
       <c r="M203" s="3" t="inlineStr">
         <is>
@@ -13220,21 +13221,21 @@
       </c>
       <c r="B204" s="3" t="inlineStr">
         <is>
-          <t>3&amp;4</t>
+          <t>25&amp;26</t>
         </is>
       </c>
       <c r="C204" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D204" s="3" t="inlineStr">
         <is>
-          <t>2房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E204" s="4" t="n">
-        <v>1970</v>
+        <v>2733</v>
       </c>
       <c r="F204" s="3" t="inlineStr">
         <is>
@@ -13243,14 +13244,14 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2016-05-19</t>
+          <t>2019-02-15</t>
         </is>
       </c>
       <c r="H204" s="5" t="n">
-        <v>62774600</v>
+        <v>213912000</v>
       </c>
       <c r="I204" s="5" t="n">
-        <v>31865</v>
+        <v>78270</v>
       </c>
       <c r="J204" s="3" t="inlineStr">
         <is>
@@ -13258,10 +13259,10 @@
         </is>
       </c>
       <c r="K204" s="5" t="n">
-        <v>62774600</v>
+        <v>213912000</v>
       </c>
       <c r="L204" s="5" t="n">
-        <v>31865</v>
+        <v>78270</v>
       </c>
       <c r="M204" s="3" t="inlineStr">
         <is>
@@ -13282,55 +13283,4271 @@
       </c>
       <c r="B205" s="3" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C205" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D205" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E205" s="4" t="n">
+        <v>2044</v>
+      </c>
+      <c r="F205" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G205" s="3" t="inlineStr">
+        <is>
+          <t>2020-02-21</t>
+        </is>
+      </c>
+      <c r="H205" s="5" t="n">
+        <v>128601000</v>
+      </c>
+      <c r="I205" s="5" t="n">
+        <v>62916</v>
+      </c>
+      <c r="J205" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K205" s="5" t="n">
+        <v>128601000</v>
+      </c>
+      <c r="L205" s="5" t="n">
+        <v>62916</v>
+      </c>
+      <c r="M205" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N205" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="3" t="inlineStr">
+        <is>
+          <t>5座</t>
+        </is>
+      </c>
+      <c r="B206" s="3" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C206" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D206" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E206" s="4" t="n">
+        <v>1316</v>
+      </c>
+      <c r="F206" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G206" s="3" t="inlineStr">
+        <is>
+          <t>2016-04-27</t>
+        </is>
+      </c>
+      <c r="H206" s="5" t="n">
+        <v>39981600</v>
+      </c>
+      <c r="I206" s="5" t="n">
+        <v>30381</v>
+      </c>
+      <c r="J206" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K206" s="5" t="n">
+        <v>39981600</v>
+      </c>
+      <c r="L206" s="5" t="n">
+        <v>30381</v>
+      </c>
+      <c r="M206" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N206" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="3" t="inlineStr">
+        <is>
+          <t>5座</t>
+        </is>
+      </c>
+      <c r="B207" s="3" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C207" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D207" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E207" s="4" t="n">
+        <v>1320</v>
+      </c>
+      <c r="F207" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G207" s="3" t="inlineStr">
+        <is>
+          <t>2016-05-09</t>
+        </is>
+      </c>
+      <c r="H207" s="5" t="n">
+        <v>43077300</v>
+      </c>
+      <c r="I207" s="5" t="n">
+        <v>32634</v>
+      </c>
+      <c r="J207" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K207" s="5" t="n">
+        <v>43077300</v>
+      </c>
+      <c r="L207" s="5" t="n">
+        <v>32634</v>
+      </c>
+      <c r="M207" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N207" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="3" t="inlineStr">
+        <is>
+          <t>5座</t>
+        </is>
+      </c>
+      <c r="B208" s="3" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C208" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D208" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E208" s="4" t="n">
+        <v>1160</v>
+      </c>
+      <c r="F208" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G208" s="3" t="inlineStr">
+        <is>
+          <t>2016-05-11</t>
+        </is>
+      </c>
+      <c r="H208" s="5" t="n">
+        <v>38618900</v>
+      </c>
+      <c r="I208" s="5" t="n">
+        <v>33292</v>
+      </c>
+      <c r="J208" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K208" s="5" t="n">
+        <v>38618900</v>
+      </c>
+      <c r="L208" s="5" t="n">
+        <v>33292</v>
+      </c>
+      <c r="M208" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N208" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="3" t="inlineStr">
+        <is>
+          <t>5座</t>
+        </is>
+      </c>
+      <c r="B209" s="3" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C209" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D209" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E209" s="4" t="n">
+        <v>1723</v>
+      </c>
+      <c r="F209" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G209" s="3" t="inlineStr">
+        <is>
+          <t>2016-04-28</t>
+        </is>
+      </c>
+      <c r="H209" s="5" t="n">
+        <v>70738800</v>
+      </c>
+      <c r="I209" s="5" t="n">
+        <v>41056</v>
+      </c>
+      <c r="J209" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K209" s="5" t="n">
+        <v>70738800</v>
+      </c>
+      <c r="L209" s="5" t="n">
+        <v>41056</v>
+      </c>
+      <c r="M209" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N209" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="3" t="inlineStr">
+        <is>
+          <t>5座</t>
+        </is>
+      </c>
+      <c r="B210" s="3" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C210" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D210" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E210" s="4" t="n">
+        <v>1221</v>
+      </c>
+      <c r="F210" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G210" s="3" t="inlineStr">
+        <is>
+          <t>2016-05-05</t>
+        </is>
+      </c>
+      <c r="H210" s="5" t="n">
+        <v>39468600</v>
+      </c>
+      <c r="I210" s="5" t="n">
+        <v>32325</v>
+      </c>
+      <c r="J210" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K210" s="5" t="n">
+        <v>39468600</v>
+      </c>
+      <c r="L210" s="5" t="n">
+        <v>32325</v>
+      </c>
+      <c r="M210" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N210" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="3" t="inlineStr">
+        <is>
+          <t>5座</t>
+        </is>
+      </c>
+      <c r="B211" s="3" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C211" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D211" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E211" s="4" t="n">
+        <v>1320</v>
+      </c>
+      <c r="F211" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G211" s="3" t="inlineStr">
+        <is>
+          <t>2016-05-13</t>
+        </is>
+      </c>
+      <c r="H211" s="5" t="n">
+        <v>42946400</v>
+      </c>
+      <c r="I211" s="5" t="n">
+        <v>32535</v>
+      </c>
+      <c r="J211" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K211" s="5" t="n">
+        <v>42946400</v>
+      </c>
+      <c r="L211" s="5" t="n">
+        <v>32535</v>
+      </c>
+      <c r="M211" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N211" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="3" t="inlineStr">
+        <is>
+          <t>5座</t>
+        </is>
+      </c>
+      <c r="B212" s="3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C212" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D212" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E212" s="4" t="n">
+        <v>1160</v>
+      </c>
+      <c r="F212" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G212" s="3" t="inlineStr">
+        <is>
+          <t>2016-05-11</t>
+        </is>
+      </c>
+      <c r="H212" s="5" t="n">
+        <v>38407700</v>
+      </c>
+      <c r="I212" s="5" t="n">
+        <v>33110</v>
+      </c>
+      <c r="J212" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K212" s="5" t="n">
+        <v>38407700</v>
+      </c>
+      <c r="L212" s="5" t="n">
+        <v>33110</v>
+      </c>
+      <c r="M212" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N212" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="3" t="inlineStr">
+        <is>
+          <t>5座</t>
+        </is>
+      </c>
+      <c r="B213" s="3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C213" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D213" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E213" s="4" t="n">
+        <v>1723</v>
+      </c>
+      <c r="F213" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G213" s="3" t="inlineStr">
+        <is>
+          <t>2019-01-31</t>
+        </is>
+      </c>
+      <c r="H213" s="5" t="n">
+        <v>71444000</v>
+      </c>
+      <c r="I213" s="5" t="n">
+        <v>41465</v>
+      </c>
+      <c r="J213" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K213" s="5" t="n">
+        <v>71444000</v>
+      </c>
+      <c r="L213" s="5" t="n">
+        <v>41465</v>
+      </c>
+      <c r="M213" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N213" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="3" t="inlineStr">
+        <is>
+          <t>5座</t>
+        </is>
+      </c>
+      <c r="B214" s="3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C214" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D214" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E214" s="4" t="n">
+        <v>1221</v>
+      </c>
+      <c r="F214" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G214" s="3" t="inlineStr">
+        <is>
+          <t>2016-04-29</t>
+        </is>
+      </c>
+      <c r="H214" s="5" t="n">
+        <v>38962000</v>
+      </c>
+      <c r="I214" s="5" t="n">
+        <v>31910</v>
+      </c>
+      <c r="J214" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K214" s="5" t="n">
+        <v>38962000</v>
+      </c>
+      <c r="L214" s="5" t="n">
+        <v>31910</v>
+      </c>
+      <c r="M214" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N214" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="3" t="inlineStr">
+        <is>
+          <t>5座</t>
+        </is>
+      </c>
+      <c r="B215" s="3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C215" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D215" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E215" s="4" t="n">
+        <v>1320</v>
+      </c>
+      <c r="F215" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G215" s="3" t="inlineStr">
+        <is>
+          <t>2016-05-12</t>
+        </is>
+      </c>
+      <c r="H215" s="5" t="n">
+        <v>42732700</v>
+      </c>
+      <c r="I215" s="5" t="n">
+        <v>32373</v>
+      </c>
+      <c r="J215" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K215" s="5" t="n">
+        <v>42732700</v>
+      </c>
+      <c r="L215" s="5" t="n">
+        <v>32373</v>
+      </c>
+      <c r="M215" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N215" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="3" t="inlineStr">
+        <is>
+          <t>5座</t>
+        </is>
+      </c>
+      <c r="B216" s="3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C216" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D216" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E216" s="4" t="n">
+        <v>1160</v>
+      </c>
+      <c r="F216" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G216" s="3" t="inlineStr">
+        <is>
+          <t>2016-05-12</t>
+        </is>
+      </c>
+      <c r="H216" s="5" t="n">
+        <v>38197600</v>
+      </c>
+      <c r="I216" s="5" t="n">
+        <v>32929</v>
+      </c>
+      <c r="J216" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K216" s="5" t="n">
+        <v>38197600</v>
+      </c>
+      <c r="L216" s="5" t="n">
+        <v>32929</v>
+      </c>
+      <c r="M216" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N216" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="3" t="inlineStr">
+        <is>
+          <t>5座</t>
+        </is>
+      </c>
+      <c r="B217" s="3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C217" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D217" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E217" s="4" t="n">
+        <v>1723</v>
+      </c>
+      <c r="F217" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G217" s="3" t="inlineStr">
+        <is>
+          <t>2019-01-15</t>
+        </is>
+      </c>
+      <c r="H217" s="5" t="n">
+        <v>63585000</v>
+      </c>
+      <c r="I217" s="5" t="n">
+        <v>36904</v>
+      </c>
+      <c r="J217" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K217" s="5" t="n">
+        <v>63585000</v>
+      </c>
+      <c r="L217" s="5" t="n">
+        <v>36904</v>
+      </c>
+      <c r="M217" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N217" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="3" t="inlineStr">
+        <is>
+          <t>5座</t>
+        </is>
+      </c>
+      <c r="B218" s="3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C218" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D218" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E218" s="4" t="n">
+        <v>1316</v>
+      </c>
+      <c r="F218" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G218" s="3" t="inlineStr">
+        <is>
+          <t>2016-04-15</t>
+        </is>
+      </c>
+      <c r="H218" s="5" t="n">
+        <v>76431800</v>
+      </c>
+      <c r="I218" s="5" t="n">
+        <v>58079</v>
+      </c>
+      <c r="J218" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K218" s="5" t="n">
+        <v>76431800</v>
+      </c>
+      <c r="L218" s="5" t="n">
+        <v>58079</v>
+      </c>
+      <c r="M218" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N218" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="3" t="inlineStr">
+        <is>
+          <t>5座</t>
+        </is>
+      </c>
+      <c r="B219" s="3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C219" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D219" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E219" s="4" t="n">
+        <v>1320</v>
+      </c>
+      <c r="F219" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G219" s="3" t="inlineStr">
+        <is>
+          <t>2016-04-29</t>
+        </is>
+      </c>
+      <c r="H219" s="5" t="n">
+        <v>41895500</v>
+      </c>
+      <c r="I219" s="5" t="n">
+        <v>31739</v>
+      </c>
+      <c r="J219" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K219" s="5" t="n">
+        <v>41895500</v>
+      </c>
+      <c r="L219" s="5" t="n">
+        <v>31739</v>
+      </c>
+      <c r="M219" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N219" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="3" t="inlineStr">
+        <is>
+          <t>5座</t>
+        </is>
+      </c>
+      <c r="B220" s="3" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C220" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D220" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E220" s="4" t="n">
+        <v>1160</v>
+      </c>
+      <c r="F220" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G220" s="3" t="inlineStr">
+        <is>
+          <t>2016-04-15</t>
+        </is>
+      </c>
+      <c r="H220" s="5" t="n">
+        <v>76431800</v>
+      </c>
+      <c r="I220" s="5" t="n">
+        <v>65889</v>
+      </c>
+      <c r="J220" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K220" s="5" t="n">
+        <v>76431800</v>
+      </c>
+      <c r="L220" s="5" t="n">
+        <v>65889</v>
+      </c>
+      <c r="M220" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N220" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="3" t="inlineStr">
+        <is>
+          <t>5座</t>
+        </is>
+      </c>
+      <c r="B221" s="3" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C221" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D221" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E221" s="4" t="n">
+        <v>1723</v>
+      </c>
+      <c r="F221" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G221" s="3" t="inlineStr">
+        <is>
+          <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="H221" s="5" t="n">
+        <v>53423338</v>
+      </c>
+      <c r="I221" s="5" t="n">
+        <v>31006</v>
+      </c>
+      <c r="J221" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K221" s="5" t="n">
+        <v>53423338</v>
+      </c>
+      <c r="L221" s="5" t="n">
+        <v>31006</v>
+      </c>
+      <c r="M221" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N221" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="3" t="inlineStr">
+        <is>
+          <t>5座</t>
+        </is>
+      </c>
+      <c r="B222" s="3" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C222" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D222" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E222" s="4" t="n">
+        <v>1316</v>
+      </c>
+      <c r="F222" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G222" s="3" t="inlineStr">
+        <is>
+          <t>2016-05-09</t>
+        </is>
+      </c>
+      <c r="H222" s="5" t="n">
+        <v>37968500</v>
+      </c>
+      <c r="I222" s="5" t="n">
+        <v>28851</v>
+      </c>
+      <c r="J222" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K222" s="5" t="n">
+        <v>37968500</v>
+      </c>
+      <c r="L222" s="5" t="n">
+        <v>28851</v>
+      </c>
+      <c r="M222" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N222" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="3" t="inlineStr">
+        <is>
+          <t>5座</t>
+        </is>
+      </c>
+      <c r="B223" s="3" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C223" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D223" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E223" s="4" t="n">
+        <v>1320</v>
+      </c>
+      <c r="F223" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G223" s="3" t="inlineStr">
+        <is>
+          <t>2016-05-17</t>
+        </is>
+      </c>
+      <c r="H223" s="5" t="n">
+        <v>41964900</v>
+      </c>
+      <c r="I223" s="5" t="n">
+        <v>31792</v>
+      </c>
+      <c r="J223" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K223" s="5" t="n">
+        <v>41964900</v>
+      </c>
+      <c r="L223" s="5" t="n">
+        <v>31792</v>
+      </c>
+      <c r="M223" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N223" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="3" t="inlineStr">
+        <is>
+          <t>5座</t>
+        </is>
+      </c>
+      <c r="B224" s="3" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C224" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D224" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E224" s="4" t="n">
+        <v>1160</v>
+      </c>
+      <c r="F224" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G224" s="3" t="inlineStr">
+        <is>
+          <t>2016-05-18</t>
+        </is>
+      </c>
+      <c r="H224" s="5" t="n">
+        <v>37816800</v>
+      </c>
+      <c r="I224" s="5" t="n">
+        <v>32601</v>
+      </c>
+      <c r="J224" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K224" s="5" t="n">
+        <v>37816800</v>
+      </c>
+      <c r="L224" s="5" t="n">
+        <v>32601</v>
+      </c>
+      <c r="M224" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N224" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="3" t="inlineStr">
+        <is>
+          <t>5座</t>
+        </is>
+      </c>
+      <c r="B225" s="3" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C225" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D225" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E225" s="4" t="n">
+        <v>1723</v>
+      </c>
+      <c r="F225" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G225" s="3" t="inlineStr">
+        <is>
+          <t>2019-01-07</t>
+        </is>
+      </c>
+      <c r="H225" s="5" t="n">
+        <v>62677000</v>
+      </c>
+      <c r="I225" s="5" t="n">
+        <v>36377</v>
+      </c>
+      <c r="J225" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K225" s="5" t="n">
+        <v>62677000</v>
+      </c>
+      <c r="L225" s="5" t="n">
+        <v>36377</v>
+      </c>
+      <c r="M225" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N225" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="3" t="inlineStr">
+        <is>
+          <t>5座</t>
+        </is>
+      </c>
+      <c r="B226" s="3" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C226" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D226" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E226" s="4" t="n">
+        <v>1316</v>
+      </c>
+      <c r="F226" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G226" s="3" t="inlineStr">
+        <is>
+          <t>2016-05-09</t>
+        </is>
+      </c>
+      <c r="H226" s="5" t="n">
+        <v>37592500</v>
+      </c>
+      <c r="I226" s="5" t="n">
+        <v>28566</v>
+      </c>
+      <c r="J226" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K226" s="5" t="n">
+        <v>37592500</v>
+      </c>
+      <c r="L226" s="5" t="n">
+        <v>28566</v>
+      </c>
+      <c r="M226" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N226" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="3" t="inlineStr">
+        <is>
+          <t>5座</t>
+        </is>
+      </c>
+      <c r="B227" s="3" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C227" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D227" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E227" s="4" t="n">
+        <v>1320</v>
+      </c>
+      <c r="F227" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G227" s="3" t="inlineStr">
+        <is>
+          <t>2016-05-13</t>
+        </is>
+      </c>
+      <c r="H227" s="5" t="n">
+        <v>41549400</v>
+      </c>
+      <c r="I227" s="5" t="n">
+        <v>31477</v>
+      </c>
+      <c r="J227" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K227" s="5" t="n">
+        <v>41549400</v>
+      </c>
+      <c r="L227" s="5" t="n">
+        <v>31477</v>
+      </c>
+      <c r="M227" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N227" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="3" t="inlineStr">
+        <is>
+          <t>5座</t>
+        </is>
+      </c>
+      <c r="B228" s="3" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C228" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D228" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E228" s="4" t="n">
+        <v>1160</v>
+      </c>
+      <c r="F228" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G228" s="3" t="inlineStr">
+        <is>
+          <t>2016-05-13</t>
+        </is>
+      </c>
+      <c r="H228" s="5" t="n">
+        <v>36529200</v>
+      </c>
+      <c r="I228" s="5" t="n">
+        <v>31491</v>
+      </c>
+      <c r="J228" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K228" s="5" t="n">
+        <v>36529200</v>
+      </c>
+      <c r="L228" s="5" t="n">
+        <v>31491</v>
+      </c>
+      <c r="M228" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N228" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="3" t="inlineStr">
+        <is>
+          <t>5座</t>
+        </is>
+      </c>
+      <c r="B229" s="3" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C229" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D229" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E229" s="4" t="n">
+        <v>1723</v>
+      </c>
+      <c r="F229" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G229" s="3" t="inlineStr">
+        <is>
+          <t>2019-01-17</t>
+        </is>
+      </c>
+      <c r="H229" s="5" t="n">
+        <v>64512640</v>
+      </c>
+      <c r="I229" s="5" t="n">
+        <v>37442</v>
+      </c>
+      <c r="J229" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K229" s="5" t="n">
+        <v>64512640</v>
+      </c>
+      <c r="L229" s="5" t="n">
+        <v>37442</v>
+      </c>
+      <c r="M229" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N229" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="3" t="inlineStr">
+        <is>
+          <t>5座</t>
+        </is>
+      </c>
+      <c r="B230" s="3" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C230" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D230" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E230" s="4" t="n">
+        <v>1221</v>
+      </c>
+      <c r="F230" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G230" s="3" t="inlineStr">
+        <is>
+          <t>2016-05-17</t>
+        </is>
+      </c>
+      <c r="H230" s="5" t="n">
+        <v>37000500</v>
+      </c>
+      <c r="I230" s="5" t="n">
+        <v>30303</v>
+      </c>
+      <c r="J230" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K230" s="5" t="n">
+        <v>37000500</v>
+      </c>
+      <c r="L230" s="5" t="n">
+        <v>30303</v>
+      </c>
+      <c r="M230" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N230" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="3" t="inlineStr">
+        <is>
+          <t>5座</t>
+        </is>
+      </c>
+      <c r="B231" s="3" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C231" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D231" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E231" s="4" t="n">
+        <v>1320</v>
+      </c>
+      <c r="F231" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G231" s="3" t="inlineStr">
+        <is>
+          <t>2016-05-05</t>
+        </is>
+      </c>
+      <c r="H231" s="5" t="n">
+        <v>40105600</v>
+      </c>
+      <c r="I231" s="5" t="n">
+        <v>30383</v>
+      </c>
+      <c r="J231" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K231" s="5" t="n">
+        <v>40105600</v>
+      </c>
+      <c r="L231" s="5" t="n">
+        <v>30383</v>
+      </c>
+      <c r="M231" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N231" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="3" t="inlineStr">
+        <is>
+          <t>5座</t>
+        </is>
+      </c>
+      <c r="B232" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C232" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D232" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E232" s="4" t="n">
+        <v>1160</v>
+      </c>
+      <c r="F232" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G232" s="3" t="inlineStr">
+        <is>
+          <t>2016-05-16</t>
+        </is>
+      </c>
+      <c r="H232" s="5" t="n">
+        <v>35396400</v>
+      </c>
+      <c r="I232" s="5" t="n">
+        <v>30514</v>
+      </c>
+      <c r="J232" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K232" s="5" t="n">
+        <v>35396400</v>
+      </c>
+      <c r="L232" s="5" t="n">
+        <v>30514</v>
+      </c>
+      <c r="M232" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N232" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="3" t="inlineStr">
+        <is>
+          <t>5座</t>
+        </is>
+      </c>
+      <c r="B233" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C233" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D233" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E233" s="4" t="n">
+        <v>1723</v>
+      </c>
+      <c r="F233" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G233" s="3" t="inlineStr">
+        <is>
+          <t>2019-01-17</t>
+        </is>
+      </c>
+      <c r="H233" s="5" t="n">
+        <v>68018820</v>
+      </c>
+      <c r="I233" s="5" t="n">
+        <v>39477</v>
+      </c>
+      <c r="J233" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K233" s="5" t="n">
+        <v>68018820</v>
+      </c>
+      <c r="L233" s="5" t="n">
+        <v>39477</v>
+      </c>
+      <c r="M233" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N233" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="3" t="inlineStr">
+        <is>
+          <t>5座</t>
+        </is>
+      </c>
+      <c r="B234" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C234" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D234" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E234" s="4" t="n">
+        <v>1316</v>
+      </c>
+      <c r="F234" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G234" s="3" t="inlineStr">
+        <is>
+          <t>2016-05-13</t>
+        </is>
+      </c>
+      <c r="H234" s="5" t="n">
+        <v>36525700</v>
+      </c>
+      <c r="I234" s="5" t="n">
+        <v>27755</v>
+      </c>
+      <c r="J234" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K234" s="5" t="n">
+        <v>36525700</v>
+      </c>
+      <c r="L234" s="5" t="n">
+        <v>27755</v>
+      </c>
+      <c r="M234" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N234" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="3" t="inlineStr">
+        <is>
+          <t>5座</t>
+        </is>
+      </c>
+      <c r="B235" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C235" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D235" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E235" s="4" t="n">
+        <v>1320</v>
+      </c>
+      <c r="F235" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G235" s="3" t="inlineStr">
+        <is>
+          <t>2016-05-06</t>
+        </is>
+      </c>
+      <c r="H235" s="5" t="n">
+        <v>39396400</v>
+      </c>
+      <c r="I235" s="5" t="n">
+        <v>29846</v>
+      </c>
+      <c r="J235" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K235" s="5" t="n">
+        <v>39396400</v>
+      </c>
+      <c r="L235" s="5" t="n">
+        <v>29846</v>
+      </c>
+      <c r="M235" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N235" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="3" t="inlineStr">
+        <is>
+          <t>5座</t>
+        </is>
+      </c>
+      <c r="B236" s="3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C236" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D236" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E236" s="4" t="n">
+        <v>1065</v>
+      </c>
+      <c r="F236" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G236" s="3" t="inlineStr">
+        <is>
+          <t>2016-05-13</t>
+        </is>
+      </c>
+      <c r="H236" s="5" t="n">
+        <v>35290300</v>
+      </c>
+      <c r="I236" s="5" t="n">
+        <v>33136</v>
+      </c>
+      <c r="J236" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K236" s="5" t="n">
+        <v>35290300</v>
+      </c>
+      <c r="L236" s="5" t="n">
+        <v>33136</v>
+      </c>
+      <c r="M236" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N236" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="3" t="inlineStr">
+        <is>
+          <t>5座</t>
+        </is>
+      </c>
+      <c r="B237" s="3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C237" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D237" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E237" s="4" t="n">
+        <v>1723</v>
+      </c>
+      <c r="F237" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G237" s="3" t="inlineStr">
+        <is>
+          <t>2019-01-07</t>
+        </is>
+      </c>
+      <c r="H237" s="5" t="n">
+        <v>58143200</v>
+      </c>
+      <c r="I237" s="5" t="n">
+        <v>33745</v>
+      </c>
+      <c r="J237" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K237" s="5" t="n">
+        <v>58143200</v>
+      </c>
+      <c r="L237" s="5" t="n">
+        <v>33745</v>
+      </c>
+      <c r="M237" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N237" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="3" t="inlineStr">
+        <is>
+          <t>5座</t>
+        </is>
+      </c>
+      <c r="B238" s="3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C238" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D238" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E238" s="4" t="n">
+        <v>1316</v>
+      </c>
+      <c r="F238" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G238" s="3" t="inlineStr">
+        <is>
+          <t>2016-05-17</t>
+        </is>
+      </c>
+      <c r="H238" s="5" t="n">
+        <v>36416100</v>
+      </c>
+      <c r="I238" s="5" t="n">
+        <v>27672</v>
+      </c>
+      <c r="J238" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K238" s="5" t="n">
+        <v>36416100</v>
+      </c>
+      <c r="L238" s="5" t="n">
+        <v>27672</v>
+      </c>
+      <c r="M238" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N238" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="3" t="inlineStr">
+        <is>
+          <t>5座</t>
+        </is>
+      </c>
+      <c r="B239" s="3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C239" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D239" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E239" s="4" t="n">
+        <v>1320</v>
+      </c>
+      <c r="F239" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G239" s="3" t="inlineStr">
+        <is>
+          <t>2016-05-05</t>
+        </is>
+      </c>
+      <c r="H239" s="5" t="n">
+        <v>39278300</v>
+      </c>
+      <c r="I239" s="5" t="n">
+        <v>29756</v>
+      </c>
+      <c r="J239" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K239" s="5" t="n">
+        <v>39278300</v>
+      </c>
+      <c r="L239" s="5" t="n">
+        <v>29756</v>
+      </c>
+      <c r="M239" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N239" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="3" t="inlineStr">
+        <is>
+          <t>5座</t>
+        </is>
+      </c>
+      <c r="B240" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C240" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D240" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E240" s="4" t="n">
+        <v>1160</v>
+      </c>
+      <c r="F240" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G240" s="3" t="inlineStr">
+        <is>
+          <t>2016-05-12</t>
+        </is>
+      </c>
+      <c r="H240" s="5" t="n">
+        <v>35007900</v>
+      </c>
+      <c r="I240" s="5" t="n">
+        <v>30179</v>
+      </c>
+      <c r="J240" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K240" s="5" t="n">
+        <v>35007900</v>
+      </c>
+      <c r="L240" s="5" t="n">
+        <v>30179</v>
+      </c>
+      <c r="M240" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N240" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="3" t="inlineStr">
+        <is>
+          <t>5座</t>
+        </is>
+      </c>
+      <c r="B241" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C241" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D241" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E241" s="4" t="n">
+        <v>1723</v>
+      </c>
+      <c r="F241" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G241" s="3" t="inlineStr">
+        <is>
+          <t>2019-01-17</t>
+        </is>
+      </c>
+      <c r="H241" s="5" t="n">
+        <v>58150600</v>
+      </c>
+      <c r="I241" s="5" t="n">
+        <v>33750</v>
+      </c>
+      <c r="J241" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K241" s="5" t="n">
+        <v>58150600</v>
+      </c>
+      <c r="L241" s="5" t="n">
+        <v>33750</v>
+      </c>
+      <c r="M241" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N241" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="3" t="inlineStr">
+        <is>
+          <t>5座</t>
+        </is>
+      </c>
+      <c r="B242" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C242" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D242" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E242" s="4" t="n">
+        <v>1316</v>
+      </c>
+      <c r="F242" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G242" s="3" t="inlineStr">
+        <is>
+          <t>2016-04-28</t>
+        </is>
+      </c>
+      <c r="H242" s="5" t="n">
+        <v>35760600</v>
+      </c>
+      <c r="I242" s="5" t="n">
+        <v>27174</v>
+      </c>
+      <c r="J242" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K242" s="5" t="n">
+        <v>35760600</v>
+      </c>
+      <c r="L242" s="5" t="n">
+        <v>27174</v>
+      </c>
+      <c r="M242" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N242" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="3" t="inlineStr">
+        <is>
+          <t>5座</t>
+        </is>
+      </c>
+      <c r="B243" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C243" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D243" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E243" s="4" t="n">
+        <v>1320</v>
+      </c>
+      <c r="F243" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G243" s="3" t="inlineStr">
+        <is>
+          <t>2016-04-28</t>
+        </is>
+      </c>
+      <c r="H243" s="5" t="n">
+        <v>38374900</v>
+      </c>
+      <c r="I243" s="5" t="n">
+        <v>29072</v>
+      </c>
+      <c r="J243" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K243" s="5" t="n">
+        <v>38374900</v>
+      </c>
+      <c r="L243" s="5" t="n">
+        <v>29072</v>
+      </c>
+      <c r="M243" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N243" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="3" t="inlineStr">
+        <is>
+          <t>5座</t>
+        </is>
+      </c>
+      <c r="B244" s="3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C244" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D244" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E244" s="4" t="n">
+        <v>1160</v>
+      </c>
+      <c r="F244" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G244" s="3" t="inlineStr">
+        <is>
+          <t>2016-05-11</t>
+        </is>
+      </c>
+      <c r="H244" s="5" t="n">
+        <v>34031200</v>
+      </c>
+      <c r="I244" s="5" t="n">
+        <v>29337</v>
+      </c>
+      <c r="J244" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K244" s="5" t="n">
+        <v>34031200</v>
+      </c>
+      <c r="L244" s="5" t="n">
+        <v>29337</v>
+      </c>
+      <c r="M244" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N244" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="3" t="inlineStr">
+        <is>
+          <t>5座</t>
+        </is>
+      </c>
+      <c r="B245" s="3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C245" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D245" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E245" s="4" t="n">
+        <v>1723</v>
+      </c>
+      <c r="F245" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G245" s="3" t="inlineStr">
+        <is>
+          <t>2016-05-09</t>
+        </is>
+      </c>
+      <c r="H245" s="5" t="n">
+        <v>56633900</v>
+      </c>
+      <c r="I245" s="5" t="n">
+        <v>32869</v>
+      </c>
+      <c r="J245" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K245" s="5" t="n">
+        <v>56633900</v>
+      </c>
+      <c r="L245" s="5" t="n">
+        <v>32869</v>
+      </c>
+      <c r="M245" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N245" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="3" t="inlineStr">
+        <is>
+          <t>5座</t>
+        </is>
+      </c>
+      <c r="B246" s="3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C246" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D246" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E246" s="4" t="n">
+        <v>1316</v>
+      </c>
+      <c r="F246" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G246" s="3" t="inlineStr">
+        <is>
+          <t>2016-04-29</t>
+        </is>
+      </c>
+      <c r="H246" s="5" t="n">
+        <v>35117000</v>
+      </c>
+      <c r="I246" s="5" t="n">
+        <v>26685</v>
+      </c>
+      <c r="J246" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K246" s="5" t="n">
+        <v>35117000</v>
+      </c>
+      <c r="L246" s="5" t="n">
+        <v>26685</v>
+      </c>
+      <c r="M246" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N246" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="3" t="inlineStr">
+        <is>
+          <t>5座</t>
+        </is>
+      </c>
+      <c r="B247" s="3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C247" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D247" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E247" s="4" t="n">
+        <v>1320</v>
+      </c>
+      <c r="F247" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G247" s="3" t="inlineStr">
+        <is>
+          <t>2016-04-27</t>
+        </is>
+      </c>
+      <c r="H247" s="5" t="n">
+        <v>37108500</v>
+      </c>
+      <c r="I247" s="5" t="n">
+        <v>28112</v>
+      </c>
+      <c r="J247" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K247" s="5" t="n">
+        <v>37108500</v>
+      </c>
+      <c r="L247" s="5" t="n">
+        <v>28112</v>
+      </c>
+      <c r="M247" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N247" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="3" t="inlineStr">
+        <is>
+          <t>5座</t>
+        </is>
+      </c>
+      <c r="B248" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C248" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D248" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E248" s="4" t="n">
+        <v>1065</v>
+      </c>
+      <c r="F248" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G248" s="3" t="inlineStr">
+        <is>
+          <t>2016-05-12</t>
+        </is>
+      </c>
+      <c r="H248" s="5" t="n">
+        <v>33078400</v>
+      </c>
+      <c r="I248" s="5" t="n">
+        <v>31060</v>
+      </c>
+      <c r="J248" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K248" s="5" t="n">
+        <v>33078400</v>
+      </c>
+      <c r="L248" s="5" t="n">
+        <v>31060</v>
+      </c>
+      <c r="M248" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N248" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="3" t="inlineStr">
+        <is>
+          <t>5座</t>
+        </is>
+      </c>
+      <c r="B249" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C249" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D249" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E249" s="4" t="n">
+        <v>1723</v>
+      </c>
+      <c r="F249" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G249" s="3" t="inlineStr">
+        <is>
+          <t>2016-05-10</t>
+        </is>
+      </c>
+      <c r="H249" s="5" t="n">
+        <v>54481700</v>
+      </c>
+      <c r="I249" s="5" t="n">
+        <v>31620</v>
+      </c>
+      <c r="J249" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K249" s="5" t="n">
+        <v>54481700</v>
+      </c>
+      <c r="L249" s="5" t="n">
+        <v>31620</v>
+      </c>
+      <c r="M249" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N249" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="3" t="inlineStr">
+        <is>
+          <t>5座</t>
+        </is>
+      </c>
+      <c r="B250" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C250" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D250" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E250" s="4" t="n">
+        <v>1221</v>
+      </c>
+      <c r="F250" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G250" s="3" t="inlineStr">
+        <is>
+          <t>2016-04-15</t>
+        </is>
+      </c>
+      <c r="H250" s="5" t="n">
+        <v>33606900</v>
+      </c>
+      <c r="I250" s="5" t="n">
+        <v>27524</v>
+      </c>
+      <c r="J250" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K250" s="5" t="n">
+        <v>33606900</v>
+      </c>
+      <c r="L250" s="5" t="n">
+        <v>27524</v>
+      </c>
+      <c r="M250" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N250" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="3" t="inlineStr">
+        <is>
+          <t>5座</t>
+        </is>
+      </c>
+      <c r="B251" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C251" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D251" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E251" s="4" t="n">
+        <v>1320</v>
+      </c>
+      <c r="F251" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G251" s="3" t="inlineStr">
+        <is>
+          <t>2016-05-12</t>
+        </is>
+      </c>
+      <c r="H251" s="5" t="n">
+        <v>34770700</v>
+      </c>
+      <c r="I251" s="5" t="n">
+        <v>26341</v>
+      </c>
+      <c r="J251" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K251" s="5" t="n">
+        <v>34770700</v>
+      </c>
+      <c r="L251" s="5" t="n">
+        <v>26341</v>
+      </c>
+      <c r="M251" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N251" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="3" t="inlineStr">
+        <is>
+          <t>5座</t>
+        </is>
+      </c>
+      <c r="B252" s="3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C252" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D252" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E252" s="4" t="n">
+        <v>1160</v>
+      </c>
+      <c r="F252" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G252" s="3" t="inlineStr">
+        <is>
+          <t>2016-05-17</t>
+        </is>
+      </c>
+      <c r="H252" s="5" t="n">
+        <v>31556800</v>
+      </c>
+      <c r="I252" s="5" t="n">
+        <v>27204</v>
+      </c>
+      <c r="J252" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K252" s="5" t="n">
+        <v>31556800</v>
+      </c>
+      <c r="L252" s="5" t="n">
+        <v>27204</v>
+      </c>
+      <c r="M252" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N252" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="3" t="inlineStr">
+        <is>
+          <t>5座</t>
+        </is>
+      </c>
+      <c r="B253" s="3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C253" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D253" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E253" s="4" t="n">
+        <v>1723</v>
+      </c>
+      <c r="F253" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G253" s="3" t="inlineStr">
+        <is>
+          <t>2016-05-20</t>
+        </is>
+      </c>
+      <c r="H253" s="5" t="n">
+        <v>52792900</v>
+      </c>
+      <c r="I253" s="5" t="n">
+        <v>30640</v>
+      </c>
+      <c r="J253" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K253" s="5" t="n">
+        <v>52792900</v>
+      </c>
+      <c r="L253" s="5" t="n">
+        <v>30640</v>
+      </c>
+      <c r="M253" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N253" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="3" t="inlineStr">
+        <is>
+          <t>5座</t>
+        </is>
+      </c>
+      <c r="B254" s="3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C254" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D254" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E254" s="4" t="n">
+        <v>1316</v>
+      </c>
+      <c r="F254" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G254" s="3" t="inlineStr">
+        <is>
+          <t>2016-05-03</t>
+        </is>
+      </c>
+      <c r="H254" s="5" t="n">
+        <v>31388900</v>
+      </c>
+      <c r="I254" s="5" t="n">
+        <v>23852</v>
+      </c>
+      <c r="J254" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K254" s="5" t="n">
+        <v>31388900</v>
+      </c>
+      <c r="L254" s="5" t="n">
+        <v>23852</v>
+      </c>
+      <c r="M254" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N254" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="3" t="inlineStr">
+        <is>
+          <t>5座</t>
+        </is>
+      </c>
+      <c r="B255" s="3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C255" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D255" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E255" s="4" t="n">
+        <v>1320</v>
+      </c>
+      <c r="F255" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G255" s="3" t="inlineStr">
+        <is>
+          <t>2016-05-16</t>
+        </is>
+      </c>
+      <c r="H255" s="5" t="n">
+        <v>33171200</v>
+      </c>
+      <c r="I255" s="5" t="n">
+        <v>25130</v>
+      </c>
+      <c r="J255" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K255" s="5" t="n">
+        <v>33171200</v>
+      </c>
+      <c r="L255" s="5" t="n">
+        <v>25130</v>
+      </c>
+      <c r="M255" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N255" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="3" t="inlineStr">
+        <is>
+          <t>5座</t>
+        </is>
+      </c>
+      <c r="B256" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C256" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D256" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E256" s="4" t="n">
+        <v>1065</v>
+      </c>
+      <c r="F256" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G256" s="3" t="inlineStr">
+        <is>
+          <t>2016-05-18</t>
+        </is>
+      </c>
+      <c r="H256" s="5" t="n">
+        <v>30454700</v>
+      </c>
+      <c r="I256" s="5" t="n">
+        <v>28596</v>
+      </c>
+      <c r="J256" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K256" s="5" t="n">
+        <v>30454700</v>
+      </c>
+      <c r="L256" s="5" t="n">
+        <v>28596</v>
+      </c>
+      <c r="M256" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N256" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="3" t="inlineStr">
+        <is>
+          <t>5座</t>
+        </is>
+      </c>
+      <c r="B257" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C257" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D257" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E257" s="4" t="n">
+        <v>1723</v>
+      </c>
+      <c r="F257" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G257" s="3" t="inlineStr">
+        <is>
+          <t>2019-01-16</t>
+        </is>
+      </c>
+      <c r="H257" s="5" t="n">
+        <v>55342040</v>
+      </c>
+      <c r="I257" s="5" t="n">
+        <v>32120</v>
+      </c>
+      <c r="J257" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K257" s="5" t="n">
+        <v>55342040</v>
+      </c>
+      <c r="L257" s="5" t="n">
+        <v>32120</v>
+      </c>
+      <c r="M257" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N257" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="3" t="inlineStr">
+        <is>
+          <t>5座</t>
+        </is>
+      </c>
+      <c r="B258" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C258" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D258" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E258" s="4" t="n">
+        <v>1316</v>
+      </c>
+      <c r="F258" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G258" s="3" t="inlineStr">
+        <is>
+          <t>2016-04-29</t>
+        </is>
+      </c>
+      <c r="H258" s="5" t="n">
+        <v>29191600</v>
+      </c>
+      <c r="I258" s="5" t="n">
+        <v>22182</v>
+      </c>
+      <c r="J258" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K258" s="5" t="n">
+        <v>29191600</v>
+      </c>
+      <c r="L258" s="5" t="n">
+        <v>22182</v>
+      </c>
+      <c r="M258" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N258" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="3" t="inlineStr">
+        <is>
+          <t>5座</t>
+        </is>
+      </c>
+      <c r="B259" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C259" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D259" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E259" s="4" t="n">
+        <v>1320</v>
+      </c>
+      <c r="F259" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G259" s="3" t="inlineStr">
+        <is>
+          <t>2016-05-10</t>
+        </is>
+      </c>
+      <c r="H259" s="5" t="n">
+        <v>30849200</v>
+      </c>
+      <c r="I259" s="5" t="n">
+        <v>23371</v>
+      </c>
+      <c r="J259" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K259" s="5" t="n">
+        <v>30849200</v>
+      </c>
+      <c r="L259" s="5" t="n">
+        <v>23371</v>
+      </c>
+      <c r="M259" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N259" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="3" t="inlineStr">
+        <is>
+          <t>5座</t>
+        </is>
+      </c>
+      <c r="B260" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C260" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D260" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E260" s="4" t="n">
+        <v>1160</v>
+      </c>
+      <c r="F260" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G260" s="3" t="inlineStr">
+        <is>
+          <t>2016-05-16</t>
+        </is>
+      </c>
+      <c r="H260" s="5" t="n">
+        <v>28749300</v>
+      </c>
+      <c r="I260" s="5" t="n">
+        <v>24784</v>
+      </c>
+      <c r="J260" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K260" s="5" t="n">
+        <v>28749300</v>
+      </c>
+      <c r="L260" s="5" t="n">
+        <v>24784</v>
+      </c>
+      <c r="M260" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N260" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="3" t="inlineStr">
+        <is>
+          <t>5座</t>
+        </is>
+      </c>
+      <c r="B261" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C261" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D261" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E261" s="4" t="n">
+        <v>1723</v>
+      </c>
+      <c r="F261" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G261" s="3" t="inlineStr">
+        <is>
+          <t>2019-01-04</t>
+        </is>
+      </c>
+      <c r="H261" s="5" t="n">
+        <v>48712000</v>
+      </c>
+      <c r="I261" s="5" t="n">
+        <v>28272</v>
+      </c>
+      <c r="J261" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K261" s="5" t="n">
+        <v>48712000</v>
+      </c>
+      <c r="L261" s="5" t="n">
+        <v>28272</v>
+      </c>
+      <c r="M261" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N261" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="3" t="inlineStr">
+        <is>
+          <t>5座</t>
+        </is>
+      </c>
+      <c r="B262" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C262" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D262" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E262" s="4" t="n">
+        <v>1316</v>
+      </c>
+      <c r="F262" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G262" s="3" t="inlineStr">
+        <is>
+          <t>2016-04-28</t>
+        </is>
+      </c>
+      <c r="H262" s="5" t="n">
+        <v>29016400</v>
+      </c>
+      <c r="I262" s="5" t="n">
+        <v>22049</v>
+      </c>
+      <c r="J262" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K262" s="5" t="n">
+        <v>29016400</v>
+      </c>
+      <c r="L262" s="5" t="n">
+        <v>22049</v>
+      </c>
+      <c r="M262" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N262" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="3" t="inlineStr">
+        <is>
+          <t>5座</t>
+        </is>
+      </c>
+      <c r="B263" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C263" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D263" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E263" s="4" t="n">
+        <v>1320</v>
+      </c>
+      <c r="F263" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G263" s="3" t="inlineStr">
+        <is>
+          <t>2016-04-15</t>
+        </is>
+      </c>
+      <c r="H263" s="5" t="n">
+        <v>30664100</v>
+      </c>
+      <c r="I263" s="5" t="n">
+        <v>23230</v>
+      </c>
+      <c r="J263" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K263" s="5" t="n">
+        <v>30664100</v>
+      </c>
+      <c r="L263" s="5" t="n">
+        <v>23230</v>
+      </c>
+      <c r="M263" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N263" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="3" t="inlineStr">
+        <is>
+          <t>5座</t>
+        </is>
+      </c>
+      <c r="B264" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C264" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D264" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E264" s="4" t="n">
+        <v>1160</v>
+      </c>
+      <c r="F264" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G264" s="3" t="inlineStr">
+        <is>
+          <t>2016-05-16</t>
+        </is>
+      </c>
+      <c r="H264" s="5" t="n">
+        <v>23286900</v>
+      </c>
+      <c r="I264" s="5" t="n">
+        <v>20075</v>
+      </c>
+      <c r="J264" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K264" s="5" t="n">
+        <v>23286900</v>
+      </c>
+      <c r="L264" s="5" t="n">
+        <v>20075</v>
+      </c>
+      <c r="M264" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N264" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="3" t="inlineStr">
+        <is>
+          <t>5座</t>
+        </is>
+      </c>
+      <c r="B265" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C265" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D265" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E265" s="4" t="n">
+        <v>1723</v>
+      </c>
+      <c r="F265" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G265" s="3" t="inlineStr">
+        <is>
+          <t>2016-05-13</t>
+        </is>
+      </c>
+      <c r="H265" s="5" t="n">
+        <v>38956200</v>
+      </c>
+      <c r="I265" s="5" t="n">
+        <v>22610</v>
+      </c>
+      <c r="J265" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K265" s="5" t="n">
+        <v>38956200</v>
+      </c>
+      <c r="L265" s="5" t="n">
+        <v>22610</v>
+      </c>
+      <c r="M265" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N265" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="3" t="inlineStr">
+        <is>
+          <t>5座</t>
+        </is>
+      </c>
+      <c r="B266" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C266" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D266" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E266" s="4" t="n">
+        <v>1221</v>
+      </c>
+      <c r="F266" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G266" s="3" t="inlineStr">
+        <is>
+          <t>2016-04-27</t>
+        </is>
+      </c>
+      <c r="H266" s="5" t="n">
+        <v>22105600</v>
+      </c>
+      <c r="I266" s="5" t="n">
+        <v>18105</v>
+      </c>
+      <c r="J266" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K266" s="5" t="n">
+        <v>22105600</v>
+      </c>
+      <c r="L266" s="5" t="n">
+        <v>18105</v>
+      </c>
+      <c r="M266" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N266" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="3" t="inlineStr">
+        <is>
+          <t>5座</t>
+        </is>
+      </c>
+      <c r="B267" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C267" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D267" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E267" s="4" t="n">
+        <v>1320</v>
+      </c>
+      <c r="F267" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G267" s="3" t="inlineStr">
+        <is>
+          <t>2016-05-19</t>
+        </is>
+      </c>
+      <c r="H267" s="5" t="n">
+        <v>25293900</v>
+      </c>
+      <c r="I267" s="5" t="n">
+        <v>19162</v>
+      </c>
+      <c r="J267" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K267" s="5" t="n">
+        <v>25293900</v>
+      </c>
+      <c r="L267" s="5" t="n">
+        <v>19162</v>
+      </c>
+      <c r="M267" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N267" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="3" t="inlineStr">
+        <is>
+          <t>5座</t>
+        </is>
+      </c>
+      <c r="B268" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C268" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D268" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E268" s="4" t="n">
+        <v>1143</v>
+      </c>
+      <c r="F268" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G268" s="3" t="inlineStr">
+        <is>
+          <t>2016-05-16</t>
+        </is>
+      </c>
+      <c r="H268" s="5" t="n">
+        <v>21729500</v>
+      </c>
+      <c r="I268" s="5" t="n">
+        <v>19011</v>
+      </c>
+      <c r="J268" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K268" s="5" t="n">
+        <v>21729500</v>
+      </c>
+      <c r="L268" s="5" t="n">
+        <v>19011</v>
+      </c>
+      <c r="M268" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N268" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="3" t="inlineStr">
+        <is>
+          <t>5座</t>
+        </is>
+      </c>
+      <c r="B269" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C269" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D269" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E269" s="4" t="n">
+        <v>1723</v>
+      </c>
+      <c r="F269" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G269" s="3" t="inlineStr">
+        <is>
+          <t>2016-05-16</t>
+        </is>
+      </c>
+      <c r="H269" s="5" t="n">
+        <v>39094700</v>
+      </c>
+      <c r="I269" s="5" t="n">
+        <v>22690</v>
+      </c>
+      <c r="J269" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K269" s="5" t="n">
+        <v>39094700</v>
+      </c>
+      <c r="L269" s="5" t="n">
+        <v>22690</v>
+      </c>
+      <c r="M269" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N269" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="3" t="inlineStr">
+        <is>
+          <t>5座</t>
+        </is>
+      </c>
+      <c r="B270" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C270" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D270" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E270" s="4" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F270" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G270" s="3" t="inlineStr">
+        <is>
+          <t>2016-05-17</t>
+        </is>
+      </c>
+      <c r="H270" s="5" t="n">
+        <v>25059000</v>
+      </c>
+      <c r="I270" s="5" t="n">
+        <v>19276</v>
+      </c>
+      <c r="J270" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K270" s="5" t="n">
+        <v>25059000</v>
+      </c>
+      <c r="L270" s="5" t="n">
+        <v>19276</v>
+      </c>
+      <c r="M270" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N270" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="3" t="inlineStr">
+        <is>
+          <t>5座</t>
+        </is>
+      </c>
+      <c r="B271" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C271" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D271" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E271" s="4" t="n">
+        <v>1150</v>
+      </c>
+      <c r="F271" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G271" s="3" t="inlineStr">
+        <is>
+          <t>2024-05-30</t>
+        </is>
+      </c>
+      <c r="H271" s="5" t="n">
+        <v>36231000</v>
+      </c>
+      <c r="I271" s="5" t="n">
+        <v>31505</v>
+      </c>
+      <c r="J271" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K271" s="5" t="n">
+        <v>36231000</v>
+      </c>
+      <c r="L271" s="5" t="n">
+        <v>31505</v>
+      </c>
+      <c r="M271" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N271" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="3" t="inlineStr">
+        <is>
+          <t>5座</t>
+        </is>
+      </c>
+      <c r="B272" s="3" t="inlineStr">
+        <is>
           <t>3&amp;4</t>
         </is>
       </c>
-      <c r="C205" s="3" t="inlineStr">
+      <c r="C272" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D272" s="3" t="inlineStr">
+        <is>
+          <t>2房</t>
+        </is>
+      </c>
+      <c r="E272" s="4" t="n">
+        <v>1970</v>
+      </c>
+      <c r="F272" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G272" s="3" t="inlineStr">
+        <is>
+          <t>2016-05-19</t>
+        </is>
+      </c>
+      <c r="H272" s="5" t="n">
+        <v>62774600</v>
+      </c>
+      <c r="I272" s="5" t="n">
+        <v>31865</v>
+      </c>
+      <c r="J272" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K272" s="5" t="n">
+        <v>62774600</v>
+      </c>
+      <c r="L272" s="5" t="n">
+        <v>31865</v>
+      </c>
+      <c r="M272" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N272" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="3" t="inlineStr">
+        <is>
+          <t>5座</t>
+        </is>
+      </c>
+      <c r="B273" s="3" t="inlineStr">
+        <is>
+          <t>3&amp;4</t>
+        </is>
+      </c>
+      <c r="C273" s="3" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D205" s="3" t="inlineStr">
+      <c r="D273" s="3" t="inlineStr">
         <is>
           <t>3房</t>
         </is>
       </c>
-      <c r="E205" s="4" t="n">
+      <c r="E273" s="4" t="n">
         <v>1929</v>
       </c>
-      <c r="F205" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G205" s="3" t="inlineStr">
+      <c r="F273" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G273" s="3" t="inlineStr">
         <is>
           <t>2016-04-08</t>
         </is>
       </c>
-      <c r="H205" s="5" t="n">
+      <c r="H273" s="5" t="n">
         <v>45931400</v>
       </c>
-      <c r="I205" s="5" t="n">
+      <c r="I273" s="5" t="n">
         <v>23811</v>
       </c>
-      <c r="J205" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K205" s="5" t="n">
+      <c r="J273" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K273" s="5" t="n">
         <v>45931400</v>
       </c>
-      <c r="L205" s="5" t="n">
+      <c r="L273" s="5" t="n">
         <v>23811</v>
       </c>
-      <c r="M205" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N205" s="3" t="inlineStr">
+      <c r="M273" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N273" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -14263,10 +18480,35 @@
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr"/>
+      <c r="C7" s="21" t="inlineStr"/>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>C | 1428呎 (4+房)
+$4207万
+$29,461/呎
+(16年-04月-20日)</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>D | 1237呎 (3房)
+$3534万
+$28,573/呎
+(16年-04月-20日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
           <t>22&amp;23</t>
         </is>
       </c>
-      <c r="B7" s="22" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>A | 2199呎 (4+房)
 $11391万
@@ -14274,7 +18516,7 @@
 (24年-04月-29日)</t>
         </is>
       </c>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t>B | 2361呎 (4+房)
 $12169万
@@ -14282,33 +18524,8 @@
 (16年-04月-22日)</t>
         </is>
       </c>
-      <c r="D7" s="21" t="inlineStr"/>
-      <c r="E7" s="21" t="inlineStr"/>
-    </row>
-    <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="B8" s="21" t="inlineStr"/>
-      <c r="C8" s="21" t="inlineStr"/>
-      <c r="D8" s="22" t="inlineStr">
-        <is>
-          <t>C | 1428呎 (4+房)
-$4207万
-$29,461/呎
-(16年-04月-20日)</t>
-        </is>
-      </c>
-      <c r="E8" s="22" t="inlineStr">
-        <is>
-          <t>D | 1237呎 (3房)
-$3534万
-$28,573/呎
-(16年-04月-20日)</t>
-        </is>
-      </c>
+      <c r="D8" s="21" t="inlineStr"/>
+      <c r="E8" s="21" t="inlineStr"/>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
@@ -14923,6 +19140,814 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
+          <t>3座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>A | 2681呎 (4+房)
+$15227万
+$56,795/呎
+(25年-11月-25日)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr"/>
+      <c r="D5" s="22" t="inlineStr">
+        <is>
+          <t>C | 1990呎 (3房)
+$12540万
+$63,015/呎
+(19年-11月-04日)</t>
+        </is>
+      </c>
+      <c r="E5" s="22" t="inlineStr">
+        <is>
+          <t>D | 2173呎 (3房)
+$7670万
+$35,298/呎
+(16年-05月-17日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr"/>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>C | 2128呎 (3房)
+$8248万
+$38,761/呎
+(16年-05月-16日)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr"/>
+      <c r="C7" s="21" t="inlineStr"/>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>C | 1237呎 (3房)
+$3250万
+$26,273/呎
+(24年-04月-16日)</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>D | 1428呎 (4+房)
+$4251万
+$29,770/呎
+(16年-04月-27日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>22&amp;23</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>A | 2265呎 (4+房)
+$15583万
+$68,797/呎
+(19年-07月-30日)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>B | 2199呎 (4+房)
+$14260万
+$64,849/呎
+(19年-02月-21日)</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr"/>
+      <c r="E8" s="21" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>A | 1708呎 (4+房)
+$7567万
+$44,304/呎
+(19年-02月-26日)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>B | 1738呎 (4+房)
+$6650万
+$38,262/呎
+(16年-04月-25日)</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>C | 1237呎 (3房)
+$7133万
+$57,666/呎
+(16年-04月-01日)</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>D | 1428呎 (4+房)
+$4238万
+$29,681/呎
+(16年-04月-27日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>A | 1708呎 (4+房)
+$7472万
+$43,746/呎
+(19年-01月-31日)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>B | 1738呎 (4+房)
+$6532万
+$37,585/呎
+(16年-05月-17日)</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>C | 1237呎 (3房)
+$3556万
+$28,747/呎
+(16年-04月-21日)</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>D | 1428呎 (4+房)
+$4226万
+$29,592/呎
+(16年-04月-27日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>A | 1708呎 (4+房)
+$6764万
+$39,600/呎
+(19年-01月-25日)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>B | 1738呎 (4+房)
+$6417万
+$36,921/呎
+(16年-05月-10日)</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>C | 1237呎 (3房)
+$3549万
+$28,689/呎
+(16年-04月-27日)</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>D | 1428呎 (4+房)
+$4213万
+$29,503/呎
+(16年-04月-27日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>A | 1708呎 (4+房)
+$13498万
+$79,030/呎
+(16年-04月-15日)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>B | 1738呎 (4+房)
+$13498万
+$77,666/呎
+(16年-04月-15日)</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>C | 1237呎 (3房)
+$3549万
+$28,689/呎
+(16年-05月-04日)</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t>D | 1428呎 (4+房)
+$4213万
+$29,503/呎
+(16年-05月-09日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>A | 1708呎 (4+房)
+$6662万
+$39,006/呎
+(23年-05月-05日)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>B | 1738呎 (4+房)
+$6192万
+$35,627/呎
+(16年-04月-21日)</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>C | 1237呎 (3房)
+$3535万
+$28,575/呎
+(16年-04月-21日)</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>D | 1428呎 (4+房)
+$4188万
+$29,328/呎
+(16年-04月-21日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 1708呎 (4+房)
+$6663万
+$39,009/呎
+(19年-01月-21日)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>B | 1738呎 (4+房)
+$6082万
+$34,997/呎
+(16年-05月-16日)</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>C | 1237呎 (3房)
+$3528万
+$28,518/呎
+(16年-04月-26日)</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>D | 1428呎 (4+房)
+$4175万
+$29,240/呎
+(16年-04月-19日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>A | 1708呎 (4+房)
+$6483万
+$37,957/呎
+(19年-01月-18日)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 1738呎 (4+房)
+$6064万
+$34,892/呎
+(16年-04月-29日)</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>C | 1237呎 (3房)
+$3517万
+$28,432/呎
+(16年-04月-29日)</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>D | 1428呎 (4+房)
+$4163万
+$29,152/呎
+(16年-05月-17日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>A | 1708呎 (4+房)
+$6290万
+$36,827/呎
+(16年-05月-09日)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>B | 1738呎 (4+房)
+$5864万
+$33,740/呎
+(16年-04月-25日)</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>C | 1237呎 (3房)
+$3454万
+$27,921/呎
+(16年-05月-13日)</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>D | 1428呎 (4+房)
+$4067万
+$28,482/呎
+(16年-04月-22日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>A | 1708呎 (4+房)
+$5890万
+$34,483/呎
+(19年-01月-22日)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>B | 1738呎 (4+房)
+$5436万
+$31,277/呎
+(16年-04月-28日)</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>C | 1237呎 (3房)
+$3340万
+$26,999/呎
+(16年-05月-05日)</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>D | 1428呎 (4+房)
+$3933万
+$27,542/呎
+(16年-05月-05日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 1708呎 (4+房)
+$5567万
+$32,593/呎
+(19年-03月-04日)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>B | 1738呎 (4+房)
+$4441万
+$25,554/呎
+(16年-05月-03日)</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>C | 1237呎 (3房)
+$3263万
+$26,378/呎
+(16年-04月-20日)</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>D | 1428呎 (4+房)
+$3842万
+$26,908/呎
+(16年-04月-26日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>A | 1708呎 (4+房)
+$8063万
+$47,206/呎
+(16年-04月-01日)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>B | 1738呎 (4+房)
+$8063万
+$46,391/呎
+(16年-04月-01日)</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>C | 1237呎 (3房)
+$3178万
+$25,692/呎
+(16年-04月-26日)</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
+        <is>
+          <t>D | 1428呎 (4+房)
+$3743万
+$26,209/呎
+(16年-04月-21日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>A | 1708呎 (4+房)
+$5332万
+$31,220/呎
+(19年-02月-01日)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>B | 1738呎 (4+房)
+$3891万
+$22,388/呎
+(16年-04月-22日)</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>C | 1237呎 (3房)
+$3115万
+$25,179/呎
+(16年-04月-25日)</t>
+        </is>
+      </c>
+      <c r="E20" s="22" t="inlineStr">
+        <is>
+          <t>D | 1428呎 (4+房)
+$3630万
+$25,422/呎
+(16年-04月-25日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>A | 1708呎 (4+房)
+$5188万
+$30,378/呎
+(19年-01月-11日)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>B | 1738呎 (4+房)
+$3790万
+$21,806/呎
+(16年-04月-28日)</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>C | 1237呎 (3房)
+$2800万
+$22,635/呎
+(16年-04月-20日)</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="inlineStr">
+        <is>
+          <t>D | 1428呎 (4+房)
+$3227万
+$22,600/呎
+(16年-04月-20日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>A | 1708呎 (4+房)
+$5049万
+$29,560/呎
+(19年-01月-15日)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>B | 1738呎 (4+房)
+$3127万
+$17,990/呎
+(16年-04月-20日)</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>C | 1237呎 (3房)
+$2082万
+$16,831/呎
+(16年-04月-19日)</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="inlineStr">
+        <is>
+          <t>D | 1428呎 (4+房)
+$2499万
+$17,500/呎
+(16年-04月-20日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>A | 1691呎 (4+房)
+$3166万
+$18,724/呎
+(16年-05月-04日)</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>B | 1722呎 (4+房)
+$3061万
+$17,778/呎
+(16年-05月-18日)</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="inlineStr">
+        <is>
+          <t>C | 1221呎 (3房)
+$2198万
+$18,005/呎
+(16年-04月-22日)</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="inlineStr">
+        <is>
+          <t>D | 1412呎 (4+房)
+$2421万
+$17,145/呎
+(16年-04月-22日)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
           <t>5座 销控网格图</t>
         </is>
       </c>
